--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE8D8851-DB15-584B-89A5-32852A221606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E09924-8EA1-C541-B16F-58674DCB1BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="51200" yWindow="6300" windowWidth="36000" windowHeight="22500" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
@@ -68,7 +68,7 @@
     <t>Y</t>
   </si>
   <si>
-    <t>VGASN1104QA1040</t>
+    <t>VGASN1107QA2830</t>
   </si>
 </sst>
 </file>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3E09924-8EA1-C541-B16F-58674DCB1BED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281C11CC-AA44-004B-BBC3-26F0A5B877F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="51200" yWindow="6300" windowWidth="36000" windowHeight="22500" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="8520" yWindow="5840" windowWidth="14400" windowHeight="9660" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
@@ -44,9 +44,6 @@
     <t>LPN_FLAG</t>
   </si>
   <si>
-    <t>Item_Flag</t>
-  </si>
-  <si>
     <t>Plant</t>
   </si>
   <si>
@@ -59,16 +56,19 @@
     <t>ASN_ID(S)</t>
   </si>
   <si>
-    <t>ITEM(S)</t>
-  </si>
-  <si>
     <t>QA</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>VGASN1107QA2830</t>
+    <t>ITEM_IDS</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>DD9293-100-7</t>
+  </si>
+  <si>
+    <t>Allocated</t>
   </si>
 </sst>
 </file>
@@ -449,25 +449,25 @@
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
-        <v>4</v>
-      </c>
       <c r="C1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D1" t="s">
         <v>0</v>
       </c>
       <c r="E1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
         <v>1</v>
@@ -476,7 +476,7 @@
         <v>7</v>
       </c>
       <c r="H1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
@@ -484,13 +484,13 @@
         <v>1081</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" t="s">
         <v>10</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{281C11CC-AA44-004B-BBC3-26F0A5B877F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425994FD-7542-7D43-907E-8B3383E3CCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8520" yWindow="5840" windowWidth="14400" windowHeight="9660" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
@@ -65,10 +65,10 @@
     <t>STATUS</t>
   </si>
   <si>
-    <t>DD9293-100-7</t>
-  </si>
-  <si>
-    <t>Allocated</t>
+    <t>VGASN1125QA4410</t>
+  </si>
+  <si>
+    <t>Y</t>
   </si>
 </sst>
 </file>
@@ -486,10 +486,10 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
+      <c r="C2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" t="s">
+      <c r="D2" t="s">
         <v>10</v>
       </c>
     </row>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{425994FD-7542-7D43-907E-8B3383E3CCFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE109373-6A46-2B47-A612-471AF271990A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8520" yWindow="5840" windowWidth="14400" windowHeight="9660" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="-30440" yWindow="4960" windowWidth="14400" windowHeight="9660" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
@@ -65,10 +65,10 @@
     <t>STATUS</t>
   </si>
   <si>
-    <t>VGASN1125QA4410</t>
-  </si>
-  <si>
     <t>Y</t>
+  </si>
+  <si>
+    <t>VGASN1126QA8010</t>
   </si>
 </sst>
 </file>
@@ -487,10 +487,10 @@
         <v>6</v>
       </c>
       <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
         <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE109373-6A46-2B47-A612-471AF271990A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6371E0-EA2E-044A-B6CF-15644C76BC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-30440" yWindow="4960" windowWidth="14400" windowHeight="9660" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="1" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
+    <sheet name="ItemSearch" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
   <si>
     <t>ASN_FLAG</t>
   </si>
@@ -68,19 +69,49 @@
     <t>Y</t>
   </si>
   <si>
-    <t>VGASN1126QA8010</t>
+    <t>VGASN1203QA1590</t>
+  </si>
+  <si>
+    <t>Num_of_Items_to_search</t>
+  </si>
+  <si>
+    <t>Search_by_Item</t>
+  </si>
+  <si>
+    <t>Search_by_Product_Type</t>
+  </si>
+  <si>
+    <t>Search_by_Missing_Dims</t>
+  </si>
+  <si>
+    <t>Search_by_Style</t>
+  </si>
+  <si>
+    <t>927205</t>
+  </si>
+  <si>
+    <t>104265</t>
+  </si>
+  <si>
+    <t>030588</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -104,8 +135,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -497,4 +530,96 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4038F4B-96B4-9849-B09E-D02D2C5271C4}">
+  <dimension ref="A1:H4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A2" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="2"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
+      <c r="G3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H3" s="2"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="1"/>
+      <c r="D4" s="1"/>
+      <c r="E4" s="1"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H4" s="2"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A6371E0-EA2E-044A-B6CF-15644C76BC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009E096E-6479-884B-8F74-042CC7F9037B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="1" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
     <sheet name="ItemSearch" sheetId="2" r:id="rId2"/>
+    <sheet name="Backup" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
   <si>
     <t>ASN_FLAG</t>
   </si>
@@ -69,9 +70,6 @@
     <t>Y</t>
   </si>
   <si>
-    <t>VGASN1203QA1590</t>
-  </si>
-  <si>
     <t>Num_of_Items_to_search</t>
   </si>
   <si>
@@ -87,20 +85,47 @@
     <t>Search_by_Style</t>
   </si>
   <si>
-    <t>927205</t>
-  </si>
-  <si>
-    <t>104265</t>
-  </si>
-  <si>
-    <t>030588</t>
+    <t>Search_by_Color</t>
+  </si>
+  <si>
+    <t>'0215055461;0215055462</t>
+  </si>
+  <si>
+    <t>0215055370</t>
+  </si>
+  <si>
+    <t>II5196</t>
+  </si>
+  <si>
+    <t>II5216</t>
+  </si>
+  <si>
+    <t>II5218</t>
+  </si>
+  <si>
+    <t>PBZ182</t>
+  </si>
+  <si>
+    <t>031</t>
+  </si>
+  <si>
+    <t>405</t>
+  </si>
+  <si>
+    <t>487</t>
+  </si>
+  <si>
+    <t>012</t>
+  </si>
+  <si>
+    <t>011</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -114,6 +139,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -123,7 +154,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -131,14 +162,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -519,8 +576,8 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" t="s">
-        <v>10</v>
+      <c r="C2" s="3" t="s">
+        <v>17</v>
       </c>
       <c r="D2" t="s">
         <v>9</v>
@@ -534,7 +591,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4038F4B-96B4-9849-B09E-D02D2C5271C4}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
@@ -555,21 +612,23 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="1"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
@@ -579,13 +638,15 @@
         <v>6</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="D2" s="4"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="2"/>
+      <c r="H2" s="2" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
@@ -595,13 +656,15 @@
         <v>6</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="D3" s="4"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H3" s="2"/>
+        <v>18</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
@@ -611,13 +674,87 @@
         <v>6</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
+      <c r="D4" s="4"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="4"/>
+      <c r="G5" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="7">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="6">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" t="s">
+        <v>21</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576B9CE8-4226-8341-81D1-B38F48D3C014}">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{009E096E-6479-884B-8F74-042CC7F9037B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C403592D-5303-1543-8D32-C8ED17B14634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="1" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
   <si>
     <t>ASN_FLAG</t>
   </si>
@@ -88,44 +88,23 @@
     <t>Search_by_Color</t>
   </si>
   <si>
-    <t>'0215055461;0215055462</t>
-  </si>
-  <si>
-    <t>0215055370</t>
-  </si>
-  <si>
-    <t>II5196</t>
-  </si>
-  <si>
-    <t>II5216</t>
-  </si>
-  <si>
-    <t>II5218</t>
-  </si>
-  <si>
-    <t>PBZ182</t>
+    <t>013</t>
   </si>
   <si>
     <t>031</t>
   </si>
   <si>
-    <t>405</t>
-  </si>
-  <si>
-    <t>487</t>
-  </si>
-  <si>
-    <t>012</t>
-  </si>
-  <si>
-    <t>011</t>
+    <t>106</t>
+  </si>
+  <si>
+    <t>0215055492;0215055325;0215055444;0215055326;0215055445</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -145,6 +124,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="15"/>
+      <color rgb="FFD1D2D3"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -154,27 +139,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -185,17 +155,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -576,10 +544,10 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="C2" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
         <v>9</v>
       </c>
     </row>
@@ -630,7 +598,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" ht="19" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1081</v>
       </c>
@@ -638,17 +606,17 @@
         <v>6</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="4"/>
+      <c r="D2" s="3"/>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="5" t="s">
-        <v>18</v>
+      <c r="G2" s="6">
+        <v>343738</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="19" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>1081</v>
       </c>
@@ -656,17 +624,17 @@
         <v>6</v>
       </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="4"/>
+      <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="2" t="s">
-        <v>18</v>
+      <c r="G3" s="6">
+        <v>343738</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>1081</v>
       </c>
@@ -674,72 +642,45 @@
         <v>6</v>
       </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="4"/>
+      <c r="D4" s="3"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="2" t="s">
-        <v>19</v>
+      <c r="G4" s="6">
+        <v>343738</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>1081</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="G5" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="7" t="s">
-        <v>25</v>
+      <c r="D5" s="3"/>
+      <c r="G5" s="6">
+        <v>343738</v>
+      </c>
+      <c r="H5" s="5">
+        <v>809</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>1081</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="7">
-        <v>110</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="1"/>
+      <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>1081</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="6">
-        <v>237</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="1"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>1081</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" t="s">
-        <v>21</v>
-      </c>
-      <c r="H8" s="7" t="s">
-        <v>26</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="1"/>
+      <c r="H8" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -752,8 +693,8 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
-        <v>16</v>
+      <c r="A1" s="7" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C403592D-5303-1543-8D32-C8ED17B14634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40EF30A-441B-424A-B12C-043888C5A1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
     <sheet name="ItemSearch" sheetId="2" r:id="rId2"/>
-    <sheet name="Backup" sheetId="3" r:id="rId3"/>
+    <sheet name="Recall_iLPN" sheetId="4" r:id="rId3"/>
+    <sheet name="Backup" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
   <si>
     <t>ASN_FLAG</t>
   </si>
@@ -67,9 +68,6 @@
     <t>STATUS</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
     <t>Num_of_Items_to_search</t>
   </si>
   <si>
@@ -91,13 +89,31 @@
     <t>013</t>
   </si>
   <si>
-    <t>031</t>
-  </si>
-  <si>
-    <t>106</t>
-  </si>
-  <si>
     <t>0215055492;0215055325;0215055444;0215055326;0215055445</t>
+  </si>
+  <si>
+    <t>487754-408-5.5</t>
+  </si>
+  <si>
+    <t>Allocated</t>
+  </si>
+  <si>
+    <t>20251210221319000114;20251210221319000135;20251210221319000202</t>
+  </si>
+  <si>
+    <t>20251210221319000005;20251210221319000127;20251210221319000104;20251210221319000131;20251210221319000119;20251210221319000139;</t>
+  </si>
+  <si>
+    <t>MESSAGE_TYPE</t>
+  </si>
+  <si>
+    <t>USER_ID</t>
+  </si>
+  <si>
+    <t>vgana3</t>
+  </si>
+  <si>
+    <t>PIX_XIN_InventoryAdjustment</t>
   </si>
 </sst>
 </file>
@@ -151,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -164,6 +180,7 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -498,20 +515,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627F3B23-F0A4-3C4D-9FCD-57514569CCB0}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="33.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -536,19 +554,35 @@
       <c r="H1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="I1" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1081</v>
       </c>
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
+      <c r="C2" s="8"/>
+      <c r="E2" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -580,22 +614,22 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="19" x14ac:dyDescent="0.2">
@@ -613,59 +647,35 @@
         <v>343738</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="19" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>1081</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
       <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="6">
-        <v>343738</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="G3" s="6"/>
+      <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
-        <v>1081</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="3"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="6">
-        <v>343738</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>18</v>
-      </c>
+      <c r="G4" s="6"/>
+      <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
-        <v>1081</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="1"/>
       <c r="D5" s="3"/>
-      <c r="G5" s="6">
-        <v>343738</v>
-      </c>
-      <c r="H5" s="5">
-        <v>809</v>
-      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
@@ -688,13 +698,48 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81303470-562A-AE41-967B-7DC015162790}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="21.5" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A2">
+        <v>1081</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576B9CE8-4226-8341-81D1-B38F48D3C014}">
   <dimension ref="A1"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A40EF30A-441B-424A-B12C-043888C5A1CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A6E48B-2B85-2E46-B92E-F7008EAFFB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>ASN_FLAG</t>
   </si>
@@ -114,6 +114,12 @@
   </si>
   <si>
     <t>PIX_XIN_InventoryAdjustment</t>
+  </si>
+  <si>
+    <t>DATE</t>
+  </si>
+  <si>
+    <t>Yesterday</t>
   </si>
 </sst>
 </file>
@@ -515,7 +521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627F3B23-F0A4-3C4D-9FCD-57514569CCB0}">
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
@@ -529,7 +535,7 @@
     <col min="9" max="9" width="33.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -560,8 +566,11 @@
       <c r="J1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="K1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1081</v>
       </c>
@@ -583,6 +592,9 @@
       </c>
       <c r="J2" t="s">
         <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30A6E48B-2B85-2E46-B92E-F7008EAFFB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30790851-7454-E244-AF18-4F41A002835B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="-4820" yWindow="-21100" windowWidth="38400" windowHeight="21100" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
     <sheet name="Recall_iLPN" sheetId="4" r:id="rId3"/>
     <sheet name="Backup" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="223">
   <si>
     <t>ASN_FLAG</t>
   </si>
@@ -86,40 +86,628 @@
     <t>Search_by_Color</t>
   </si>
   <si>
-    <t>013</t>
-  </si>
-  <si>
     <t>0215055492;0215055325;0215055444;0215055326;0215055445</t>
   </si>
   <si>
-    <t>487754-408-5.5</t>
-  </si>
-  <si>
-    <t>Allocated</t>
-  </si>
-  <si>
     <t>20251210221319000114;20251210221319000135;20251210221319000202</t>
   </si>
   <si>
-    <t>20251210221319000005;20251210221319000127;20251210221319000104;20251210221319000131;20251210221319000119;20251210221319000139;</t>
-  </si>
-  <si>
     <t>MESSAGE_TYPE</t>
   </si>
   <si>
     <t>USER_ID</t>
   </si>
   <si>
-    <t>vgana3</t>
-  </si>
-  <si>
-    <t>PIX_XIN_InventoryAdjustment</t>
-  </si>
-  <si>
     <t>DATE</t>
   </si>
   <si>
+    <t>XNT_ITM_MANIKEImportItemFacility</t>
+  </si>
+  <si>
+    <t>DM0825-600-7.5</t>
+  </si>
+  <si>
     <t>Yesterday</t>
+  </si>
+  <si>
+    <t>565860-10-MISC</t>
+  </si>
+  <si>
+    <t>565973-500-MISC</t>
+  </si>
+  <si>
+    <t>102180-441-7.5</t>
+  </si>
+  <si>
+    <t>102180-441-8</t>
+  </si>
+  <si>
+    <t>102180-441-8.5</t>
+  </si>
+  <si>
+    <t>102180-441-9</t>
+  </si>
+  <si>
+    <t>102180-441-9.5</t>
+  </si>
+  <si>
+    <t>102180-441-10</t>
+  </si>
+  <si>
+    <t>104238-601-6.5</t>
+  </si>
+  <si>
+    <t>104238-601-7</t>
+  </si>
+  <si>
+    <t>104238-601-7.5</t>
+  </si>
+  <si>
+    <t>104238-601-8</t>
+  </si>
+  <si>
+    <t>104238-601-8.5</t>
+  </si>
+  <si>
+    <t>104238-601-9</t>
+  </si>
+  <si>
+    <t>104238-601-9.5</t>
+  </si>
+  <si>
+    <t>104238-601-10</t>
+  </si>
+  <si>
+    <t>104238-601-10.5</t>
+  </si>
+  <si>
+    <t>104238-601-11</t>
+  </si>
+  <si>
+    <t>171965-101-5.5</t>
+  </si>
+  <si>
+    <t>171965-101-6</t>
+  </si>
+  <si>
+    <t>171965-101-6.5</t>
+  </si>
+  <si>
+    <t>171965-101-7</t>
+  </si>
+  <si>
+    <t>171965-101-7.5</t>
+  </si>
+  <si>
+    <t>171965-101-8</t>
+  </si>
+  <si>
+    <t>183279-1-6.5</t>
+  </si>
+  <si>
+    <t>183279-1-7</t>
+  </si>
+  <si>
+    <t>183279-1-7.5</t>
+  </si>
+  <si>
+    <t>183279-1-8</t>
+  </si>
+  <si>
+    <t>183279-1-8.5</t>
+  </si>
+  <si>
+    <t>183279-1-9</t>
+  </si>
+  <si>
+    <t>183279-1-9.5</t>
+  </si>
+  <si>
+    <t>183279-1-10</t>
+  </si>
+  <si>
+    <t>190072-472-4</t>
+  </si>
+  <si>
+    <t>190072-472-6</t>
+  </si>
+  <si>
+    <t>190072-472-7</t>
+  </si>
+  <si>
+    <t>190072-472-8</t>
+  </si>
+  <si>
+    <t>190072-472-9</t>
+  </si>
+  <si>
+    <t>190072-472-11</t>
+  </si>
+  <si>
+    <t>840051-141-7</t>
+  </si>
+  <si>
+    <t>840051-141-7.5</t>
+  </si>
+  <si>
+    <t>840051-141-8</t>
+  </si>
+  <si>
+    <t>840051-141-8.5</t>
+  </si>
+  <si>
+    <t>840051-141-9</t>
+  </si>
+  <si>
+    <t>840051-141-9.5</t>
+  </si>
+  <si>
+    <t>840051-141-10</t>
+  </si>
+  <si>
+    <t>840051-141-10.5</t>
+  </si>
+  <si>
+    <t>104249-171-6.5</t>
+  </si>
+  <si>
+    <t>104249-171-7</t>
+  </si>
+  <si>
+    <t>104249-171-7.5</t>
+  </si>
+  <si>
+    <t>104249-171-8</t>
+  </si>
+  <si>
+    <t>104249-171-8.5</t>
+  </si>
+  <si>
+    <t>104249-171-9</t>
+  </si>
+  <si>
+    <t>104249-171-9.5</t>
+  </si>
+  <si>
+    <t>104249-171-10</t>
+  </si>
+  <si>
+    <t>104249-171-10.5</t>
+  </si>
+  <si>
+    <t>104249-171-11</t>
+  </si>
+  <si>
+    <t>104249-171-11.5</t>
+  </si>
+  <si>
+    <t>104249-171-12</t>
+  </si>
+  <si>
+    <t>185163-71-11C</t>
+  </si>
+  <si>
+    <t>185163-71-12C</t>
+  </si>
+  <si>
+    <t>185163-71-13C</t>
+  </si>
+  <si>
+    <t>185163-71-1Y</t>
+  </si>
+  <si>
+    <t>185163-71-2Y</t>
+  </si>
+  <si>
+    <t>185163-71-3Y</t>
+  </si>
+  <si>
+    <t>962049-441-10C</t>
+  </si>
+  <si>
+    <t>962049-441-10.5C</t>
+  </si>
+  <si>
+    <t>962049-441-11C</t>
+  </si>
+  <si>
+    <t>962049-441-11.5C</t>
+  </si>
+  <si>
+    <t>962049-441-12C</t>
+  </si>
+  <si>
+    <t>962049-441-12.5C</t>
+  </si>
+  <si>
+    <t>962049-441-13C</t>
+  </si>
+  <si>
+    <t>962049-441-13.5C</t>
+  </si>
+  <si>
+    <t>962049-441-1Y</t>
+  </si>
+  <si>
+    <t>962049-441-1.5Y</t>
+  </si>
+  <si>
+    <t>962049-441-2Y</t>
+  </si>
+  <si>
+    <t>962049-441-2.5Y</t>
+  </si>
+  <si>
+    <t>962049-441-3Y</t>
+  </si>
+  <si>
+    <t>962060-181-10C</t>
+  </si>
+  <si>
+    <t>962060-181-10.5C</t>
+  </si>
+  <si>
+    <t>962060-181-11C</t>
+  </si>
+  <si>
+    <t>962060-181-11.5C</t>
+  </si>
+  <si>
+    <t>962060-181-12C</t>
+  </si>
+  <si>
+    <t>962060-181-12.5C</t>
+  </si>
+  <si>
+    <t>962060-181-13C</t>
+  </si>
+  <si>
+    <t>962060-181-13.5C</t>
+  </si>
+  <si>
+    <t>962060-181-1Y</t>
+  </si>
+  <si>
+    <t>962060-181-1.5Y</t>
+  </si>
+  <si>
+    <t>962060-181-2Y</t>
+  </si>
+  <si>
+    <t>962060-181-2.5Y</t>
+  </si>
+  <si>
+    <t>962060-181-3Y</t>
+  </si>
+  <si>
+    <t>WK0004-601-MISC</t>
+  </si>
+  <si>
+    <t>WK0004-501-MISC</t>
+  </si>
+  <si>
+    <t>WK0004-801-MISC</t>
+  </si>
+  <si>
+    <t>190088-1-7</t>
+  </si>
+  <si>
+    <t>870002-411-2C</t>
+  </si>
+  <si>
+    <t>870002-411-3C</t>
+  </si>
+  <si>
+    <t>870002-411-3.5C</t>
+  </si>
+  <si>
+    <t>870002-411-4C</t>
+  </si>
+  <si>
+    <t>870002-411-5C</t>
+  </si>
+  <si>
+    <t>870002-411-6C</t>
+  </si>
+  <si>
+    <t>870002-411-6.5C</t>
+  </si>
+  <si>
+    <t>870002-411-7C</t>
+  </si>
+  <si>
+    <t>870002-411-7.5C</t>
+  </si>
+  <si>
+    <t>870002-411-8C</t>
+  </si>
+  <si>
+    <t>870002-411-9C</t>
+  </si>
+  <si>
+    <t>870002-411-10C</t>
+  </si>
+  <si>
+    <t>147098-2-4Y</t>
+  </si>
+  <si>
+    <t>147098-2-5Y</t>
+  </si>
+  <si>
+    <t>147098-2-6Y</t>
+  </si>
+  <si>
+    <t>173204-141-6</t>
+  </si>
+  <si>
+    <t>173204-141-6.5</t>
+  </si>
+  <si>
+    <t>173204-141-7</t>
+  </si>
+  <si>
+    <t>173204-141-7.5</t>
+  </si>
+  <si>
+    <t>173204-141-8</t>
+  </si>
+  <si>
+    <t>173204-141-8.5</t>
+  </si>
+  <si>
+    <t>173204-141-9</t>
+  </si>
+  <si>
+    <t>173204-141-9.5</t>
+  </si>
+  <si>
+    <t>173204-141-10</t>
+  </si>
+  <si>
+    <t>173204-141-10.5</t>
+  </si>
+  <si>
+    <t>173204-141-11</t>
+  </si>
+  <si>
+    <t>173204-141-11.5</t>
+  </si>
+  <si>
+    <t>173204-141-12</t>
+  </si>
+  <si>
+    <t>173204-141-12.5</t>
+  </si>
+  <si>
+    <t>173204-141-13</t>
+  </si>
+  <si>
+    <t>173204-141-14</t>
+  </si>
+  <si>
+    <t>173204-141-15</t>
+  </si>
+  <si>
+    <t>103151-141-5</t>
+  </si>
+  <si>
+    <t>103151-141-5.5</t>
+  </si>
+  <si>
+    <t>103151-141-6</t>
+  </si>
+  <si>
+    <t>103151-141-6.5</t>
+  </si>
+  <si>
+    <t>103151-141-7</t>
+  </si>
+  <si>
+    <t>103151-141-7.5</t>
+  </si>
+  <si>
+    <t>103151-141-8</t>
+  </si>
+  <si>
+    <t>103151-141-8.5</t>
+  </si>
+  <si>
+    <t>183279-161-7.5</t>
+  </si>
+  <si>
+    <t>BG0036-401-MISC</t>
+  </si>
+  <si>
+    <t>840051-141-11</t>
+  </si>
+  <si>
+    <t>840055-11-9.5</t>
+  </si>
+  <si>
+    <t>840055-11-10</t>
+  </si>
+  <si>
+    <t>840055-11-10.5</t>
+  </si>
+  <si>
+    <t>840055-11-11</t>
+  </si>
+  <si>
+    <t>190088-1-9</t>
+  </si>
+  <si>
+    <t>141516-141-5</t>
+  </si>
+  <si>
+    <t>141516-141-6</t>
+  </si>
+  <si>
+    <t>141516-141-6.5</t>
+  </si>
+  <si>
+    <t>141516-141-7</t>
+  </si>
+  <si>
+    <t>141516-141-7.5</t>
+  </si>
+  <si>
+    <t>141516-141-8</t>
+  </si>
+  <si>
+    <t>141516-141-8.5</t>
+  </si>
+  <si>
+    <t>141516-141-9</t>
+  </si>
+  <si>
+    <t>141516-141-9.5</t>
+  </si>
+  <si>
+    <t>147115-61-3.5Y</t>
+  </si>
+  <si>
+    <t>147115-61-4Y</t>
+  </si>
+  <si>
+    <t>147115-61-5Y</t>
+  </si>
+  <si>
+    <t>147115-61-5.5Y</t>
+  </si>
+  <si>
+    <t>147115-61-6Y</t>
+  </si>
+  <si>
+    <t>850301-411-2C</t>
+  </si>
+  <si>
+    <t>850301-411-2.5C</t>
+  </si>
+  <si>
+    <t>850301-411-3C</t>
+  </si>
+  <si>
+    <t>850301-411-3.5C</t>
+  </si>
+  <si>
+    <t>850301-411-4C</t>
+  </si>
+  <si>
+    <t>850301-411-4.5C</t>
+  </si>
+  <si>
+    <t>850301-411-5C</t>
+  </si>
+  <si>
+    <t>850301-411-5.5C</t>
+  </si>
+  <si>
+    <t>850301-411-6.5C</t>
+  </si>
+  <si>
+    <t>850301-411-7C</t>
+  </si>
+  <si>
+    <t>850301-411-7.5C</t>
+  </si>
+  <si>
+    <t>850301-411-8C</t>
+  </si>
+  <si>
+    <t>850301-411-8.5C</t>
+  </si>
+  <si>
+    <t>850301-411-9.5C</t>
+  </si>
+  <si>
+    <t>855091-2-3.5Y</t>
+  </si>
+  <si>
+    <t>855091-2-4Y</t>
+  </si>
+  <si>
+    <t>855091-2-5Y</t>
+  </si>
+  <si>
+    <t>855091-2-6Y</t>
+  </si>
+  <si>
+    <t>679059-771-6.5</t>
+  </si>
+  <si>
+    <t>679059-771-7.5</t>
+  </si>
+  <si>
+    <t>679059-771-8</t>
+  </si>
+  <si>
+    <t>679059-771-8.5</t>
+  </si>
+  <si>
+    <t>679059-771-9</t>
+  </si>
+  <si>
+    <t>679059-771-9.5</t>
+  </si>
+  <si>
+    <t>679059-771-10</t>
+  </si>
+  <si>
+    <t>679059-771-10.5</t>
+  </si>
+  <si>
+    <t>679059-771-11.5</t>
+  </si>
+  <si>
+    <t>679059-771-13</t>
+  </si>
+  <si>
+    <t>183278-101-9.5</t>
+  </si>
+  <si>
+    <t>183278-101-10</t>
+  </si>
+  <si>
+    <t>183278-101-10.5</t>
+  </si>
+  <si>
+    <t>183278-101-11</t>
+  </si>
+  <si>
+    <t>183278-102-9.5</t>
+  </si>
+  <si>
+    <t>183278-102-10</t>
+  </si>
+  <si>
+    <t>183278-102-10.5</t>
+  </si>
+  <si>
+    <t>183278-102-11</t>
+  </si>
+  <si>
+    <t>183279-101-9.5</t>
+  </si>
+  <si>
+    <t>183279-101-10</t>
+  </si>
+  <si>
+    <t>183279-101-10.5</t>
+  </si>
+  <si>
+    <t>183279-101-11</t>
+  </si>
+  <si>
+    <t>183279-161-9</t>
+  </si>
+  <si>
+    <t>183279-161-9.5</t>
+  </si>
+  <si>
+    <t>183279-161-10</t>
+  </si>
+  <si>
+    <t>81ASN1219QA2130;81ASN1219QA1341</t>
   </si>
 </sst>
 </file>
@@ -561,13 +1149,13 @@
         <v>8</v>
       </c>
       <c r="I1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="K1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -577,24 +1165,18 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="E2" s="7" t="s">
+      <c r="C2" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="E2" s="7"/>
+      <c r="I2" t="s">
         <v>20</v>
       </c>
-      <c r="G2" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" t="s">
-        <v>18</v>
-      </c>
-      <c r="I2" t="s">
-        <v>24</v>
-      </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="K2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -605,13 +1187,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4038F4B-96B4-9849-B09E-D02D2C5271C4}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H292"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.83203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="21.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -644,7 +1226,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="19" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1081</v>
       </c>
@@ -652,57 +1234,2570 @@
         <v>6</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="3"/>
+      <c r="D2" t="s">
+        <v>23</v>
+      </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="6">
-        <v>343738</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>15</v>
-      </c>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" ht="19" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
+      <c r="A3" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C3" s="1"/>
-      <c r="D3" s="3"/>
+      <c r="D3" s="3" t="s">
+        <v>24</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="6"/>
       <c r="H3" s="2"/>
     </row>
     <row r="4" spans="1:8" ht="19" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
+      <c r="A4" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="C4" s="1"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="3" t="s">
+        <v>25</v>
+      </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="6"/>
       <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" ht="19" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="D5" s="3"/>
+      <c r="A5" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>26</v>
+      </c>
       <c r="G5" s="6"/>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
+      <c r="A6" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D6" t="s">
+        <v>27</v>
+      </c>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+      <c r="A7" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D7" t="s">
+        <v>28</v>
+      </c>
       <c r="H7" s="4"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
+      <c r="A8" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8" t="s">
+        <v>29</v>
+      </c>
       <c r="H8" s="5"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A14" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A15" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D15" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A16" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A17" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A18" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D18" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A19" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A20" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D20" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A21" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D21" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A22" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A23" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D23" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A24" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A25" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A26" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D26" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A27" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D27" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A28" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A29" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D29" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A30" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D30" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A31" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D31" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A32" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D32" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A33" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A34" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D35" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D36" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D37" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D38" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D39" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D40" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A41" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D41" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A42" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D42" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A43" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D43" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A44" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D44" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A45" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D45" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A46" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D46" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A47" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D47" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A48" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D48" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A49" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D49" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A50" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D50" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A51" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D51" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A52" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D52" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A53" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D53" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A54" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D54" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A55" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B55" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D55" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A56" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D56" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A57" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D57" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A58" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D58" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A59" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D59" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A60" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D60" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A61" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D61" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A62" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D62" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A63" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D63" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A64" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D64" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A65" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D65" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A66" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A67" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D67" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A68" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D68" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A69" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D69" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A70" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D70" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A71" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D71" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D72" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D73" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D74" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D75" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D76" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D77" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B78" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D78" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D79" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B80" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D80" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D81" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B82" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D82" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D83" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D84" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B85" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D85" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B86" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D86" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B87" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D87" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B88" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D88" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B89" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D89" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B90" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D90" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B91" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D91" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B92" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D92" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D93" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D94" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B95" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D95" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B96" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D96" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B97" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D97" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D98" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D99" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D100" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B101" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D101" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B102" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D102" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A103" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B103" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D103" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A104" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B104" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D104" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A105" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B105" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D105" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A106" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B106" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D106" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A107" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B107" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D107" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A108" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B108" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D108" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A109" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B109" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D109" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A110" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B110" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D110" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A111" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B111" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D111" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A112" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B112" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D112" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A113" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B113" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D113" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A114" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B114" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D114" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A115" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B115" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D115" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A116" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B116" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D116" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A117" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B117" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D117" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A118" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B118" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D118" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A119" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B119" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D119" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A120" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B120" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D120" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A121" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B121" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D121" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A122" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B122" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D122" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A123" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B123" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D123" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A124" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B124" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D124" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A125" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B125" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D125" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A126" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B126" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D126" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A127" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B127" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D127" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A128" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B128" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D128" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A129" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B129" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D129" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A130" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B130" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D130" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A131" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B131" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D131" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A132" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B132" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D132" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A133" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B133" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D133" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A134" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B134" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D134" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A135" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B135" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D135" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A136" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B136" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D136" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A137" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B137" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D137" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A138" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B138" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D138" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A139" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B139" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D139" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A140" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B140" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D140" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A141" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B141" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D141" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A142" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B142" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D142" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A143" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B143" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D143" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A144" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B144" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D144" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A145" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B145" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D145" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A146" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B146" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D146" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A147" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B147" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D147" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A148" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B148" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D148" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A149" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B149" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D149" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A150" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B150" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D150" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A151" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B151" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D151" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A152" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B152" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D152" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A153" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B153" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D153" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A154" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B154" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D154" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A155" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B155" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D155" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A156" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D156" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A157" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D157" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A158" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B158" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D158" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A159" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B159" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D159" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A160" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B160" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D160" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A161" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B161" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D161" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A162" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B162" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D162" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A163" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B163" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D163" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A164" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B164" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D164" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A165" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B165" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D165" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A166" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B166" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D166" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A167" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B167" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D167" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A168" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B168" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D168" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A169" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B169" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D169" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A170" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B170" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D170" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A171" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B171" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D171" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A172" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D172" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A173" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D173" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A174" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D174" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A175" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D175" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A176" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D176" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A177" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B177" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D177" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A178" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B178" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D178" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A179" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B179" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D179" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A180" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B180" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D180" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A181" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B181" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D181" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A182" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B182" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D182" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A183" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B183" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D183" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A184" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B184" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D184" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A185" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B185" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D185" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A186" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B186" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D186" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A187" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B187" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D187" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A188" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B188" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D188" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A189" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B189" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D189" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A190" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B190" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D190" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A191" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B191" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D191" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A192" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B192" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D192" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A193" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B193" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D193" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A194" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B194" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D194" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A195" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B195" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D195" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A196" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B196" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D196" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A197" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B197" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D197" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A198" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D198" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A199" s="1">
+        <v>1081</v>
+      </c>
+      <c r="B199" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D199" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A200" s="1"/>
+      <c r="B200" s="1"/>
+      <c r="D200" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A201" s="1"/>
+      <c r="B201" s="1"/>
+    </row>
+    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A202" s="1"/>
+      <c r="B202" s="1"/>
+    </row>
+    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A203" s="1"/>
+      <c r="B203" s="1"/>
+    </row>
+    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A204" s="1"/>
+      <c r="B204" s="1"/>
+    </row>
+    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A205" s="1"/>
+      <c r="B205" s="1"/>
+    </row>
+    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A206" s="1"/>
+      <c r="B206" s="1"/>
+    </row>
+    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A207" s="1"/>
+      <c r="B207" s="1"/>
+    </row>
+    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A208" s="1"/>
+      <c r="B208" s="1"/>
+    </row>
+    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A209" s="1"/>
+      <c r="B209" s="1"/>
+    </row>
+    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A210" s="1"/>
+      <c r="B210" s="1"/>
+    </row>
+    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A211" s="1"/>
+      <c r="B211" s="1"/>
+    </row>
+    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A212" s="1"/>
+      <c r="B212" s="1"/>
+    </row>
+    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A213" s="1"/>
+      <c r="B213" s="1"/>
+    </row>
+    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A214" s="1"/>
+      <c r="B214" s="1"/>
+    </row>
+    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A215" s="1"/>
+      <c r="B215" s="1"/>
+    </row>
+    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A216" s="1"/>
+      <c r="B216" s="1"/>
+    </row>
+    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A217" s="1"/>
+      <c r="B217" s="1"/>
+    </row>
+    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A218" s="1"/>
+      <c r="B218" s="1"/>
+    </row>
+    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A219" s="1"/>
+      <c r="B219" s="1"/>
+    </row>
+    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A220" s="1"/>
+      <c r="B220" s="1"/>
+    </row>
+    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A221" s="1"/>
+      <c r="B221" s="1"/>
+    </row>
+    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A222" s="1"/>
+      <c r="B222" s="1"/>
+    </row>
+    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A223" s="1"/>
+      <c r="B223" s="1"/>
+    </row>
+    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A224" s="1"/>
+      <c r="B224" s="1"/>
+    </row>
+    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A225" s="1"/>
+      <c r="B225" s="1"/>
+    </row>
+    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A226" s="1"/>
+      <c r="B226" s="1"/>
+    </row>
+    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A227" s="1"/>
+      <c r="B227" s="1"/>
+    </row>
+    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A228" s="1"/>
+      <c r="B228" s="1"/>
+    </row>
+    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A229" s="1"/>
+      <c r="B229" s="1"/>
+    </row>
+    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A230" s="1"/>
+      <c r="B230" s="1"/>
+    </row>
+    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A231" s="1"/>
+      <c r="B231" s="1"/>
+    </row>
+    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A232" s="1"/>
+      <c r="B232" s="1"/>
+    </row>
+    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A233" s="1"/>
+      <c r="B233" s="1"/>
+    </row>
+    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A234" s="1"/>
+      <c r="B234" s="1"/>
+    </row>
+    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A235" s="1"/>
+      <c r="B235" s="1"/>
+    </row>
+    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A236" s="1"/>
+      <c r="B236" s="1"/>
+    </row>
+    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A237" s="1"/>
+      <c r="B237" s="1"/>
+    </row>
+    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A238" s="1"/>
+      <c r="B238" s="1"/>
+    </row>
+    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A239" s="1"/>
+      <c r="B239" s="1"/>
+    </row>
+    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A240" s="1"/>
+      <c r="B240" s="1"/>
+    </row>
+    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A241" s="1"/>
+      <c r="B241" s="1"/>
+    </row>
+    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A242" s="1"/>
+      <c r="B242" s="1"/>
+    </row>
+    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A243" s="1"/>
+      <c r="B243" s="1"/>
+    </row>
+    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A244" s="1"/>
+      <c r="B244" s="1"/>
+    </row>
+    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A245" s="1"/>
+      <c r="B245" s="1"/>
+    </row>
+    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A246" s="1"/>
+      <c r="B246" s="1"/>
+    </row>
+    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A247" s="1"/>
+      <c r="B247" s="1"/>
+    </row>
+    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A248" s="1"/>
+      <c r="B248" s="1"/>
+    </row>
+    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A249" s="1"/>
+      <c r="B249" s="1"/>
+    </row>
+    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A250" s="1"/>
+      <c r="B250" s="1"/>
+    </row>
+    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A251" s="1"/>
+      <c r="B251" s="1"/>
+    </row>
+    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A252" s="1"/>
+      <c r="B252" s="1"/>
+    </row>
+    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A253" s="1"/>
+      <c r="B253" s="1"/>
+    </row>
+    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A254" s="1"/>
+      <c r="B254" s="1"/>
+    </row>
+    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A255" s="1"/>
+      <c r="B255" s="1"/>
+    </row>
+    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A256" s="1"/>
+      <c r="B256" s="1"/>
+    </row>
+    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A257" s="1"/>
+      <c r="B257" s="1"/>
+    </row>
+    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A258" s="1"/>
+      <c r="B258" s="1"/>
+    </row>
+    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A259" s="1"/>
+      <c r="B259" s="1"/>
+    </row>
+    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A260" s="1"/>
+      <c r="B260" s="1"/>
+    </row>
+    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A261" s="1"/>
+      <c r="B261" s="1"/>
+    </row>
+    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A262" s="1"/>
+      <c r="B262" s="1"/>
+    </row>
+    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A263" s="1"/>
+      <c r="B263" s="1"/>
+    </row>
+    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A264" s="1"/>
+      <c r="B264" s="1"/>
+    </row>
+    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A265" s="1"/>
+      <c r="B265" s="1"/>
+    </row>
+    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A266" s="1"/>
+      <c r="B266" s="1"/>
+    </row>
+    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A267" s="1"/>
+      <c r="B267" s="1"/>
+    </row>
+    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A268" s="1"/>
+      <c r="B268" s="1"/>
+    </row>
+    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A269" s="1"/>
+      <c r="B269" s="1"/>
+    </row>
+    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A270" s="1"/>
+      <c r="B270" s="1"/>
+    </row>
+    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A271" s="1"/>
+      <c r="B271" s="1"/>
+    </row>
+    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A272" s="1"/>
+      <c r="B272" s="1"/>
+    </row>
+    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A273" s="1"/>
+      <c r="B273" s="1"/>
+    </row>
+    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A274" s="1"/>
+      <c r="B274" s="1"/>
+    </row>
+    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A275" s="1"/>
+      <c r="B275" s="1"/>
+    </row>
+    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A276" s="1"/>
+      <c r="B276" s="1"/>
+    </row>
+    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A277" s="1"/>
+      <c r="B277" s="1"/>
+    </row>
+    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A278" s="1"/>
+      <c r="B278" s="1"/>
+    </row>
+    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A279" s="1"/>
+      <c r="B279" s="1"/>
+    </row>
+    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A280" s="1"/>
+      <c r="B280" s="1"/>
+    </row>
+    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A281" s="1"/>
+      <c r="B281" s="1"/>
+    </row>
+    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A282" s="1"/>
+      <c r="B282" s="1"/>
+    </row>
+    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A283" s="1"/>
+      <c r="B283" s="1"/>
+    </row>
+    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A284" s="1"/>
+      <c r="B284" s="1"/>
+    </row>
+    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A285" s="1"/>
+      <c r="B285" s="1"/>
+    </row>
+    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A286" s="1"/>
+      <c r="B286" s="1"/>
+    </row>
+    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A287" s="1"/>
+      <c r="B287" s="1"/>
+    </row>
+    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A288" s="1"/>
+      <c r="B288" s="1"/>
+    </row>
+    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A289" s="1"/>
+      <c r="B289" s="1"/>
+    </row>
+    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A290" s="1"/>
+      <c r="B290" s="1"/>
+    </row>
+    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A291" s="1"/>
+      <c r="B291" s="1"/>
+    </row>
+    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A292" s="1"/>
+      <c r="B292" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -736,7 +3831,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -747,11 +3842,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576B9CE8-4226-8341-81D1-B38F48D3C014}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="166.1640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB916783-ED98-0149-807F-3B17A0ACCAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF85218-C7FB-044F-9F99-2720ADB78D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" activeTab="1" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="-37380" yWindow="-2980" windowWidth="36000" windowHeight="21000" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>ASN_FLAG</t>
   </si>
@@ -101,22 +101,25 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>XNT_ITM_MANIKEImportItemFacility</t>
-  </si>
-  <si>
-    <t>DM0825-600-7.5</t>
-  </si>
-  <si>
-    <t>Yesterday</t>
-  </si>
-  <si>
     <t>0215055575</t>
   </si>
   <si>
-    <t>SX5728-411-S</t>
-  </si>
-  <si>
-    <t>SX5728-412-XL</t>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Apparel</t>
+  </si>
+  <si>
+    <t>20251204155507000004</t>
+  </si>
+  <si>
+    <t>vgana3</t>
+  </si>
+  <si>
+    <t>706510-306-L/XL</t>
+  </si>
+  <si>
+    <t>PIX_XIN_InventoryAdjustment</t>
   </si>
 </sst>
 </file>
@@ -530,6 +533,7 @@
     <col min="7" max="7" width="14" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="33.5" customWidth="1"/>
+    <col min="10" max="10" width="14.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.2">
@@ -575,17 +579,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="7"/>
+      <c r="G2" t="s">
+        <v>25</v>
+      </c>
       <c r="I2" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="K2">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -642,26 +651,24 @@
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="D2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3"/>
+      <c r="E2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
     </row>
     <row r="3" spans="1:8" ht="19" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
-        <v>1081</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>6</v>
-      </c>
+      <c r="A3" s="1"/>
+      <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="D3" s="3"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="6"/>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FF85218-C7FB-044F-9F99-2720ADB78D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E99BBF-040F-C344-8758-1A984F9A4411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37380" yWindow="-2980" windowWidth="36000" windowHeight="21000" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="-37380" yWindow="-3000" windowWidth="36000" windowHeight="21000" activeTab="1" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
   <si>
     <t>ASN_FLAG</t>
   </si>
@@ -86,9 +86,6 @@
     <t>Search_by_Color</t>
   </si>
   <si>
-    <t>0215055492;0215055325;0215055444;0215055326;0215055445</t>
-  </si>
-  <si>
     <t>20251210221319000114;20251210221319000135;20251210221319000202</t>
   </si>
   <si>
@@ -101,25 +98,31 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>0215055575</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
     <t>Apparel</t>
   </si>
   <si>
-    <t>20251204155507000004</t>
-  </si>
-  <si>
     <t>vgana3</t>
   </si>
   <si>
-    <t>706510-306-L/XL</t>
-  </si>
-  <si>
     <t>PIX_XIN_InventoryAdjustment</t>
+  </si>
+  <si>
+    <t>81ASN0114QA1240</t>
+  </si>
+  <si>
+    <t>20251207133116000001;20251210221319000104;20251208173045000003;20251203004902000001;20251204184940000009;20251223154106000004</t>
+  </si>
+  <si>
+    <t>;20260114000000000001;20260114000000000002</t>
+  </si>
+  <si>
+    <t>20260114000000000001;20260114000000000002</t>
+  </si>
+  <si>
+    <t>DD9293-100-7</t>
   </si>
 </sst>
 </file>
@@ -526,7 +529,7 @@
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="26.1640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -562,13 +565,13 @@
         <v>8</v>
       </c>
       <c r="I1" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>18</v>
-      </c>
-      <c r="K1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
@@ -579,19 +582,19 @@
         <v>6</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="E2" s="7" t="s">
+        <v>26</v>
+      </c>
       <c r="G2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -656,10 +659,10 @@
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
@@ -1881,7 +1884,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1891,7 +1894,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576B9CE8-4226-8341-81D1-B38F48D3C014}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="166.1640625" bestFit="1" customWidth="1"/>
@@ -1899,7 +1902,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" s="7" t="s">
-        <v>15</v>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A4" s="8" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05E99BBF-040F-C344-8758-1A984F9A4411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE1BA31-445C-004A-8FBE-40D857627FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37380" yWindow="-3000" windowWidth="36000" windowHeight="21000" activeTab="1" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="-38400" yWindow="-3000" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>ASN_FLAG</t>
   </si>
@@ -98,19 +98,10 @@
     <t>DATE</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>Apparel</t>
-  </si>
-  <si>
     <t>vgana3</t>
   </si>
   <si>
     <t>PIX_XIN_InventoryAdjustment</t>
-  </si>
-  <si>
-    <t>81ASN0114QA1240</t>
   </si>
   <si>
     <t>20251207133116000001;20251210221319000104;20251208173045000003;20251203004902000001;20251204184940000009;20251223154106000004</t>
@@ -124,12 +115,18 @@
   <si>
     <t>DD9293-100-7</t>
   </si>
+  <si>
+    <t>81ASN0122QA3510</t>
+  </si>
+  <si>
+    <t>HJ1183</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -147,12 +144,6 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <color rgb="FFD1D2D3"/>
-      <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -176,20 +167,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -581,20 +570,20 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>26</v>
-      </c>
       <c r="G2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K2">
         <v>7</v>
@@ -608,7 +597,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4038F4B-96B4-9849-B09E-D02D2C5271C4}">
-  <dimension ref="A1:H292"/>
+  <dimension ref="A1:H501"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
@@ -654,1203 +643,3024 @@
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1">
-        <v>1</v>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="5" t="s">
+        <v>26</v>
       </c>
-      <c r="D2" s="3"/>
-      <c r="E2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-    </row>
-    <row r="3" spans="1:8" ht="19" x14ac:dyDescent="0.2">
+      <c r="H2" s="6"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="1"/>
-      <c r="D3" s="3"/>
+      <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="2"/>
-    </row>
-    <row r="4" spans="1:8" ht="19" x14ac:dyDescent="0.2">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="3"/>
+      <c r="D4" s="1"/>
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="2"/>
-    </row>
-    <row r="5" spans="1:8" ht="19" x14ac:dyDescent="0.2">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
-      <c r="D5" s="3"/>
-      <c r="G5" s="6"/>
+      <c r="D5" s="1"/>
+      <c r="G5" s="5"/>
       <c r="H5" s="5"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
-      <c r="D6" s="3"/>
+      <c r="D6" s="1"/>
+      <c r="G6" s="5"/>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
-      <c r="D7" s="3"/>
-      <c r="H7" s="4"/>
+      <c r="D7" s="1"/>
+      <c r="G7" s="5"/>
+      <c r="H7" s="5"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
-      <c r="D8" s="3"/>
+      <c r="D8" s="2"/>
+      <c r="G8" s="5"/>
       <c r="H8" s="5"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
-      <c r="D9" s="3"/>
+      <c r="D9" s="2"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="5"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
-      <c r="D10" s="3"/>
+      <c r="D10" s="2"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="5"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
-      <c r="D11" s="3"/>
+      <c r="D11" s="2"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="5"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
-      <c r="D12" s="3"/>
+      <c r="D12" s="2"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
+      <c r="G13" s="5"/>
+      <c r="H13" s="5"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
+      <c r="G14" s="5"/>
+      <c r="H14" s="5"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
+      <c r="G15" s="5"/>
+      <c r="H15" s="5"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G16" s="5"/>
+      <c r="H16" s="5"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G17" s="5"/>
+      <c r="H17" s="5"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G18" s="5"/>
+      <c r="H18" s="5"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G19" s="5"/>
+      <c r="H19" s="5"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G20" s="5"/>
+      <c r="H20" s="5"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G21" s="5"/>
+      <c r="H21" s="5"/>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
-    </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G22" s="5"/>
+      <c r="H22" s="5"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G23" s="5"/>
+      <c r="H23" s="5"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G24" s="5"/>
+      <c r="H24" s="5"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G25" s="5"/>
+      <c r="H25" s="5"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G26" s="5"/>
+      <c r="H26" s="5"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G27" s="5"/>
+      <c r="H27" s="5"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G29" s="5"/>
+      <c r="H29" s="5"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G30" s="5"/>
+      <c r="H30" s="5"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G31" s="5"/>
+      <c r="H31" s="5"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
-    </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G32" s="5"/>
+      <c r="H32" s="5"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
-    </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G33" s="5"/>
+      <c r="H33" s="5"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
-    </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G34" s="5"/>
+      <c r="H34" s="5"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
-    </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G35" s="5"/>
+      <c r="H35" s="5"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G36" s="5"/>
+      <c r="H36" s="5"/>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
-    </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
-    </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G38" s="5"/>
+      <c r="H38" s="5"/>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
-    </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G39" s="5"/>
+      <c r="H39" s="5"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
-    </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G40" s="5"/>
+      <c r="H40" s="5"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
-    </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G41" s="5"/>
+      <c r="H41" s="5"/>
+    </row>
+    <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
-    </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G42" s="5"/>
+      <c r="H42" s="5"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
-    </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G43" s="5"/>
+      <c r="H43" s="5"/>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
-    </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G44" s="5"/>
+      <c r="H44" s="5"/>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
-    </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G45" s="5"/>
+      <c r="H45" s="5"/>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
-    </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G46" s="5"/>
+      <c r="H46" s="5"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
-    </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G47" s="5"/>
+      <c r="H47" s="5"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G48" s="5"/>
+      <c r="H48" s="5"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G49" s="5"/>
+      <c r="H49" s="5"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G50" s="5"/>
+      <c r="H50" s="5"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G51" s="5"/>
+      <c r="H51" s="5"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G53" s="5"/>
+      <c r="H53" s="5"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G54" s="5"/>
+      <c r="H54" s="5"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
-    </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G55" s="5"/>
+      <c r="H55" s="5"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G56" s="5"/>
+      <c r="H56" s="5"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
-    </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G57" s="5"/>
+      <c r="H57" s="5"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G58" s="5"/>
+      <c r="H58" s="5"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
-    </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G60" s="5"/>
+      <c r="H60" s="5"/>
+    </row>
+    <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G61" s="5"/>
+      <c r="H61" s="5"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G62" s="5"/>
+      <c r="H62" s="5"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G63" s="5"/>
+      <c r="H63" s="5"/>
+    </row>
+    <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
-    </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G64" s="5"/>
+      <c r="H64" s="5"/>
+    </row>
+    <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
-    </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G65" s="5"/>
+      <c r="H65" s="5"/>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
-    </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G66" s="5"/>
+      <c r="H66" s="5"/>
+    </row>
+    <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
-    </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G67" s="5"/>
+      <c r="H67" s="5"/>
+    </row>
+    <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
-    </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G68" s="5"/>
+      <c r="H68" s="5"/>
+    </row>
+    <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
-    </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G69" s="5"/>
+      <c r="H69" s="5"/>
+    </row>
+    <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
-    </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G70" s="5"/>
+      <c r="H70" s="5"/>
+    </row>
+    <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
-    </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G71" s="5"/>
+      <c r="H71" s="5"/>
+    </row>
+    <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
-    </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
-    </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G73" s="5"/>
+      <c r="H73" s="5"/>
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
-    </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G74" s="5"/>
+      <c r="H74" s="5"/>
+    </row>
+    <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
-    </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G75" s="5"/>
+      <c r="H75" s="5"/>
+    </row>
+    <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
-    </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G76" s="5"/>
+      <c r="H76" s="5"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
-    </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G77" s="5"/>
+      <c r="H77" s="5"/>
+    </row>
+    <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
-    </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G78" s="5"/>
+      <c r="H78" s="5"/>
+    </row>
+    <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
-    </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G79" s="5"/>
+      <c r="H79" s="5"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
-    </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G80" s="5"/>
+      <c r="H80" s="5"/>
+    </row>
+    <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
-    </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G81" s="5"/>
+      <c r="H81" s="5"/>
+    </row>
+    <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
-    </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G82" s="5"/>
+      <c r="H82" s="5"/>
+    </row>
+    <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
-    </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G83" s="5"/>
+      <c r="H83" s="5"/>
+    </row>
+    <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
-    </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G84" s="5"/>
+      <c r="H84" s="5"/>
+    </row>
+    <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
-    </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G85" s="5"/>
+      <c r="H85" s="5"/>
+    </row>
+    <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
-    </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G86" s="5"/>
+      <c r="H86" s="5"/>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
-    </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G87" s="5"/>
+      <c r="H87" s="5"/>
+    </row>
+    <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
-    </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G88" s="5"/>
+      <c r="H88" s="5"/>
+    </row>
+    <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
-    </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
-    </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G90" s="5"/>
+      <c r="H90" s="5"/>
+    </row>
+    <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
-    </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G91" s="5"/>
+      <c r="H91" s="5"/>
+    </row>
+    <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
-    </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G92" s="5"/>
+      <c r="H92" s="5"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
-    </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G93" s="5"/>
+      <c r="H93" s="5"/>
+    </row>
+    <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
-    </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G94" s="5"/>
+      <c r="H94" s="5"/>
+    </row>
+    <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
-    </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G95" s="5"/>
+      <c r="H95" s="5"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
-    </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G96" s="5"/>
+      <c r="H96" s="5"/>
+    </row>
+    <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
-    </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G97" s="5"/>
+      <c r="H97" s="5"/>
+    </row>
+    <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
-    </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G98" s="5"/>
+      <c r="H98" s="5"/>
+    </row>
+    <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
-    </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G99" s="5"/>
+      <c r="H99" s="5"/>
+    </row>
+    <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
-    </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G100" s="5"/>
+      <c r="H100" s="5"/>
+    </row>
+    <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
-    </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G101" s="5"/>
+      <c r="H101" s="5"/>
+    </row>
+    <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
-    </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G102" s="5"/>
+      <c r="H102" s="5"/>
+    </row>
+    <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
-    </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G103" s="5"/>
+      <c r="H103" s="5"/>
+    </row>
+    <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
-    </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+    </row>
+    <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
-    </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+    </row>
+    <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
-    </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G106" s="5"/>
+      <c r="H106" s="5"/>
+    </row>
+    <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
-    </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G107" s="5"/>
+      <c r="H107" s="5"/>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
-    </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G108" s="5"/>
+      <c r="H108" s="5"/>
+    </row>
+    <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
-    </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G109" s="5"/>
+      <c r="H109" s="5"/>
+    </row>
+    <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
-    </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G110" s="5"/>
+      <c r="H110" s="5"/>
+    </row>
+    <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
-    </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G111" s="5"/>
+      <c r="H111" s="5"/>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
-    </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G112" s="5"/>
+      <c r="H112" s="5"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
-    </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G113" s="5"/>
+      <c r="H113" s="5"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
-    </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G114" s="5"/>
+      <c r="H114" s="5"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
-    </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G115" s="5"/>
+      <c r="H115" s="5"/>
+    </row>
+    <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
-    </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G116" s="5"/>
+      <c r="H116" s="5"/>
+    </row>
+    <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
-    </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G117" s="5"/>
+      <c r="H117" s="5"/>
+    </row>
+    <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
-    </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G118" s="5"/>
+      <c r="H118" s="5"/>
+    </row>
+    <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
-    </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G119" s="5"/>
+      <c r="H119" s="5"/>
+    </row>
+    <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
-    </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G120" s="5"/>
+      <c r="H120" s="5"/>
+    </row>
+    <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
-    </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G121" s="5"/>
+      <c r="H121" s="5"/>
+    </row>
+    <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
-    </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G122" s="5"/>
+      <c r="H122" s="5"/>
+    </row>
+    <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
-    </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G123" s="5"/>
+      <c r="H123" s="5"/>
+    </row>
+    <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
-    </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G124" s="5"/>
+      <c r="H124" s="5"/>
+    </row>
+    <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
-    </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G125" s="5"/>
+      <c r="H125" s="5"/>
+    </row>
+    <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
-    </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G126" s="5"/>
+      <c r="H126" s="5"/>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
-    </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G127" s="5"/>
+      <c r="H127" s="5"/>
+    </row>
+    <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
-    </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G128" s="5"/>
+      <c r="H128" s="5"/>
+    </row>
+    <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
-    </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G129" s="5"/>
+      <c r="H129" s="5"/>
+    </row>
+    <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
-    </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G130" s="5"/>
+      <c r="H130" s="5"/>
+    </row>
+    <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
-    </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G131" s="5"/>
+      <c r="H131" s="5"/>
+    </row>
+    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
-    </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G132" s="5"/>
+      <c r="H132" s="5"/>
+    </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
-    </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G133" s="5"/>
+      <c r="H133" s="5"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
-    </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G134" s="5"/>
+      <c r="H134" s="5"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
-    </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G135" s="5"/>
+      <c r="H135" s="5"/>
+    </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
-    </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G136" s="5"/>
+      <c r="H136" s="5"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
-    </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G137" s="5"/>
+      <c r="H137" s="5"/>
+    </row>
+    <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
-    </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G138" s="5"/>
+      <c r="H138" s="5"/>
+    </row>
+    <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
-    </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G139" s="5"/>
+      <c r="H139" s="5"/>
+    </row>
+    <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
-    </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G140" s="5"/>
+      <c r="H140" s="5"/>
+    </row>
+    <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
-    </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G141" s="5"/>
+      <c r="H141" s="5"/>
+    </row>
+    <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
-    </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G142" s="5"/>
+      <c r="H142" s="5"/>
+    </row>
+    <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
-    </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G143" s="5"/>
+      <c r="H143" s="5"/>
+    </row>
+    <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
-    </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G144" s="5"/>
+      <c r="H144" s="5"/>
+    </row>
+    <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
-    </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G145" s="5"/>
+      <c r="H145" s="5"/>
+    </row>
+    <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
-    </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G146" s="5"/>
+      <c r="H146" s="5"/>
+    </row>
+    <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
-    </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G147" s="5"/>
+      <c r="H147" s="5"/>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
-    </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G148" s="5"/>
+      <c r="H148" s="5"/>
+    </row>
+    <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
-    </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G149" s="5"/>
+      <c r="H149" s="5"/>
+    </row>
+    <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
-    </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G150" s="5"/>
+      <c r="H150" s="5"/>
+    </row>
+    <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
-    </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G151" s="5"/>
+      <c r="H151" s="5"/>
+    </row>
+    <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
-    </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G152" s="5"/>
+      <c r="H152" s="5"/>
+    </row>
+    <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
-    </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G153" s="5"/>
+      <c r="H153" s="5"/>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
-    </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G154" s="5"/>
+      <c r="H154" s="5"/>
+    </row>
+    <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
-    </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G155" s="5"/>
+      <c r="H155" s="5"/>
+    </row>
+    <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
-    </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G156" s="5"/>
+      <c r="H156" s="5"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
-    </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G157" s="5"/>
+      <c r="H157" s="5"/>
+    </row>
+    <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
-    </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G158" s="5"/>
+      <c r="H158" s="5"/>
+    </row>
+    <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
-    </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G159" s="5"/>
+      <c r="H159" s="5"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
-    </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G160" s="5"/>
+      <c r="H160" s="5"/>
+    </row>
+    <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
-    </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G161" s="5"/>
+      <c r="H161" s="5"/>
+    </row>
+    <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
-    </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G162" s="5"/>
+      <c r="H162" s="5"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
-    </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G163" s="5"/>
+      <c r="H163" s="5"/>
+    </row>
+    <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
-    </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G164" s="5"/>
+      <c r="H164" s="5"/>
+    </row>
+    <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
-    </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G165" s="5"/>
+      <c r="H165" s="5"/>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
-    </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G166" s="5"/>
+      <c r="H166" s="5"/>
+    </row>
+    <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
-    </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G167" s="5"/>
+      <c r="H167" s="5"/>
+    </row>
+    <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
-    </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G168" s="5"/>
+      <c r="H168" s="5"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
-    </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G169" s="5"/>
+      <c r="H169" s="5"/>
+    </row>
+    <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
-    </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G170" s="5"/>
+      <c r="H170" s="5"/>
+    </row>
+    <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
-    </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G171" s="5"/>
+      <c r="H171" s="5"/>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
-    </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G172" s="5"/>
+      <c r="H172" s="5"/>
+    </row>
+    <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
-    </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G173" s="5"/>
+      <c r="H173" s="5"/>
+    </row>
+    <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
-    </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G174" s="5"/>
+      <c r="H174" s="5"/>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
-    </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G175" s="5"/>
+      <c r="H175" s="5"/>
+    </row>
+    <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
-    </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G176" s="5"/>
+      <c r="H176" s="5"/>
+    </row>
+    <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
-    </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G177" s="5"/>
+      <c r="H177" s="5"/>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
-    </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G178" s="5"/>
+      <c r="H178" s="5"/>
+    </row>
+    <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
-    </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G179" s="5"/>
+      <c r="H179" s="5"/>
+    </row>
+    <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
-    </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G180" s="5"/>
+      <c r="H180" s="5"/>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
-    </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G181" s="5"/>
+      <c r="H181" s="5"/>
+    </row>
+    <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
-    </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G182" s="5"/>
+      <c r="H182" s="5"/>
+    </row>
+    <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
-    </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G183" s="5"/>
+      <c r="H183" s="5"/>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
-    </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G184" s="5"/>
+      <c r="H184" s="5"/>
+    </row>
+    <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
-    </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G185" s="5"/>
+      <c r="H185" s="5"/>
+    </row>
+    <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
-    </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G186" s="5"/>
+      <c r="H186" s="5"/>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
-    </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G187" s="5"/>
+      <c r="H187" s="5"/>
+    </row>
+    <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
-    </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G188" s="5"/>
+      <c r="H188" s="5"/>
+    </row>
+    <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
-    </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G189" s="5"/>
+      <c r="H189" s="5"/>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
-    </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G190" s="5"/>
+      <c r="H190" s="5"/>
+    </row>
+    <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
-    </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G191" s="5"/>
+      <c r="H191" s="5"/>
+    </row>
+    <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
-    </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G192" s="5"/>
+      <c r="H192" s="5"/>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
-    </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G193" s="5"/>
+      <c r="H193" s="5"/>
+    </row>
+    <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
-    </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G194" s="5"/>
+      <c r="H194" s="5"/>
+    </row>
+    <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
-    </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G195" s="5"/>
+      <c r="H195" s="5"/>
+    </row>
+    <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
-    </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G196" s="5"/>
+      <c r="H196" s="5"/>
+    </row>
+    <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
-    </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G197" s="5"/>
+      <c r="H197" s="5"/>
+    </row>
+    <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
-    </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G198" s="5"/>
+      <c r="H198" s="5"/>
+    </row>
+    <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
-    </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G199" s="5"/>
+      <c r="H199" s="5"/>
+    </row>
+    <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
-    </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G200" s="5"/>
+      <c r="H200" s="5"/>
+    </row>
+    <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
-    </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G201" s="5"/>
+      <c r="H201" s="5"/>
+    </row>
+    <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
-    </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G202" s="5"/>
+      <c r="H202" s="5"/>
+    </row>
+    <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
-    </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G203" s="5"/>
+      <c r="H203" s="5"/>
+    </row>
+    <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
-    </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G204" s="5"/>
+      <c r="H204" s="5"/>
+    </row>
+    <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
-    </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G205" s="5"/>
+      <c r="H205" s="5"/>
+    </row>
+    <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
-    </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G206" s="5"/>
+      <c r="H206" s="5"/>
+    </row>
+    <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
-    </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G207" s="5"/>
+      <c r="H207" s="5"/>
+    </row>
+    <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
-    </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G208" s="5"/>
+      <c r="H208" s="5"/>
+    </row>
+    <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
-    </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G209" s="5"/>
+      <c r="H209" s="5"/>
+    </row>
+    <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
-    </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G210" s="5"/>
+      <c r="H210" s="5"/>
+    </row>
+    <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
-    </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G211" s="5"/>
+      <c r="H211" s="5"/>
+    </row>
+    <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
-    </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G212" s="5"/>
+      <c r="H212" s="5"/>
+    </row>
+    <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
-    </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G213" s="5"/>
+      <c r="H213" s="5"/>
+    </row>
+    <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
-    </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G214" s="5"/>
+      <c r="H214" s="5"/>
+    </row>
+    <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
-    </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G215" s="5"/>
+      <c r="H215" s="5"/>
+    </row>
+    <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
-    </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G216" s="5"/>
+      <c r="H216" s="5"/>
+    </row>
+    <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
-    </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G217" s="5"/>
+      <c r="H217" s="5"/>
+    </row>
+    <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
-    </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G218" s="5"/>
+      <c r="H218" s="5"/>
+    </row>
+    <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
-    </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G219" s="5"/>
+      <c r="H219" s="5"/>
+    </row>
+    <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
-    </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G220" s="5"/>
+      <c r="H220" s="5"/>
+    </row>
+    <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
-    </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G221" s="5"/>
+      <c r="H221" s="5"/>
+    </row>
+    <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
-    </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G222" s="5"/>
+      <c r="H222" s="5"/>
+    </row>
+    <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
-    </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G223" s="5"/>
+      <c r="H223" s="5"/>
+    </row>
+    <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
-    </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G224" s="5"/>
+      <c r="H224" s="5"/>
+    </row>
+    <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
-    </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G225" s="5"/>
+      <c r="H225" s="5"/>
+    </row>
+    <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
-    </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G226" s="5"/>
+      <c r="H226" s="5"/>
+    </row>
+    <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
-    </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G227" s="5"/>
+      <c r="H227" s="5"/>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
-    </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G228" s="5"/>
+      <c r="H228" s="5"/>
+    </row>
+    <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
-    </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G229" s="5"/>
+      <c r="H229" s="5"/>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
-    </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G230" s="5"/>
+      <c r="H230" s="5"/>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
-    </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G231" s="5"/>
+      <c r="H231" s="5"/>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
-    </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G232" s="5"/>
+      <c r="H232" s="5"/>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
-    </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G233" s="5"/>
+      <c r="H233" s="5"/>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
-    </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G234" s="5"/>
+      <c r="H234" s="5"/>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
-    </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G235" s="5"/>
+      <c r="H235" s="5"/>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
-    </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G236" s="5"/>
+      <c r="H236" s="5"/>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
-    </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G237" s="5"/>
+      <c r="H237" s="5"/>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
-    </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G238" s="5"/>
+      <c r="H238" s="5"/>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
-    </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G239" s="5"/>
+      <c r="H239" s="5"/>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
-    </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G240" s="5"/>
+      <c r="H240" s="5"/>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
-    </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G241" s="5"/>
+      <c r="H241" s="5"/>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
-    </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G242" s="5"/>
+      <c r="H242" s="5"/>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
-    </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G243" s="5"/>
+      <c r="H243" s="5"/>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
-    </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G244" s="5"/>
+      <c r="H244" s="5"/>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
-    </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G245" s="5"/>
+      <c r="H245" s="5"/>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
-    </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G246" s="5"/>
+      <c r="H246" s="5"/>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
-    </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G247" s="5"/>
+      <c r="H247" s="5"/>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
-    </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G248" s="5"/>
+      <c r="H248" s="5"/>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
-    </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G249" s="5"/>
+      <c r="H249" s="5"/>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
-    </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G250" s="5"/>
+      <c r="H250" s="5"/>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
-    </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G251" s="5"/>
+      <c r="H251" s="5"/>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
-    </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G252" s="5"/>
+      <c r="H252" s="5"/>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
-    </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G253" s="5"/>
+      <c r="H253" s="5"/>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
-    </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G254" s="5"/>
+      <c r="H254" s="5"/>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
-    </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G255" s="5"/>
+      <c r="H255" s="5"/>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
-    </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G256" s="5"/>
+      <c r="H256" s="5"/>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
-    </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G257" s="5"/>
+      <c r="H257" s="5"/>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
-    </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G258" s="5"/>
+      <c r="H258" s="5"/>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
-    </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G259" s="5"/>
+      <c r="H259" s="5"/>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
-    </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G260" s="5"/>
+      <c r="H260" s="5"/>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
-    </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G261" s="5"/>
+      <c r="H261" s="5"/>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
-    </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G262" s="5"/>
+      <c r="H262" s="5"/>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
-    </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G263" s="5"/>
+      <c r="H263" s="5"/>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
-    </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G264" s="5"/>
+      <c r="H264" s="5"/>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
-    </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G265" s="5"/>
+      <c r="H265" s="5"/>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
-    </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G266" s="5"/>
+      <c r="H266" s="5"/>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
-    </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G267" s="5"/>
+      <c r="H267" s="5"/>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
-    </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G268" s="5"/>
+      <c r="H268" s="5"/>
+    </row>
+    <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
-    </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G269" s="5"/>
+      <c r="H269" s="5"/>
+    </row>
+    <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
-    </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G270" s="5"/>
+      <c r="H270" s="5"/>
+    </row>
+    <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
-    </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G271" s="5"/>
+      <c r="H271" s="5"/>
+    </row>
+    <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
-    </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G272" s="5"/>
+      <c r="H272" s="5"/>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
-    </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G273" s="5"/>
+      <c r="H273" s="5"/>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
-    </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G274" s="5"/>
+      <c r="H274" s="5"/>
+    </row>
+    <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
-    </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G275" s="5"/>
+      <c r="H275" s="5"/>
+    </row>
+    <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
-    </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G276" s="5"/>
+      <c r="H276" s="5"/>
+    </row>
+    <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
-    </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G277" s="5"/>
+      <c r="H277" s="5"/>
+    </row>
+    <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
-    </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G278" s="5"/>
+      <c r="H278" s="5"/>
+    </row>
+    <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
-    </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G279" s="5"/>
+      <c r="H279" s="5"/>
+    </row>
+    <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
-    </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G280" s="5"/>
+      <c r="H280" s="5"/>
+    </row>
+    <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
-    </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G281" s="5"/>
+      <c r="H281" s="5"/>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
-    </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G282" s="5"/>
+      <c r="H282" s="5"/>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
-    </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G283" s="5"/>
+      <c r="H283" s="5"/>
+    </row>
+    <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
-    </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G284" s="5"/>
+      <c r="H284" s="5"/>
+    </row>
+    <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
-    </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G285" s="5"/>
+      <c r="H285" s="5"/>
+    </row>
+    <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
-    </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G286" s="5"/>
+      <c r="H286" s="5"/>
+    </row>
+    <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
-    </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G287" s="5"/>
+      <c r="H287" s="5"/>
+    </row>
+    <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
-    </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G288" s="5"/>
+      <c r="H288" s="5"/>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
-    </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G289" s="5"/>
+      <c r="H289" s="5"/>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
-    </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G290" s="5"/>
+      <c r="H290" s="5"/>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
-    </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="G291" s="5"/>
+      <c r="H291" s="5"/>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
+      <c r="G292" s="5"/>
+      <c r="H292" s="5"/>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A293" s="1"/>
+      <c r="B293" s="1"/>
+      <c r="G293" s="5"/>
+      <c r="H293" s="5"/>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A294" s="1"/>
+      <c r="B294" s="1"/>
+      <c r="G294" s="5"/>
+      <c r="H294" s="5"/>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A295" s="1"/>
+      <c r="B295" s="1"/>
+      <c r="G295" s="5"/>
+      <c r="H295" s="5"/>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A296" s="1"/>
+      <c r="B296" s="1"/>
+      <c r="G296" s="5"/>
+      <c r="H296" s="5"/>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A297" s="1"/>
+      <c r="B297" s="1"/>
+      <c r="G297" s="5"/>
+      <c r="H297" s="5"/>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A298" s="1"/>
+      <c r="B298" s="1"/>
+      <c r="G298" s="5"/>
+      <c r="H298" s="5"/>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A299" s="1"/>
+      <c r="B299" s="1"/>
+      <c r="G299" s="5"/>
+      <c r="H299" s="5"/>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A300" s="1"/>
+      <c r="B300" s="1"/>
+      <c r="G300" s="5"/>
+      <c r="H300" s="5"/>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A301" s="1"/>
+      <c r="B301" s="1"/>
+      <c r="G301" s="5"/>
+      <c r="H301" s="5"/>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A302" s="1"/>
+      <c r="B302" s="1"/>
+      <c r="G302" s="5"/>
+      <c r="H302" s="5"/>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A303" s="1"/>
+      <c r="B303" s="1"/>
+      <c r="G303" s="5"/>
+      <c r="H303" s="5"/>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A304" s="1"/>
+      <c r="B304" s="1"/>
+      <c r="G304" s="5"/>
+      <c r="H304" s="5"/>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A305" s="1"/>
+      <c r="B305" s="1"/>
+      <c r="G305" s="5"/>
+      <c r="H305" s="5"/>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A306" s="1"/>
+      <c r="B306" s="1"/>
+      <c r="G306" s="5"/>
+      <c r="H306" s="5"/>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A307" s="1"/>
+      <c r="B307" s="1"/>
+      <c r="G307" s="5"/>
+      <c r="H307" s="5"/>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A308" s="1"/>
+      <c r="B308" s="1"/>
+      <c r="G308" s="5"/>
+      <c r="H308" s="5"/>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A309" s="1"/>
+      <c r="B309" s="1"/>
+      <c r="G309" s="5"/>
+      <c r="H309" s="5"/>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A310" s="1"/>
+      <c r="B310" s="1"/>
+      <c r="G310" s="5"/>
+      <c r="H310" s="5"/>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A311" s="1"/>
+      <c r="B311" s="1"/>
+      <c r="G311" s="5"/>
+      <c r="H311" s="5"/>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A312" s="1"/>
+      <c r="B312" s="1"/>
+      <c r="G312" s="5"/>
+      <c r="H312" s="5"/>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A313" s="1"/>
+      <c r="B313" s="1"/>
+      <c r="G313" s="5"/>
+      <c r="H313" s="5"/>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A314" s="1"/>
+      <c r="B314" s="1"/>
+      <c r="G314" s="5"/>
+      <c r="H314" s="5"/>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A315" s="1"/>
+      <c r="B315" s="1"/>
+      <c r="G315" s="5"/>
+      <c r="H315" s="5"/>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A316" s="1"/>
+      <c r="B316" s="1"/>
+      <c r="G316" s="5"/>
+      <c r="H316" s="5"/>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A317" s="1"/>
+      <c r="B317" s="1"/>
+      <c r="G317" s="5"/>
+      <c r="H317" s="5"/>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A318" s="1"/>
+      <c r="B318" s="1"/>
+      <c r="G318" s="5"/>
+      <c r="H318" s="5"/>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A319" s="1"/>
+      <c r="B319" s="1"/>
+      <c r="G319" s="5"/>
+      <c r="H319" s="5"/>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A320" s="1"/>
+      <c r="B320" s="1"/>
+      <c r="G320" s="5"/>
+      <c r="H320" s="5"/>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A321" s="1"/>
+      <c r="B321" s="1"/>
+      <c r="G321" s="5"/>
+      <c r="H321" s="5"/>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A322" s="1"/>
+      <c r="B322" s="1"/>
+      <c r="G322" s="5"/>
+      <c r="H322" s="5"/>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A323" s="1"/>
+      <c r="B323" s="1"/>
+      <c r="G323" s="5"/>
+      <c r="H323" s="5"/>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A324" s="1"/>
+      <c r="B324" s="1"/>
+      <c r="G324" s="5"/>
+      <c r="H324" s="5"/>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A325" s="1"/>
+      <c r="B325" s="1"/>
+      <c r="G325" s="5"/>
+      <c r="H325" s="5"/>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A326" s="1"/>
+      <c r="B326" s="1"/>
+      <c r="G326" s="5"/>
+      <c r="H326" s="5"/>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A327" s="1"/>
+      <c r="B327" s="1"/>
+      <c r="G327" s="5"/>
+      <c r="H327" s="5"/>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A328" s="1"/>
+      <c r="B328" s="1"/>
+      <c r="G328" s="5"/>
+      <c r="H328" s="5"/>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A329" s="1"/>
+      <c r="B329" s="1"/>
+      <c r="G329" s="5"/>
+      <c r="H329" s="5"/>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A330" s="1"/>
+      <c r="B330" s="1"/>
+      <c r="G330" s="5"/>
+      <c r="H330" s="5"/>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A331" s="1"/>
+      <c r="B331" s="1"/>
+      <c r="G331" s="5"/>
+      <c r="H331" s="5"/>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A332" s="1"/>
+      <c r="B332" s="1"/>
+      <c r="G332" s="5"/>
+      <c r="H332" s="5"/>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A333" s="1"/>
+      <c r="B333" s="1"/>
+      <c r="G333" s="5"/>
+      <c r="H333" s="5"/>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A334" s="1"/>
+      <c r="B334" s="1"/>
+      <c r="G334" s="5"/>
+      <c r="H334" s="5"/>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A335" s="1"/>
+      <c r="B335" s="1"/>
+      <c r="G335" s="5"/>
+      <c r="H335" s="5"/>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A336" s="1"/>
+      <c r="B336" s="1"/>
+      <c r="G336" s="5"/>
+      <c r="H336" s="5"/>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A337" s="1"/>
+      <c r="B337" s="1"/>
+      <c r="G337" s="5"/>
+      <c r="H337" s="5"/>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A338" s="1"/>
+      <c r="B338" s="1"/>
+      <c r="G338" s="5"/>
+      <c r="H338" s="5"/>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A339" s="1"/>
+      <c r="B339" s="1"/>
+      <c r="G339" s="5"/>
+      <c r="H339" s="5"/>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A340" s="1"/>
+      <c r="B340" s="1"/>
+      <c r="G340" s="5"/>
+      <c r="H340" s="5"/>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A341" s="1"/>
+      <c r="B341" s="1"/>
+      <c r="G341" s="5"/>
+      <c r="H341" s="5"/>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A342" s="1"/>
+      <c r="B342" s="1"/>
+      <c r="G342" s="5"/>
+      <c r="H342" s="5"/>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A343" s="1"/>
+      <c r="B343" s="1"/>
+      <c r="G343" s="5"/>
+      <c r="H343" s="5"/>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A344" s="1"/>
+      <c r="B344" s="1"/>
+      <c r="G344" s="5"/>
+      <c r="H344" s="5"/>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A345" s="1"/>
+      <c r="B345" s="1"/>
+      <c r="G345" s="5"/>
+      <c r="H345" s="5"/>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A346" s="1"/>
+      <c r="B346" s="1"/>
+      <c r="G346" s="5"/>
+      <c r="H346" s="5"/>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A347" s="1"/>
+      <c r="B347" s="1"/>
+      <c r="G347" s="5"/>
+      <c r="H347" s="5"/>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A348" s="1"/>
+      <c r="B348" s="1"/>
+      <c r="G348" s="5"/>
+      <c r="H348" s="5"/>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A349" s="1"/>
+      <c r="B349" s="1"/>
+      <c r="G349" s="5"/>
+      <c r="H349" s="5"/>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A350" s="1"/>
+      <c r="B350" s="1"/>
+      <c r="G350" s="5"/>
+      <c r="H350" s="5"/>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A351" s="1"/>
+      <c r="B351" s="1"/>
+      <c r="G351" s="5"/>
+      <c r="H351" s="5"/>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A352" s="1"/>
+      <c r="B352" s="1"/>
+      <c r="G352" s="5"/>
+      <c r="H352" s="5"/>
+    </row>
+    <row r="353" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A353" s="1"/>
+      <c r="B353" s="1"/>
+      <c r="G353" s="5"/>
+      <c r="H353" s="5"/>
+    </row>
+    <row r="354" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A354" s="1"/>
+      <c r="B354" s="1"/>
+      <c r="G354" s="5"/>
+      <c r="H354" s="5"/>
+    </row>
+    <row r="355" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A355" s="1"/>
+      <c r="B355" s="1"/>
+      <c r="G355" s="5"/>
+      <c r="H355" s="5"/>
+    </row>
+    <row r="356" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A356" s="1"/>
+      <c r="B356" s="1"/>
+      <c r="G356" s="5"/>
+      <c r="H356" s="5"/>
+    </row>
+    <row r="357" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A357" s="1"/>
+      <c r="B357" s="1"/>
+      <c r="G357" s="5"/>
+      <c r="H357" s="5"/>
+    </row>
+    <row r="358" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A358" s="1"/>
+      <c r="B358" s="1"/>
+      <c r="G358" s="5"/>
+      <c r="H358" s="5"/>
+    </row>
+    <row r="359" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A359" s="1"/>
+      <c r="B359" s="1"/>
+      <c r="G359" s="5"/>
+      <c r="H359" s="5"/>
+    </row>
+    <row r="360" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A360" s="1"/>
+      <c r="B360" s="1"/>
+      <c r="G360" s="5"/>
+      <c r="H360" s="5"/>
+    </row>
+    <row r="361" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A361" s="1"/>
+      <c r="B361" s="1"/>
+      <c r="G361" s="5"/>
+      <c r="H361" s="5"/>
+    </row>
+    <row r="362" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A362" s="1"/>
+      <c r="B362" s="1"/>
+      <c r="G362" s="5"/>
+      <c r="H362" s="5"/>
+    </row>
+    <row r="363" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A363" s="1"/>
+      <c r="B363" s="1"/>
+      <c r="G363" s="5"/>
+      <c r="H363" s="5"/>
+    </row>
+    <row r="364" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A364" s="1"/>
+      <c r="B364" s="1"/>
+      <c r="G364" s="5"/>
+      <c r="H364" s="5"/>
+    </row>
+    <row r="365" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A365" s="1"/>
+      <c r="B365" s="1"/>
+      <c r="G365" s="5"/>
+      <c r="H365" s="5"/>
+    </row>
+    <row r="366" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A366" s="1"/>
+      <c r="B366" s="1"/>
+      <c r="G366" s="5"/>
+      <c r="H366" s="5"/>
+    </row>
+    <row r="367" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A367" s="1"/>
+      <c r="B367" s="1"/>
+      <c r="G367" s="5"/>
+      <c r="H367" s="5"/>
+    </row>
+    <row r="368" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A368" s="1"/>
+      <c r="B368" s="1"/>
+      <c r="G368" s="5"/>
+      <c r="H368" s="5"/>
+    </row>
+    <row r="369" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A369" s="1"/>
+      <c r="B369" s="1"/>
+      <c r="G369" s="5"/>
+      <c r="H369" s="5"/>
+    </row>
+    <row r="370" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A370" s="1"/>
+      <c r="B370" s="1"/>
+      <c r="G370" s="5"/>
+      <c r="H370" s="5"/>
+    </row>
+    <row r="371" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A371" s="1"/>
+      <c r="B371" s="1"/>
+      <c r="G371" s="5"/>
+      <c r="H371" s="5"/>
+    </row>
+    <row r="372" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A372" s="1"/>
+      <c r="B372" s="1"/>
+      <c r="G372" s="5"/>
+      <c r="H372" s="5"/>
+    </row>
+    <row r="373" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A373" s="1"/>
+      <c r="B373" s="1"/>
+      <c r="G373" s="5"/>
+      <c r="H373" s="5"/>
+    </row>
+    <row r="374" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A374" s="1"/>
+      <c r="B374" s="1"/>
+      <c r="G374" s="5"/>
+      <c r="H374" s="5"/>
+    </row>
+    <row r="375" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A375" s="1"/>
+      <c r="B375" s="1"/>
+      <c r="G375" s="5"/>
+      <c r="H375" s="5"/>
+    </row>
+    <row r="376" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A376" s="1"/>
+      <c r="B376" s="1"/>
+      <c r="G376" s="5"/>
+      <c r="H376" s="5"/>
+    </row>
+    <row r="377" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A377" s="1"/>
+      <c r="B377" s="1"/>
+      <c r="G377" s="5"/>
+      <c r="H377" s="5"/>
+    </row>
+    <row r="378" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A378" s="1"/>
+      <c r="B378" s="1"/>
+      <c r="G378" s="5"/>
+      <c r="H378" s="5"/>
+    </row>
+    <row r="379" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A379" s="1"/>
+      <c r="B379" s="1"/>
+      <c r="G379" s="5"/>
+      <c r="H379" s="5"/>
+    </row>
+    <row r="380" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A380" s="1"/>
+      <c r="B380" s="1"/>
+      <c r="G380" s="5"/>
+      <c r="H380" s="5"/>
+    </row>
+    <row r="381" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A381" s="1"/>
+      <c r="B381" s="1"/>
+      <c r="G381" s="5"/>
+      <c r="H381" s="5"/>
+    </row>
+    <row r="382" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A382" s="1"/>
+      <c r="B382" s="1"/>
+      <c r="G382" s="5"/>
+      <c r="H382" s="5"/>
+    </row>
+    <row r="383" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A383" s="1"/>
+      <c r="B383" s="1"/>
+      <c r="G383" s="5"/>
+      <c r="H383" s="5"/>
+    </row>
+    <row r="384" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A384" s="1"/>
+      <c r="B384" s="1"/>
+      <c r="G384" s="5"/>
+      <c r="H384" s="5"/>
+    </row>
+    <row r="385" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A385" s="1"/>
+      <c r="B385" s="1"/>
+      <c r="G385" s="5"/>
+      <c r="H385" s="5"/>
+    </row>
+    <row r="386" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A386" s="1"/>
+      <c r="B386" s="1"/>
+      <c r="G386" s="5"/>
+      <c r="H386" s="5"/>
+    </row>
+    <row r="387" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A387" s="1"/>
+      <c r="B387" s="1"/>
+      <c r="G387" s="5"/>
+      <c r="H387" s="5"/>
+    </row>
+    <row r="388" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A388" s="1"/>
+      <c r="B388" s="1"/>
+      <c r="G388" s="5"/>
+      <c r="H388" s="5"/>
+    </row>
+    <row r="389" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A389" s="1"/>
+      <c r="B389" s="1"/>
+      <c r="G389" s="5"/>
+      <c r="H389" s="5"/>
+    </row>
+    <row r="390" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A390" s="1"/>
+      <c r="B390" s="1"/>
+      <c r="G390" s="5"/>
+      <c r="H390" s="5"/>
+    </row>
+    <row r="391" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A391" s="1"/>
+      <c r="B391" s="1"/>
+      <c r="G391" s="5"/>
+      <c r="H391" s="5"/>
+    </row>
+    <row r="392" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A392" s="1"/>
+      <c r="B392" s="1"/>
+      <c r="G392" s="5"/>
+      <c r="H392" s="5"/>
+    </row>
+    <row r="393" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A393" s="1"/>
+      <c r="B393" s="1"/>
+      <c r="G393" s="5"/>
+      <c r="H393" s="5"/>
+    </row>
+    <row r="394" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A394" s="1"/>
+      <c r="B394" s="1"/>
+      <c r="G394" s="5"/>
+      <c r="H394" s="5"/>
+    </row>
+    <row r="395" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A395" s="1"/>
+      <c r="B395" s="1"/>
+      <c r="G395" s="5"/>
+      <c r="H395" s="5"/>
+    </row>
+    <row r="396" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A396" s="1"/>
+      <c r="B396" s="1"/>
+      <c r="G396" s="5"/>
+      <c r="H396" s="5"/>
+    </row>
+    <row r="397" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A397" s="1"/>
+      <c r="B397" s="1"/>
+      <c r="G397" s="5"/>
+      <c r="H397" s="5"/>
+    </row>
+    <row r="398" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A398" s="1"/>
+      <c r="B398" s="1"/>
+      <c r="G398" s="5"/>
+      <c r="H398" s="5"/>
+    </row>
+    <row r="399" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A399" s="1"/>
+      <c r="B399" s="1"/>
+      <c r="G399" s="5"/>
+      <c r="H399" s="5"/>
+    </row>
+    <row r="400" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A400" s="1"/>
+      <c r="B400" s="1"/>
+      <c r="G400" s="5"/>
+      <c r="H400" s="5"/>
+    </row>
+    <row r="401" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A401" s="1"/>
+      <c r="B401" s="1"/>
+      <c r="G401" s="5"/>
+      <c r="H401" s="5"/>
+    </row>
+    <row r="402" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A402" s="1"/>
+      <c r="B402" s="1"/>
+      <c r="G402" s="5"/>
+      <c r="H402" s="5"/>
+    </row>
+    <row r="403" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A403" s="1"/>
+      <c r="B403" s="1"/>
+      <c r="G403" s="5"/>
+      <c r="H403" s="5"/>
+    </row>
+    <row r="404" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A404" s="1"/>
+      <c r="B404" s="1"/>
+      <c r="G404" s="5"/>
+      <c r="H404" s="5"/>
+    </row>
+    <row r="405" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A405" s="1"/>
+      <c r="B405" s="1"/>
+      <c r="G405" s="5"/>
+      <c r="H405" s="5"/>
+    </row>
+    <row r="406" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A406" s="1"/>
+      <c r="B406" s="1"/>
+      <c r="G406" s="5"/>
+      <c r="H406" s="5"/>
+    </row>
+    <row r="407" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A407" s="1"/>
+      <c r="B407" s="1"/>
+      <c r="G407" s="5"/>
+      <c r="H407" s="5"/>
+    </row>
+    <row r="408" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A408" s="1"/>
+      <c r="B408" s="1"/>
+      <c r="G408" s="5"/>
+      <c r="H408" s="5"/>
+    </row>
+    <row r="409" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A409" s="1"/>
+      <c r="B409" s="1"/>
+      <c r="G409" s="5"/>
+      <c r="H409" s="5"/>
+    </row>
+    <row r="410" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A410" s="1"/>
+      <c r="B410" s="1"/>
+      <c r="G410" s="5"/>
+      <c r="H410" s="5"/>
+    </row>
+    <row r="411" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A411" s="1"/>
+      <c r="B411" s="1"/>
+      <c r="G411" s="5"/>
+      <c r="H411" s="5"/>
+    </row>
+    <row r="412" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A412" s="1"/>
+      <c r="B412" s="1"/>
+      <c r="G412" s="5"/>
+      <c r="H412" s="5"/>
+    </row>
+    <row r="413" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A413" s="1"/>
+      <c r="B413" s="1"/>
+      <c r="G413" s="5"/>
+      <c r="H413" s="5"/>
+    </row>
+    <row r="414" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A414" s="1"/>
+      <c r="B414" s="1"/>
+      <c r="G414" s="5"/>
+      <c r="H414" s="5"/>
+    </row>
+    <row r="415" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A415" s="1"/>
+      <c r="B415" s="1"/>
+      <c r="G415" s="5"/>
+      <c r="H415" s="5"/>
+    </row>
+    <row r="416" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A416" s="1"/>
+      <c r="B416" s="1"/>
+      <c r="G416" s="5"/>
+      <c r="H416" s="5"/>
+    </row>
+    <row r="417" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A417" s="1"/>
+      <c r="B417" s="1"/>
+      <c r="G417" s="5"/>
+      <c r="H417" s="5"/>
+    </row>
+    <row r="418" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A418" s="1"/>
+      <c r="B418" s="1"/>
+      <c r="G418" s="5"/>
+      <c r="H418" s="5"/>
+    </row>
+    <row r="419" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A419" s="1"/>
+      <c r="B419" s="1"/>
+      <c r="G419" s="5"/>
+      <c r="H419" s="5"/>
+    </row>
+    <row r="420" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A420" s="1"/>
+      <c r="B420" s="1"/>
+      <c r="G420" s="5"/>
+      <c r="H420" s="5"/>
+    </row>
+    <row r="421" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A421" s="1"/>
+      <c r="B421" s="1"/>
+      <c r="G421" s="5"/>
+      <c r="H421" s="5"/>
+    </row>
+    <row r="422" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A422" s="1"/>
+      <c r="B422" s="1"/>
+      <c r="G422" s="5"/>
+      <c r="H422" s="5"/>
+    </row>
+    <row r="423" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A423" s="1"/>
+      <c r="B423" s="1"/>
+      <c r="G423" s="5"/>
+      <c r="H423" s="5"/>
+    </row>
+    <row r="424" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A424" s="1"/>
+      <c r="B424" s="1"/>
+      <c r="G424" s="5"/>
+      <c r="H424" s="5"/>
+    </row>
+    <row r="425" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A425" s="1"/>
+      <c r="B425" s="1"/>
+      <c r="G425" s="5"/>
+      <c r="H425" s="5"/>
+    </row>
+    <row r="426" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A426" s="1"/>
+      <c r="B426" s="1"/>
+      <c r="G426" s="5"/>
+      <c r="H426" s="5"/>
+    </row>
+    <row r="427" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A427" s="1"/>
+      <c r="B427" s="1"/>
+      <c r="G427" s="5"/>
+      <c r="H427" s="5"/>
+    </row>
+    <row r="428" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A428" s="1"/>
+      <c r="B428" s="1"/>
+      <c r="G428" s="5"/>
+      <c r="H428" s="5"/>
+    </row>
+    <row r="429" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A429" s="1"/>
+      <c r="B429" s="1"/>
+      <c r="G429" s="5"/>
+      <c r="H429" s="5"/>
+    </row>
+    <row r="430" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A430" s="1"/>
+      <c r="B430" s="1"/>
+      <c r="G430" s="5"/>
+      <c r="H430" s="5"/>
+    </row>
+    <row r="431" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A431" s="1"/>
+      <c r="B431" s="1"/>
+      <c r="G431" s="5"/>
+      <c r="H431" s="5"/>
+    </row>
+    <row r="432" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A432" s="1"/>
+      <c r="B432" s="1"/>
+      <c r="G432" s="5"/>
+      <c r="H432" s="5"/>
+    </row>
+    <row r="433" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A433" s="1"/>
+      <c r="B433" s="1"/>
+      <c r="G433" s="5"/>
+      <c r="H433" s="5"/>
+    </row>
+    <row r="434" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A434" s="1"/>
+      <c r="B434" s="1"/>
+      <c r="G434" s="5"/>
+      <c r="H434" s="5"/>
+    </row>
+    <row r="435" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A435" s="1"/>
+      <c r="B435" s="1"/>
+      <c r="G435" s="5"/>
+      <c r="H435" s="5"/>
+    </row>
+    <row r="436" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A436" s="1"/>
+      <c r="B436" s="1"/>
+      <c r="G436" s="5"/>
+      <c r="H436" s="5"/>
+    </row>
+    <row r="437" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A437" s="1"/>
+      <c r="B437" s="1"/>
+      <c r="G437" s="5"/>
+      <c r="H437" s="5"/>
+    </row>
+    <row r="438" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A438" s="1"/>
+      <c r="B438" s="1"/>
+      <c r="G438" s="5"/>
+      <c r="H438" s="5"/>
+    </row>
+    <row r="439" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A439" s="1"/>
+      <c r="B439" s="1"/>
+      <c r="G439" s="5"/>
+      <c r="H439" s="5"/>
+    </row>
+    <row r="440" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A440" s="1"/>
+      <c r="B440" s="1"/>
+      <c r="G440" s="5"/>
+      <c r="H440" s="5"/>
+    </row>
+    <row r="441" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A441" s="1"/>
+      <c r="B441" s="1"/>
+      <c r="G441" s="5"/>
+      <c r="H441" s="5"/>
+    </row>
+    <row r="442" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A442" s="1"/>
+      <c r="B442" s="1"/>
+      <c r="G442" s="5"/>
+      <c r="H442" s="5"/>
+    </row>
+    <row r="443" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A443" s="1"/>
+      <c r="B443" s="1"/>
+      <c r="G443" s="5"/>
+      <c r="H443" s="5"/>
+    </row>
+    <row r="444" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A444" s="1"/>
+      <c r="B444" s="1"/>
+      <c r="G444" s="5"/>
+      <c r="H444" s="5"/>
+    </row>
+    <row r="445" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A445" s="1"/>
+      <c r="B445" s="1"/>
+      <c r="G445" s="5"/>
+      <c r="H445" s="5"/>
+    </row>
+    <row r="446" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A446" s="1"/>
+      <c r="B446" s="1"/>
+      <c r="G446" s="5"/>
+      <c r="H446" s="5"/>
+    </row>
+    <row r="447" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A447" s="1"/>
+      <c r="B447" s="1"/>
+      <c r="G447" s="5"/>
+      <c r="H447" s="5"/>
+    </row>
+    <row r="448" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A448" s="1"/>
+      <c r="B448" s="1"/>
+      <c r="G448" s="5"/>
+      <c r="H448" s="5"/>
+    </row>
+    <row r="449" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A449" s="1"/>
+      <c r="B449" s="1"/>
+      <c r="G449" s="5"/>
+      <c r="H449" s="5"/>
+    </row>
+    <row r="450" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A450" s="1"/>
+      <c r="B450" s="1"/>
+      <c r="G450" s="5"/>
+      <c r="H450" s="5"/>
+    </row>
+    <row r="451" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A451" s="1"/>
+      <c r="B451" s="1"/>
+      <c r="G451" s="5"/>
+      <c r="H451" s="5"/>
+    </row>
+    <row r="452" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A452" s="1"/>
+      <c r="B452" s="1"/>
+      <c r="G452" s="5"/>
+      <c r="H452" s="5"/>
+    </row>
+    <row r="453" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A453" s="1"/>
+      <c r="B453" s="1"/>
+      <c r="G453" s="5"/>
+      <c r="H453" s="5"/>
+    </row>
+    <row r="454" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A454" s="1"/>
+      <c r="B454" s="1"/>
+      <c r="G454" s="5"/>
+      <c r="H454" s="5"/>
+    </row>
+    <row r="455" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A455" s="1"/>
+      <c r="B455" s="1"/>
+      <c r="G455" s="5"/>
+      <c r="H455" s="5"/>
+    </row>
+    <row r="456" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A456" s="1"/>
+      <c r="B456" s="1"/>
+      <c r="G456" s="5"/>
+      <c r="H456" s="5"/>
+    </row>
+    <row r="457" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A457" s="1"/>
+      <c r="B457" s="1"/>
+      <c r="G457" s="5"/>
+      <c r="H457" s="5"/>
+    </row>
+    <row r="458" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A458" s="1"/>
+      <c r="B458" s="1"/>
+      <c r="G458" s="5"/>
+      <c r="H458" s="5"/>
+    </row>
+    <row r="459" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A459" s="1"/>
+      <c r="B459" s="1"/>
+      <c r="G459" s="5"/>
+      <c r="H459" s="5"/>
+    </row>
+    <row r="460" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A460" s="1"/>
+      <c r="B460" s="1"/>
+      <c r="G460" s="5"/>
+      <c r="H460" s="5"/>
+    </row>
+    <row r="461" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A461" s="1"/>
+      <c r="B461" s="1"/>
+      <c r="G461" s="5"/>
+      <c r="H461" s="5"/>
+    </row>
+    <row r="462" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A462" s="1"/>
+      <c r="B462" s="1"/>
+      <c r="G462" s="5"/>
+      <c r="H462" s="5"/>
+    </row>
+    <row r="463" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A463" s="1"/>
+      <c r="B463" s="1"/>
+      <c r="G463" s="5"/>
+      <c r="H463" s="5"/>
+    </row>
+    <row r="464" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A464" s="1"/>
+      <c r="B464" s="1"/>
+      <c r="G464" s="5"/>
+      <c r="H464" s="5"/>
+    </row>
+    <row r="465" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A465" s="1"/>
+      <c r="B465" s="1"/>
+      <c r="G465" s="5"/>
+      <c r="H465" s="5"/>
+    </row>
+    <row r="466" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A466" s="1"/>
+      <c r="B466" s="1"/>
+      <c r="G466" s="5"/>
+      <c r="H466" s="5"/>
+    </row>
+    <row r="467" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A467" s="1"/>
+      <c r="B467" s="1"/>
+      <c r="G467" s="5"/>
+      <c r="H467" s="5"/>
+    </row>
+    <row r="468" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A468" s="1"/>
+      <c r="B468" s="1"/>
+      <c r="G468" s="5"/>
+      <c r="H468" s="5"/>
+    </row>
+    <row r="469" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A469" s="1"/>
+      <c r="B469" s="1"/>
+      <c r="G469" s="5"/>
+      <c r="H469" s="5"/>
+    </row>
+    <row r="470" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A470" s="1"/>
+      <c r="B470" s="1"/>
+      <c r="G470" s="5"/>
+      <c r="H470" s="5"/>
+    </row>
+    <row r="471" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A471" s="1"/>
+      <c r="B471" s="1"/>
+      <c r="G471" s="5"/>
+      <c r="H471" s="5"/>
+    </row>
+    <row r="472" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A472" s="1"/>
+      <c r="B472" s="1"/>
+      <c r="G472" s="5"/>
+      <c r="H472" s="5"/>
+    </row>
+    <row r="473" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A473" s="1"/>
+      <c r="B473" s="1"/>
+      <c r="G473" s="5"/>
+      <c r="H473" s="5"/>
+    </row>
+    <row r="474" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A474" s="1"/>
+      <c r="B474" s="1"/>
+      <c r="G474" s="5"/>
+      <c r="H474" s="5"/>
+    </row>
+    <row r="475" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A475" s="1"/>
+      <c r="B475" s="1"/>
+      <c r="G475" s="5"/>
+      <c r="H475" s="5"/>
+    </row>
+    <row r="476" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A476" s="1"/>
+      <c r="B476" s="1"/>
+      <c r="G476" s="5"/>
+      <c r="H476" s="5"/>
+    </row>
+    <row r="477" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A477" s="1"/>
+      <c r="B477" s="1"/>
+      <c r="G477" s="5"/>
+      <c r="H477" s="5"/>
+    </row>
+    <row r="478" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A478" s="1"/>
+      <c r="B478" s="1"/>
+      <c r="G478" s="5"/>
+      <c r="H478" s="5"/>
+    </row>
+    <row r="479" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A479" s="1"/>
+      <c r="B479" s="1"/>
+      <c r="G479" s="5"/>
+      <c r="H479" s="5"/>
+    </row>
+    <row r="480" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A480" s="1"/>
+      <c r="B480" s="1"/>
+      <c r="G480" s="5"/>
+      <c r="H480" s="5"/>
+    </row>
+    <row r="481" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A481" s="1"/>
+      <c r="B481" s="1"/>
+      <c r="G481" s="5"/>
+      <c r="H481" s="5"/>
+    </row>
+    <row r="482" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A482" s="1"/>
+      <c r="B482" s="1"/>
+      <c r="G482" s="5"/>
+      <c r="H482" s="5"/>
+    </row>
+    <row r="483" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A483" s="1"/>
+      <c r="B483" s="1"/>
+      <c r="G483" s="5"/>
+      <c r="H483" s="5"/>
+    </row>
+    <row r="484" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A484" s="1"/>
+      <c r="B484" s="1"/>
+      <c r="G484" s="5"/>
+      <c r="H484" s="5"/>
+    </row>
+    <row r="485" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A485" s="1"/>
+      <c r="B485" s="1"/>
+      <c r="G485" s="5"/>
+      <c r="H485" s="5"/>
+    </row>
+    <row r="486" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A486" s="1"/>
+      <c r="B486" s="1"/>
+      <c r="G486" s="5"/>
+      <c r="H486" s="5"/>
+    </row>
+    <row r="487" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A487" s="1"/>
+      <c r="B487" s="1"/>
+      <c r="G487" s="5"/>
+      <c r="H487" s="5"/>
+    </row>
+    <row r="488" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A488" s="1"/>
+      <c r="B488" s="1"/>
+      <c r="G488" s="5"/>
+      <c r="H488" s="5"/>
+    </row>
+    <row r="489" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A489" s="1"/>
+      <c r="B489" s="1"/>
+      <c r="G489" s="5"/>
+      <c r="H489" s="5"/>
+    </row>
+    <row r="490" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A490" s="1"/>
+      <c r="B490" s="1"/>
+      <c r="G490" s="5"/>
+      <c r="H490" s="5"/>
+    </row>
+    <row r="491" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A491" s="1"/>
+      <c r="B491" s="1"/>
+      <c r="G491" s="5"/>
+      <c r="H491" s="5"/>
+    </row>
+    <row r="492" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A492" s="1"/>
+      <c r="B492" s="1"/>
+      <c r="G492" s="5"/>
+      <c r="H492" s="5"/>
+    </row>
+    <row r="493" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A493" s="1"/>
+      <c r="B493" s="1"/>
+      <c r="G493" s="5"/>
+      <c r="H493" s="5"/>
+    </row>
+    <row r="494" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A494" s="1"/>
+      <c r="B494" s="1"/>
+      <c r="G494" s="5"/>
+      <c r="H494" s="5"/>
+    </row>
+    <row r="495" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A495" s="1"/>
+      <c r="B495" s="1"/>
+      <c r="G495" s="5"/>
+      <c r="H495" s="5"/>
+    </row>
+    <row r="496" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A496" s="1"/>
+      <c r="B496" s="1"/>
+      <c r="G496" s="5"/>
+      <c r="H496" s="5"/>
+    </row>
+    <row r="497" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A497" s="1"/>
+      <c r="B497" s="1"/>
+      <c r="G497" s="5"/>
+      <c r="H497" s="5"/>
+    </row>
+    <row r="498" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A498" s="1"/>
+      <c r="B498" s="1"/>
+      <c r="G498" s="5"/>
+      <c r="H498" s="5"/>
+    </row>
+    <row r="499" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A499" s="1"/>
+      <c r="B499" s="1"/>
+      <c r="G499" s="5"/>
+      <c r="H499" s="5"/>
+    </row>
+    <row r="500" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A500" s="1"/>
+      <c r="B500" s="1"/>
+      <c r="G500" s="5"/>
+      <c r="H500" s="5"/>
+    </row>
+    <row r="501" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A501" s="1"/>
+      <c r="B501" s="1"/>
+      <c r="G501" s="5"/>
+      <c r="H501" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1883,7 +3693,7 @@
       <c r="B2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
     </row>
@@ -1901,13 +3711,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A1" s="7" t="s">
-        <v>25</v>
+      <c r="A1" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
-      <c r="A4" s="8" t="s">
-        <v>24</v>
+      <c r="A4" s="4" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AE1BA31-445C-004A-8FBE-40D857627FD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23563E9E-4AD0-EA46-9269-A44F74A6BF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-38400" yWindow="-3000" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
@@ -119,7 +119,7 @@
     <t>81ASN0122QA3510</t>
   </si>
   <si>
-    <t>HJ1183</t>
+    <t>SX4492-901-S</t>
   </si>
 </sst>
 </file>
@@ -644,12 +644,12 @@
         <v>6</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="5" t="s">
-        <v>26</v>
-      </c>
+      <c r="G2" s="5"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23563E9E-4AD0-EA46-9269-A44F74A6BF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FC8A2A-5E01-7C45-8007-DC7C8EE44E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-3000" windowWidth="38400" windowHeight="21000" activeTab="1" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="-38400" yWindow="-3000" windowWidth="38400" windowHeight="21000" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
@@ -110,16 +110,16 @@
     <t>;20260114000000000001;20260114000000000002</t>
   </si>
   <si>
-    <t>20260114000000000001;20260114000000000002</t>
+    <t>SX4492-901-S</t>
   </si>
   <si>
-    <t>DD9293-100-7</t>
+    <t>136064-140-10</t>
   </si>
   <si>
-    <t>81ASN0122QA3510</t>
+    <t>Today</t>
   </si>
   <si>
-    <t>SX4492-901-S</t>
+    <t>0215055848</t>
   </si>
 </sst>
 </file>
@@ -571,11 +571,9 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
-      <c r="E2" s="3" t="s">
-        <v>23</v>
-      </c>
+      <c r="E2" s="3"/>
       <c r="G2" t="s">
         <v>24</v>
       </c>
@@ -585,8 +583,8 @@
       <c r="J2" t="s">
         <v>19</v>
       </c>
-      <c r="K2">
-        <v>7</v>
+      <c r="K2" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -645,7 +643,7 @@
       </c>
       <c r="C2" s="1"/>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09FC8A2A-5E01-7C45-8007-DC7C8EE44E8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62CBCF8-97A5-824E-9AF6-013DB5F12A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38400" yWindow="-3000" windowWidth="38400" windowHeight="21000" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="-37040" yWindow="-3000" windowWidth="36000" windowHeight="21000" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
   <si>
     <t>ASN_FLAG</t>
   </si>
@@ -110,16 +110,13 @@
     <t>;20260114000000000001;20260114000000000002</t>
   </si>
   <si>
-    <t>SX4492-901-S</t>
-  </si>
-  <si>
     <t>136064-140-10</t>
   </si>
   <si>
     <t>Today</t>
   </si>
   <si>
-    <t>0215055848</t>
+    <t>0215056185;0215056175</t>
   </si>
 </sst>
 </file>
@@ -571,11 +568,11 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3"/>
       <c r="G2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
         <v>20</v>
@@ -584,7 +581,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -642,12 +639,11 @@
         <v>6</v>
       </c>
       <c r="C2" s="1"/>
-      <c r="D2" t="s">
-        <v>23</v>
-      </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
-      <c r="G2" s="5"/>
+      <c r="G2" s="5">
+        <v>203690</v>
+      </c>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A62CBCF8-97A5-824E-9AF6-013DB5F12A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344F5748-6BD5-0647-A16F-ED5580D5AAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-37040" yWindow="-3000" windowWidth="36000" windowHeight="21000" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
@@ -116,7 +116,7 @@
     <t>Today</t>
   </si>
   <si>
-    <t>0215056185;0215056175</t>
+    <t>0215056059</t>
   </si>
 </sst>
 </file>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{344F5748-6BD5-0647-A16F-ED5580D5AAE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1A2511-01CE-A94B-B998-1A6032BA3890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37040" yWindow="-3000" windowWidth="36000" windowHeight="21000" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
   <si>
     <t>ASN_FLAG</t>
   </si>
@@ -116,7 +116,10 @@
     <t>Today</t>
   </si>
   <si>
-    <t>0215056059</t>
+    <t>Equipment</t>
+  </si>
+  <si>
+    <t>0215056616</t>
   </si>
 </sst>
 </file>
@@ -164,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -176,6 +179,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -568,7 +576,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3"/>
       <c r="G2" t="s">
@@ -602,7 +610,7 @@
     <col min="5" max="5" width="21.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.83203125" style="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.2">
@@ -627,7 +635,7 @@
       <c r="G1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="8" t="s">
         <v>14</v>
       </c>
     </row>
@@ -638,12 +646,14 @@
       <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="1"/>
-      <c r="E2" s="1"/>
+      <c r="C2" s="1">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>25</v>
+      </c>
       <c r="F2" s="1"/>
-      <c r="G2" s="5">
-        <v>203690</v>
-      </c>
+      <c r="G2" s="7"/>
       <c r="H2" s="6"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
@@ -653,8 +663,8 @@
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="6"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
@@ -664,2997 +674,2997 @@
       <c r="E4" s="1"/>
       <c r="F4" s="1"/>
       <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
+      <c r="H4" s="6"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="D5" s="1"/>
       <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="H5" s="6"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="1"/>
       <c r="D6" s="1"/>
       <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
+      <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="D7" s="1"/>
       <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="H7" s="6"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="D8" s="2"/>
       <c r="G8" s="5"/>
-      <c r="H8" s="5"/>
+      <c r="H8" s="6"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="1"/>
       <c r="D9" s="2"/>
       <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="H9" s="6"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="D10" s="2"/>
       <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
+      <c r="H10" s="6"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="1"/>
       <c r="D11" s="2"/>
       <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="H11" s="6"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="D12" s="2"/>
       <c r="G12" s="5"/>
-      <c r="H12" s="5"/>
+      <c r="H12" s="6"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="H13" s="6"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="1"/>
       <c r="G14" s="5"/>
-      <c r="H14" s="5"/>
+      <c r="H14" s="6"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="H15" s="6"/>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A16" s="1"/>
       <c r="B16" s="1"/>
       <c r="G16" s="5"/>
-      <c r="H16" s="5"/>
+      <c r="H16" s="6"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
       <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="H17" s="6"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="G18" s="5"/>
-      <c r="H18" s="5"/>
+      <c r="H18" s="6"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+      <c r="H19" s="6"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="G20" s="5"/>
-      <c r="H20" s="5"/>
+      <c r="H20" s="6"/>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="H21" s="6"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="G22" s="5"/>
-      <c r="H22" s="5"/>
+      <c r="H22" s="6"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
+      <c r="H23" s="6"/>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="G24" s="5"/>
-      <c r="H24" s="5"/>
+      <c r="H24" s="6"/>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
+      <c r="H25" s="6"/>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="G26" s="5"/>
-      <c r="H26" s="5"/>
+      <c r="H26" s="6"/>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="G27" s="5"/>
-      <c r="H27" s="5"/>
+      <c r="H27" s="6"/>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="B28" s="1"/>
       <c r="G28" s="5"/>
-      <c r="H28" s="5"/>
+      <c r="H28" s="6"/>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="B29" s="1"/>
       <c r="G29" s="5"/>
-      <c r="H29" s="5"/>
+      <c r="H29" s="6"/>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="B30" s="1"/>
       <c r="G30" s="5"/>
-      <c r="H30" s="5"/>
+      <c r="H30" s="6"/>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="B31" s="1"/>
       <c r="G31" s="5"/>
-      <c r="H31" s="5"/>
+      <c r="H31" s="6"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="B32" s="1"/>
       <c r="G32" s="5"/>
-      <c r="H32" s="5"/>
+      <c r="H32" s="6"/>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="B33" s="1"/>
       <c r="G33" s="5"/>
-      <c r="H33" s="5"/>
+      <c r="H33" s="6"/>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="G34" s="5"/>
-      <c r="H34" s="5"/>
+      <c r="H34" s="6"/>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A35" s="1"/>
       <c r="B35" s="1"/>
       <c r="G35" s="5"/>
-      <c r="H35" s="5"/>
+      <c r="H35" s="6"/>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A36" s="1"/>
       <c r="B36" s="1"/>
       <c r="G36" s="5"/>
-      <c r="H36" s="5"/>
+      <c r="H36" s="6"/>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A37" s="1"/>
       <c r="B37" s="1"/>
       <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
+      <c r="H37" s="6"/>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A38" s="1"/>
       <c r="B38" s="1"/>
       <c r="G38" s="5"/>
-      <c r="H38" s="5"/>
+      <c r="H38" s="6"/>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A39" s="1"/>
       <c r="B39" s="1"/>
       <c r="G39" s="5"/>
-      <c r="H39" s="5"/>
+      <c r="H39" s="6"/>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A40" s="1"/>
       <c r="B40" s="1"/>
       <c r="G40" s="5"/>
-      <c r="H40" s="5"/>
+      <c r="H40" s="6"/>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A41" s="1"/>
       <c r="B41" s="1"/>
       <c r="G41" s="5"/>
-      <c r="H41" s="5"/>
+      <c r="H41" s="6"/>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A42" s="1"/>
       <c r="B42" s="1"/>
       <c r="G42" s="5"/>
-      <c r="H42" s="5"/>
+      <c r="H42" s="6"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A43" s="1"/>
       <c r="B43" s="1"/>
       <c r="G43" s="5"/>
-      <c r="H43" s="5"/>
+      <c r="H43" s="6"/>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A44" s="1"/>
       <c r="B44" s="1"/>
       <c r="G44" s="5"/>
-      <c r="H44" s="5"/>
+      <c r="H44" s="6"/>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A45" s="1"/>
       <c r="B45" s="1"/>
       <c r="G45" s="5"/>
-      <c r="H45" s="5"/>
+      <c r="H45" s="6"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A46" s="1"/>
       <c r="B46" s="1"/>
       <c r="G46" s="5"/>
-      <c r="H46" s="5"/>
+      <c r="H46" s="6"/>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A47" s="1"/>
       <c r="B47" s="1"/>
       <c r="G47" s="5"/>
-      <c r="H47" s="5"/>
+      <c r="H47" s="6"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A48" s="1"/>
       <c r="B48" s="1"/>
       <c r="G48" s="5"/>
-      <c r="H48" s="5"/>
+      <c r="H48" s="6"/>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A49" s="1"/>
       <c r="B49" s="1"/>
       <c r="G49" s="5"/>
-      <c r="H49" s="5"/>
+      <c r="H49" s="6"/>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A50" s="1"/>
       <c r="B50" s="1"/>
       <c r="G50" s="5"/>
-      <c r="H50" s="5"/>
+      <c r="H50" s="6"/>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A51" s="1"/>
       <c r="B51" s="1"/>
       <c r="G51" s="5"/>
-      <c r="H51" s="5"/>
+      <c r="H51" s="6"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A52" s="1"/>
       <c r="B52" s="1"/>
       <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
+      <c r="H52" s="6"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A53" s="1"/>
       <c r="B53" s="1"/>
       <c r="G53" s="5"/>
-      <c r="H53" s="5"/>
+      <c r="H53" s="6"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A54" s="1"/>
       <c r="B54" s="1"/>
       <c r="G54" s="5"/>
-      <c r="H54" s="5"/>
+      <c r="H54" s="6"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A55" s="1"/>
       <c r="B55" s="1"/>
       <c r="G55" s="5"/>
-      <c r="H55" s="5"/>
+      <c r="H55" s="6"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A56" s="1"/>
       <c r="B56" s="1"/>
       <c r="G56" s="5"/>
-      <c r="H56" s="5"/>
+      <c r="H56" s="6"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A57" s="1"/>
       <c r="B57" s="1"/>
       <c r="G57" s="5"/>
-      <c r="H57" s="5"/>
+      <c r="H57" s="6"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A58" s="1"/>
       <c r="B58" s="1"/>
       <c r="G58" s="5"/>
-      <c r="H58" s="5"/>
+      <c r="H58" s="6"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A59" s="1"/>
       <c r="B59" s="1"/>
       <c r="G59" s="5"/>
-      <c r="H59" s="5"/>
+      <c r="H59" s="6"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A60" s="1"/>
       <c r="B60" s="1"/>
       <c r="G60" s="5"/>
-      <c r="H60" s="5"/>
+      <c r="H60" s="6"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A61" s="1"/>
       <c r="B61" s="1"/>
       <c r="G61" s="5"/>
-      <c r="H61" s="5"/>
+      <c r="H61" s="6"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A62" s="1"/>
       <c r="B62" s="1"/>
       <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
+      <c r="H62" s="6"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A63" s="1"/>
       <c r="B63" s="1"/>
       <c r="G63" s="5"/>
-      <c r="H63" s="5"/>
+      <c r="H63" s="6"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A64" s="1"/>
       <c r="B64" s="1"/>
       <c r="G64" s="5"/>
-      <c r="H64" s="5"/>
+      <c r="H64" s="6"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
       <c r="G65" s="5"/>
-      <c r="H65" s="5"/>
+      <c r="H65" s="6"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A66" s="1"/>
       <c r="B66" s="1"/>
       <c r="G66" s="5"/>
-      <c r="H66" s="5"/>
+      <c r="H66" s="6"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A67" s="1"/>
       <c r="B67" s="1"/>
       <c r="G67" s="5"/>
-      <c r="H67" s="5"/>
+      <c r="H67" s="6"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A68" s="1"/>
       <c r="B68" s="1"/>
       <c r="G68" s="5"/>
-      <c r="H68" s="5"/>
+      <c r="H68" s="6"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A69" s="1"/>
       <c r="B69" s="1"/>
       <c r="G69" s="5"/>
-      <c r="H69" s="5"/>
+      <c r="H69" s="6"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A70" s="1"/>
       <c r="B70" s="1"/>
       <c r="G70" s="5"/>
-      <c r="H70" s="5"/>
+      <c r="H70" s="6"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A71" s="1"/>
       <c r="B71" s="1"/>
       <c r="G71" s="5"/>
-      <c r="H71" s="5"/>
+      <c r="H71" s="6"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A72" s="1"/>
       <c r="B72" s="1"/>
       <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
+      <c r="H72" s="6"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A73" s="1"/>
       <c r="B73" s="1"/>
       <c r="G73" s="5"/>
-      <c r="H73" s="5"/>
+      <c r="H73" s="6"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A74" s="1"/>
       <c r="B74" s="1"/>
       <c r="G74" s="5"/>
-      <c r="H74" s="5"/>
+      <c r="H74" s="6"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A75" s="1"/>
       <c r="B75" s="1"/>
       <c r="G75" s="5"/>
-      <c r="H75" s="5"/>
+      <c r="H75" s="6"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A76" s="1"/>
       <c r="B76" s="1"/>
       <c r="G76" s="5"/>
-      <c r="H76" s="5"/>
+      <c r="H76" s="6"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A77" s="1"/>
       <c r="B77" s="1"/>
       <c r="G77" s="5"/>
-      <c r="H77" s="5"/>
+      <c r="H77" s="6"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A78" s="1"/>
       <c r="B78" s="1"/>
       <c r="G78" s="5"/>
-      <c r="H78" s="5"/>
+      <c r="H78" s="6"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A79" s="1"/>
       <c r="B79" s="1"/>
       <c r="G79" s="5"/>
-      <c r="H79" s="5"/>
+      <c r="H79" s="6"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A80" s="1"/>
       <c r="B80" s="1"/>
       <c r="G80" s="5"/>
-      <c r="H80" s="5"/>
+      <c r="H80" s="6"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A81" s="1"/>
       <c r="B81" s="1"/>
       <c r="G81" s="5"/>
-      <c r="H81" s="5"/>
+      <c r="H81" s="6"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A82" s="1"/>
       <c r="B82" s="1"/>
       <c r="G82" s="5"/>
-      <c r="H82" s="5"/>
+      <c r="H82" s="6"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A83" s="1"/>
       <c r="B83" s="1"/>
       <c r="G83" s="5"/>
-      <c r="H83" s="5"/>
+      <c r="H83" s="6"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A84" s="1"/>
       <c r="B84" s="1"/>
       <c r="G84" s="5"/>
-      <c r="H84" s="5"/>
+      <c r="H84" s="6"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A85" s="1"/>
       <c r="B85" s="1"/>
       <c r="G85" s="5"/>
-      <c r="H85" s="5"/>
+      <c r="H85" s="6"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A86" s="1"/>
       <c r="B86" s="1"/>
       <c r="G86" s="5"/>
-      <c r="H86" s="5"/>
+      <c r="H86" s="6"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A87" s="1"/>
       <c r="B87" s="1"/>
       <c r="G87" s="5"/>
-      <c r="H87" s="5"/>
+      <c r="H87" s="6"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A88" s="1"/>
       <c r="B88" s="1"/>
       <c r="G88" s="5"/>
-      <c r="H88" s="5"/>
+      <c r="H88" s="6"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A89" s="1"/>
       <c r="B89" s="1"/>
       <c r="G89" s="5"/>
-      <c r="H89" s="5"/>
+      <c r="H89" s="6"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A90" s="1"/>
       <c r="B90" s="1"/>
       <c r="G90" s="5"/>
-      <c r="H90" s="5"/>
+      <c r="H90" s="6"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A91" s="1"/>
       <c r="B91" s="1"/>
       <c r="G91" s="5"/>
-      <c r="H91" s="5"/>
+      <c r="H91" s="6"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A92" s="1"/>
       <c r="B92" s="1"/>
       <c r="G92" s="5"/>
-      <c r="H92" s="5"/>
+      <c r="H92" s="6"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A93" s="1"/>
       <c r="B93" s="1"/>
       <c r="G93" s="5"/>
-      <c r="H93" s="5"/>
+      <c r="H93" s="6"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A94" s="1"/>
       <c r="B94" s="1"/>
       <c r="G94" s="5"/>
-      <c r="H94" s="5"/>
+      <c r="H94" s="6"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A95" s="1"/>
       <c r="B95" s="1"/>
       <c r="G95" s="5"/>
-      <c r="H95" s="5"/>
+      <c r="H95" s="6"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A96" s="1"/>
       <c r="B96" s="1"/>
       <c r="G96" s="5"/>
-      <c r="H96" s="5"/>
+      <c r="H96" s="6"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A97" s="1"/>
       <c r="B97" s="1"/>
       <c r="G97" s="5"/>
-      <c r="H97" s="5"/>
+      <c r="H97" s="6"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A98" s="1"/>
       <c r="B98" s="1"/>
       <c r="G98" s="5"/>
-      <c r="H98" s="5"/>
+      <c r="H98" s="6"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A99" s="1"/>
       <c r="B99" s="1"/>
       <c r="G99" s="5"/>
-      <c r="H99" s="5"/>
+      <c r="H99" s="6"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A100" s="1"/>
       <c r="B100" s="1"/>
       <c r="G100" s="5"/>
-      <c r="H100" s="5"/>
+      <c r="H100" s="6"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A101" s="1"/>
       <c r="B101" s="1"/>
       <c r="G101" s="5"/>
-      <c r="H101" s="5"/>
+      <c r="H101" s="6"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A102" s="1"/>
       <c r="B102" s="1"/>
       <c r="G102" s="5"/>
-      <c r="H102" s="5"/>
+      <c r="H102" s="6"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A103" s="1"/>
       <c r="B103" s="1"/>
       <c r="G103" s="5"/>
-      <c r="H103" s="5"/>
+      <c r="H103" s="6"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A104" s="1"/>
       <c r="B104" s="1"/>
       <c r="G104" s="5"/>
-      <c r="H104" s="5"/>
+      <c r="H104" s="6"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A105" s="1"/>
       <c r="B105" s="1"/>
       <c r="G105" s="5"/>
-      <c r="H105" s="5"/>
+      <c r="H105" s="6"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A106" s="1"/>
       <c r="B106" s="1"/>
       <c r="G106" s="5"/>
-      <c r="H106" s="5"/>
+      <c r="H106" s="6"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A107" s="1"/>
       <c r="B107" s="1"/>
       <c r="G107" s="5"/>
-      <c r="H107" s="5"/>
+      <c r="H107" s="6"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A108" s="1"/>
       <c r="B108" s="1"/>
       <c r="G108" s="5"/>
-      <c r="H108" s="5"/>
+      <c r="H108" s="6"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A109" s="1"/>
       <c r="B109" s="1"/>
       <c r="G109" s="5"/>
-      <c r="H109" s="5"/>
+      <c r="H109" s="6"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A110" s="1"/>
       <c r="B110" s="1"/>
       <c r="G110" s="5"/>
-      <c r="H110" s="5"/>
+      <c r="H110" s="6"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A111" s="1"/>
       <c r="B111" s="1"/>
       <c r="G111" s="5"/>
-      <c r="H111" s="5"/>
+      <c r="H111" s="6"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A112" s="1"/>
       <c r="B112" s="1"/>
       <c r="G112" s="5"/>
-      <c r="H112" s="5"/>
+      <c r="H112" s="6"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A113" s="1"/>
       <c r="B113" s="1"/>
       <c r="G113" s="5"/>
-      <c r="H113" s="5"/>
+      <c r="H113" s="6"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A114" s="1"/>
       <c r="B114" s="1"/>
       <c r="G114" s="5"/>
-      <c r="H114" s="5"/>
+      <c r="H114" s="6"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A115" s="1"/>
       <c r="B115" s="1"/>
       <c r="G115" s="5"/>
-      <c r="H115" s="5"/>
+      <c r="H115" s="6"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A116" s="1"/>
       <c r="B116" s="1"/>
       <c r="G116" s="5"/>
-      <c r="H116" s="5"/>
+      <c r="H116" s="6"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A117" s="1"/>
       <c r="B117" s="1"/>
       <c r="G117" s="5"/>
-      <c r="H117" s="5"/>
+      <c r="H117" s="6"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A118" s="1"/>
       <c r="B118" s="1"/>
       <c r="G118" s="5"/>
-      <c r="H118" s="5"/>
+      <c r="H118" s="6"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="1"/>
       <c r="B119" s="1"/>
       <c r="G119" s="5"/>
-      <c r="H119" s="5"/>
+      <c r="H119" s="6"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="1"/>
       <c r="B120" s="1"/>
       <c r="G120" s="5"/>
-      <c r="H120" s="5"/>
+      <c r="H120" s="6"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="1"/>
       <c r="B121" s="1"/>
       <c r="G121" s="5"/>
-      <c r="H121" s="5"/>
+      <c r="H121" s="6"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="1"/>
       <c r="B122" s="1"/>
       <c r="G122" s="5"/>
-      <c r="H122" s="5"/>
+      <c r="H122" s="6"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="1"/>
       <c r="B123" s="1"/>
       <c r="G123" s="5"/>
-      <c r="H123" s="5"/>
+      <c r="H123" s="6"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="1"/>
       <c r="B124" s="1"/>
       <c r="G124" s="5"/>
-      <c r="H124" s="5"/>
+      <c r="H124" s="6"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="1"/>
       <c r="B125" s="1"/>
       <c r="G125" s="5"/>
-      <c r="H125" s="5"/>
+      <c r="H125" s="6"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="1"/>
       <c r="B126" s="1"/>
       <c r="G126" s="5"/>
-      <c r="H126" s="5"/>
+      <c r="H126" s="6"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="1"/>
       <c r="B127" s="1"/>
       <c r="G127" s="5"/>
-      <c r="H127" s="5"/>
+      <c r="H127" s="6"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="1"/>
       <c r="B128" s="1"/>
       <c r="G128" s="5"/>
-      <c r="H128" s="5"/>
+      <c r="H128" s="6"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="1"/>
       <c r="B129" s="1"/>
       <c r="G129" s="5"/>
-      <c r="H129" s="5"/>
+      <c r="H129" s="6"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="1"/>
       <c r="B130" s="1"/>
       <c r="G130" s="5"/>
-      <c r="H130" s="5"/>
+      <c r="H130" s="6"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="1"/>
       <c r="B131" s="1"/>
       <c r="G131" s="5"/>
-      <c r="H131" s="5"/>
+      <c r="H131" s="6"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="1"/>
       <c r="B132" s="1"/>
       <c r="G132" s="5"/>
-      <c r="H132" s="5"/>
+      <c r="H132" s="6"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A133" s="1"/>
       <c r="B133" s="1"/>
       <c r="G133" s="5"/>
-      <c r="H133" s="5"/>
+      <c r="H133" s="6"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A134" s="1"/>
       <c r="B134" s="1"/>
       <c r="G134" s="5"/>
-      <c r="H134" s="5"/>
+      <c r="H134" s="6"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A135" s="1"/>
       <c r="B135" s="1"/>
       <c r="G135" s="5"/>
-      <c r="H135" s="5"/>
+      <c r="H135" s="6"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A136" s="1"/>
       <c r="B136" s="1"/>
       <c r="G136" s="5"/>
-      <c r="H136" s="5"/>
+      <c r="H136" s="6"/>
     </row>
     <row r="137" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A137" s="1"/>
       <c r="B137" s="1"/>
       <c r="G137" s="5"/>
-      <c r="H137" s="5"/>
+      <c r="H137" s="6"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A138" s="1"/>
       <c r="B138" s="1"/>
       <c r="G138" s="5"/>
-      <c r="H138" s="5"/>
+      <c r="H138" s="6"/>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A139" s="1"/>
       <c r="B139" s="1"/>
       <c r="G139" s="5"/>
-      <c r="H139" s="5"/>
+      <c r="H139" s="6"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A140" s="1"/>
       <c r="B140" s="1"/>
       <c r="G140" s="5"/>
-      <c r="H140" s="5"/>
+      <c r="H140" s="6"/>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A141" s="1"/>
       <c r="B141" s="1"/>
       <c r="G141" s="5"/>
-      <c r="H141" s="5"/>
+      <c r="H141" s="6"/>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A142" s="1"/>
       <c r="B142" s="1"/>
       <c r="G142" s="5"/>
-      <c r="H142" s="5"/>
+      <c r="H142" s="6"/>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A143" s="1"/>
       <c r="B143" s="1"/>
       <c r="G143" s="5"/>
-      <c r="H143" s="5"/>
+      <c r="H143" s="6"/>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A144" s="1"/>
       <c r="B144" s="1"/>
       <c r="G144" s="5"/>
-      <c r="H144" s="5"/>
+      <c r="H144" s="6"/>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A145" s="1"/>
       <c r="B145" s="1"/>
       <c r="G145" s="5"/>
-      <c r="H145" s="5"/>
+      <c r="H145" s="6"/>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A146" s="1"/>
       <c r="B146" s="1"/>
       <c r="G146" s="5"/>
-      <c r="H146" s="5"/>
+      <c r="H146" s="6"/>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A147" s="1"/>
       <c r="B147" s="1"/>
       <c r="G147" s="5"/>
-      <c r="H147" s="5"/>
+      <c r="H147" s="6"/>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A148" s="1"/>
       <c r="B148" s="1"/>
       <c r="G148" s="5"/>
-      <c r="H148" s="5"/>
+      <c r="H148" s="6"/>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A149" s="1"/>
       <c r="B149" s="1"/>
       <c r="G149" s="5"/>
-      <c r="H149" s="5"/>
+      <c r="H149" s="6"/>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A150" s="1"/>
       <c r="B150" s="1"/>
       <c r="G150" s="5"/>
-      <c r="H150" s="5"/>
+      <c r="H150" s="6"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A151" s="1"/>
       <c r="B151" s="1"/>
       <c r="G151" s="5"/>
-      <c r="H151" s="5"/>
+      <c r="H151" s="6"/>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A152" s="1"/>
       <c r="B152" s="1"/>
       <c r="G152" s="5"/>
-      <c r="H152" s="5"/>
+      <c r="H152" s="6"/>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A153" s="1"/>
       <c r="B153" s="1"/>
       <c r="G153" s="5"/>
-      <c r="H153" s="5"/>
+      <c r="H153" s="6"/>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A154" s="1"/>
       <c r="B154" s="1"/>
       <c r="G154" s="5"/>
-      <c r="H154" s="5"/>
+      <c r="H154" s="6"/>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A155" s="1"/>
       <c r="B155" s="1"/>
       <c r="G155" s="5"/>
-      <c r="H155" s="5"/>
+      <c r="H155" s="6"/>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A156" s="1"/>
       <c r="B156" s="1"/>
       <c r="G156" s="5"/>
-      <c r="H156" s="5"/>
+      <c r="H156" s="6"/>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A157" s="1"/>
       <c r="B157" s="1"/>
       <c r="G157" s="5"/>
-      <c r="H157" s="5"/>
+      <c r="H157" s="6"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A158" s="1"/>
       <c r="B158" s="1"/>
       <c r="G158" s="5"/>
-      <c r="H158" s="5"/>
+      <c r="H158" s="6"/>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A159" s="1"/>
       <c r="B159" s="1"/>
       <c r="G159" s="5"/>
-      <c r="H159" s="5"/>
+      <c r="H159" s="6"/>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A160" s="1"/>
       <c r="B160" s="1"/>
       <c r="G160" s="5"/>
-      <c r="H160" s="5"/>
+      <c r="H160" s="6"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A161" s="1"/>
       <c r="B161" s="1"/>
       <c r="G161" s="5"/>
-      <c r="H161" s="5"/>
+      <c r="H161" s="6"/>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A162" s="1"/>
       <c r="B162" s="1"/>
       <c r="G162" s="5"/>
-      <c r="H162" s="5"/>
+      <c r="H162" s="6"/>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A163" s="1"/>
       <c r="B163" s="1"/>
       <c r="G163" s="5"/>
-      <c r="H163" s="5"/>
+      <c r="H163" s="6"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A164" s="1"/>
       <c r="B164" s="1"/>
       <c r="G164" s="5"/>
-      <c r="H164" s="5"/>
+      <c r="H164" s="6"/>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A165" s="1"/>
       <c r="B165" s="1"/>
       <c r="G165" s="5"/>
-      <c r="H165" s="5"/>
+      <c r="H165" s="6"/>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A166" s="1"/>
       <c r="B166" s="1"/>
       <c r="G166" s="5"/>
-      <c r="H166" s="5"/>
+      <c r="H166" s="6"/>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A167" s="1"/>
       <c r="B167" s="1"/>
       <c r="G167" s="5"/>
-      <c r="H167" s="5"/>
+      <c r="H167" s="6"/>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A168" s="1"/>
       <c r="B168" s="1"/>
       <c r="G168" s="5"/>
-      <c r="H168" s="5"/>
+      <c r="H168" s="6"/>
     </row>
     <row r="169" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A169" s="1"/>
       <c r="B169" s="1"/>
       <c r="G169" s="5"/>
-      <c r="H169" s="5"/>
+      <c r="H169" s="6"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A170" s="1"/>
       <c r="B170" s="1"/>
       <c r="G170" s="5"/>
-      <c r="H170" s="5"/>
+      <c r="H170" s="6"/>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A171" s="1"/>
       <c r="B171" s="1"/>
       <c r="G171" s="5"/>
-      <c r="H171" s="5"/>
+      <c r="H171" s="6"/>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A172" s="1"/>
       <c r="B172" s="1"/>
       <c r="G172" s="5"/>
-      <c r="H172" s="5"/>
+      <c r="H172" s="6"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A173" s="1"/>
       <c r="B173" s="1"/>
       <c r="G173" s="5"/>
-      <c r="H173" s="5"/>
+      <c r="H173" s="6"/>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A174" s="1"/>
       <c r="B174" s="1"/>
       <c r="G174" s="5"/>
-      <c r="H174" s="5"/>
+      <c r="H174" s="6"/>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A175" s="1"/>
       <c r="B175" s="1"/>
       <c r="G175" s="5"/>
-      <c r="H175" s="5"/>
+      <c r="H175" s="6"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A176" s="1"/>
       <c r="B176" s="1"/>
       <c r="G176" s="5"/>
-      <c r="H176" s="5"/>
+      <c r="H176" s="6"/>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A177" s="1"/>
       <c r="B177" s="1"/>
       <c r="G177" s="5"/>
-      <c r="H177" s="5"/>
+      <c r="H177" s="6"/>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A178" s="1"/>
       <c r="B178" s="1"/>
       <c r="G178" s="5"/>
-      <c r="H178" s="5"/>
+      <c r="H178" s="6"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A179" s="1"/>
       <c r="B179" s="1"/>
       <c r="G179" s="5"/>
-      <c r="H179" s="5"/>
+      <c r="H179" s="6"/>
     </row>
     <row r="180" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A180" s="1"/>
       <c r="B180" s="1"/>
       <c r="G180" s="5"/>
-      <c r="H180" s="5"/>
+      <c r="H180" s="6"/>
     </row>
     <row r="181" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A181" s="1"/>
       <c r="B181" s="1"/>
       <c r="G181" s="5"/>
-      <c r="H181" s="5"/>
+      <c r="H181" s="6"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A182" s="1"/>
       <c r="B182" s="1"/>
       <c r="G182" s="5"/>
-      <c r="H182" s="5"/>
+      <c r="H182" s="6"/>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A183" s="1"/>
       <c r="B183" s="1"/>
       <c r="G183" s="5"/>
-      <c r="H183" s="5"/>
+      <c r="H183" s="6"/>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A184" s="1"/>
       <c r="B184" s="1"/>
       <c r="G184" s="5"/>
-      <c r="H184" s="5"/>
+      <c r="H184" s="6"/>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A185" s="1"/>
       <c r="B185" s="1"/>
       <c r="G185" s="5"/>
-      <c r="H185" s="5"/>
+      <c r="H185" s="6"/>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A186" s="1"/>
       <c r="B186" s="1"/>
       <c r="G186" s="5"/>
-      <c r="H186" s="5"/>
+      <c r="H186" s="6"/>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A187" s="1"/>
       <c r="B187" s="1"/>
       <c r="G187" s="5"/>
-      <c r="H187" s="5"/>
+      <c r="H187" s="6"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A188" s="1"/>
       <c r="B188" s="1"/>
       <c r="G188" s="5"/>
-      <c r="H188" s="5"/>
+      <c r="H188" s="6"/>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A189" s="1"/>
       <c r="B189" s="1"/>
       <c r="G189" s="5"/>
-      <c r="H189" s="5"/>
+      <c r="H189" s="6"/>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A190" s="1"/>
       <c r="B190" s="1"/>
       <c r="G190" s="5"/>
-      <c r="H190" s="5"/>
+      <c r="H190" s="6"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A191" s="1"/>
       <c r="B191" s="1"/>
       <c r="G191" s="5"/>
-      <c r="H191" s="5"/>
+      <c r="H191" s="6"/>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A192" s="1"/>
       <c r="B192" s="1"/>
       <c r="G192" s="5"/>
-      <c r="H192" s="5"/>
+      <c r="H192" s="6"/>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A193" s="1"/>
       <c r="B193" s="1"/>
       <c r="G193" s="5"/>
-      <c r="H193" s="5"/>
+      <c r="H193" s="6"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A194" s="1"/>
       <c r="B194" s="1"/>
       <c r="G194" s="5"/>
-      <c r="H194" s="5"/>
+      <c r="H194" s="6"/>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A195" s="1"/>
       <c r="B195" s="1"/>
       <c r="G195" s="5"/>
-      <c r="H195" s="5"/>
+      <c r="H195" s="6"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A196" s="1"/>
       <c r="B196" s="1"/>
       <c r="G196" s="5"/>
-      <c r="H196" s="5"/>
+      <c r="H196" s="6"/>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A197" s="1"/>
       <c r="B197" s="1"/>
       <c r="G197" s="5"/>
-      <c r="H197" s="5"/>
+      <c r="H197" s="6"/>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A198" s="1"/>
       <c r="B198" s="1"/>
       <c r="G198" s="5"/>
-      <c r="H198" s="5"/>
+      <c r="H198" s="6"/>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A199" s="1"/>
       <c r="B199" s="1"/>
       <c r="G199" s="5"/>
-      <c r="H199" s="5"/>
+      <c r="H199" s="6"/>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A200" s="1"/>
       <c r="B200" s="1"/>
       <c r="G200" s="5"/>
-      <c r="H200" s="5"/>
+      <c r="H200" s="6"/>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A201" s="1"/>
       <c r="B201" s="1"/>
       <c r="G201" s="5"/>
-      <c r="H201" s="5"/>
+      <c r="H201" s="6"/>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A202" s="1"/>
       <c r="B202" s="1"/>
       <c r="G202" s="5"/>
-      <c r="H202" s="5"/>
+      <c r="H202" s="6"/>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A203" s="1"/>
       <c r="B203" s="1"/>
       <c r="G203" s="5"/>
-      <c r="H203" s="5"/>
+      <c r="H203" s="6"/>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A204" s="1"/>
       <c r="B204" s="1"/>
       <c r="G204" s="5"/>
-      <c r="H204" s="5"/>
+      <c r="H204" s="6"/>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A205" s="1"/>
       <c r="B205" s="1"/>
       <c r="G205" s="5"/>
-      <c r="H205" s="5"/>
+      <c r="H205" s="6"/>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A206" s="1"/>
       <c r="B206" s="1"/>
       <c r="G206" s="5"/>
-      <c r="H206" s="5"/>
+      <c r="H206" s="6"/>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A207" s="1"/>
       <c r="B207" s="1"/>
       <c r="G207" s="5"/>
-      <c r="H207" s="5"/>
+      <c r="H207" s="6"/>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A208" s="1"/>
       <c r="B208" s="1"/>
       <c r="G208" s="5"/>
-      <c r="H208" s="5"/>
+      <c r="H208" s="6"/>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A209" s="1"/>
       <c r="B209" s="1"/>
       <c r="G209" s="5"/>
-      <c r="H209" s="5"/>
+      <c r="H209" s="6"/>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A210" s="1"/>
       <c r="B210" s="1"/>
       <c r="G210" s="5"/>
-      <c r="H210" s="5"/>
+      <c r="H210" s="6"/>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A211" s="1"/>
       <c r="B211" s="1"/>
       <c r="G211" s="5"/>
-      <c r="H211" s="5"/>
+      <c r="H211" s="6"/>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A212" s="1"/>
       <c r="B212" s="1"/>
       <c r="G212" s="5"/>
-      <c r="H212" s="5"/>
+      <c r="H212" s="6"/>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A213" s="1"/>
       <c r="B213" s="1"/>
       <c r="G213" s="5"/>
-      <c r="H213" s="5"/>
+      <c r="H213" s="6"/>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A214" s="1"/>
       <c r="B214" s="1"/>
       <c r="G214" s="5"/>
-      <c r="H214" s="5"/>
+      <c r="H214" s="6"/>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A215" s="1"/>
       <c r="B215" s="1"/>
       <c r="G215" s="5"/>
-      <c r="H215" s="5"/>
+      <c r="H215" s="6"/>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A216" s="1"/>
       <c r="B216" s="1"/>
       <c r="G216" s="5"/>
-      <c r="H216" s="5"/>
+      <c r="H216" s="6"/>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A217" s="1"/>
       <c r="B217" s="1"/>
       <c r="G217" s="5"/>
-      <c r="H217" s="5"/>
+      <c r="H217" s="6"/>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A218" s="1"/>
       <c r="B218" s="1"/>
       <c r="G218" s="5"/>
-      <c r="H218" s="5"/>
+      <c r="H218" s="6"/>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A219" s="1"/>
       <c r="B219" s="1"/>
       <c r="G219" s="5"/>
-      <c r="H219" s="5"/>
+      <c r="H219" s="6"/>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A220" s="1"/>
       <c r="B220" s="1"/>
       <c r="G220" s="5"/>
-      <c r="H220" s="5"/>
+      <c r="H220" s="6"/>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A221" s="1"/>
       <c r="B221" s="1"/>
       <c r="G221" s="5"/>
-      <c r="H221" s="5"/>
+      <c r="H221" s="6"/>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A222" s="1"/>
       <c r="B222" s="1"/>
       <c r="G222" s="5"/>
-      <c r="H222" s="5"/>
+      <c r="H222" s="6"/>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A223" s="1"/>
       <c r="B223" s="1"/>
       <c r="G223" s="5"/>
-      <c r="H223" s="5"/>
+      <c r="H223" s="6"/>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A224" s="1"/>
       <c r="B224" s="1"/>
       <c r="G224" s="5"/>
-      <c r="H224" s="5"/>
+      <c r="H224" s="6"/>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A225" s="1"/>
       <c r="B225" s="1"/>
       <c r="G225" s="5"/>
-      <c r="H225" s="5"/>
+      <c r="H225" s="6"/>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A226" s="1"/>
       <c r="B226" s="1"/>
       <c r="G226" s="5"/>
-      <c r="H226" s="5"/>
+      <c r="H226" s="6"/>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A227" s="1"/>
       <c r="B227" s="1"/>
       <c r="G227" s="5"/>
-      <c r="H227" s="5"/>
+      <c r="H227" s="6"/>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A228" s="1"/>
       <c r="B228" s="1"/>
       <c r="G228" s="5"/>
-      <c r="H228" s="5"/>
+      <c r="H228" s="6"/>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A229" s="1"/>
       <c r="B229" s="1"/>
       <c r="G229" s="5"/>
-      <c r="H229" s="5"/>
+      <c r="H229" s="6"/>
     </row>
     <row r="230" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A230" s="1"/>
       <c r="B230" s="1"/>
       <c r="G230" s="5"/>
-      <c r="H230" s="5"/>
+      <c r="H230" s="6"/>
     </row>
     <row r="231" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A231" s="1"/>
       <c r="B231" s="1"/>
       <c r="G231" s="5"/>
-      <c r="H231" s="5"/>
+      <c r="H231" s="6"/>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A232" s="1"/>
       <c r="B232" s="1"/>
       <c r="G232" s="5"/>
-      <c r="H232" s="5"/>
+      <c r="H232" s="6"/>
     </row>
     <row r="233" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A233" s="1"/>
       <c r="B233" s="1"/>
       <c r="G233" s="5"/>
-      <c r="H233" s="5"/>
+      <c r="H233" s="6"/>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A234" s="1"/>
       <c r="B234" s="1"/>
       <c r="G234" s="5"/>
-      <c r="H234" s="5"/>
+      <c r="H234" s="6"/>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A235" s="1"/>
       <c r="B235" s="1"/>
       <c r="G235" s="5"/>
-      <c r="H235" s="5"/>
+      <c r="H235" s="6"/>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A236" s="1"/>
       <c r="B236" s="1"/>
       <c r="G236" s="5"/>
-      <c r="H236" s="5"/>
+      <c r="H236" s="6"/>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A237" s="1"/>
       <c r="B237" s="1"/>
       <c r="G237" s="5"/>
-      <c r="H237" s="5"/>
+      <c r="H237" s="6"/>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A238" s="1"/>
       <c r="B238" s="1"/>
       <c r="G238" s="5"/>
-      <c r="H238" s="5"/>
+      <c r="H238" s="6"/>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A239" s="1"/>
       <c r="B239" s="1"/>
       <c r="G239" s="5"/>
-      <c r="H239" s="5"/>
+      <c r="H239" s="6"/>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A240" s="1"/>
       <c r="B240" s="1"/>
       <c r="G240" s="5"/>
-      <c r="H240" s="5"/>
+      <c r="H240" s="6"/>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A241" s="1"/>
       <c r="B241" s="1"/>
       <c r="G241" s="5"/>
-      <c r="H241" s="5"/>
+      <c r="H241" s="6"/>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A242" s="1"/>
       <c r="B242" s="1"/>
       <c r="G242" s="5"/>
-      <c r="H242" s="5"/>
+      <c r="H242" s="6"/>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A243" s="1"/>
       <c r="B243" s="1"/>
       <c r="G243" s="5"/>
-      <c r="H243" s="5"/>
+      <c r="H243" s="6"/>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A244" s="1"/>
       <c r="B244" s="1"/>
       <c r="G244" s="5"/>
-      <c r="H244" s="5"/>
+      <c r="H244" s="6"/>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A245" s="1"/>
       <c r="B245" s="1"/>
       <c r="G245" s="5"/>
-      <c r="H245" s="5"/>
+      <c r="H245" s="6"/>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A246" s="1"/>
       <c r="B246" s="1"/>
       <c r="G246" s="5"/>
-      <c r="H246" s="5"/>
+      <c r="H246" s="6"/>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A247" s="1"/>
       <c r="B247" s="1"/>
       <c r="G247" s="5"/>
-      <c r="H247" s="5"/>
+      <c r="H247" s="6"/>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A248" s="1"/>
       <c r="B248" s="1"/>
       <c r="G248" s="5"/>
-      <c r="H248" s="5"/>
+      <c r="H248" s="6"/>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A249" s="1"/>
       <c r="B249" s="1"/>
       <c r="G249" s="5"/>
-      <c r="H249" s="5"/>
+      <c r="H249" s="6"/>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A250" s="1"/>
       <c r="B250" s="1"/>
       <c r="G250" s="5"/>
-      <c r="H250" s="5"/>
+      <c r="H250" s="6"/>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A251" s="1"/>
       <c r="B251" s="1"/>
       <c r="G251" s="5"/>
-      <c r="H251" s="5"/>
+      <c r="H251" s="6"/>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A252" s="1"/>
       <c r="B252" s="1"/>
       <c r="G252" s="5"/>
-      <c r="H252" s="5"/>
+      <c r="H252" s="6"/>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A253" s="1"/>
       <c r="B253" s="1"/>
       <c r="G253" s="5"/>
-      <c r="H253" s="5"/>
+      <c r="H253" s="6"/>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A254" s="1"/>
       <c r="B254" s="1"/>
       <c r="G254" s="5"/>
-      <c r="H254" s="5"/>
+      <c r="H254" s="6"/>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A255" s="1"/>
       <c r="B255" s="1"/>
       <c r="G255" s="5"/>
-      <c r="H255" s="5"/>
+      <c r="H255" s="6"/>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A256" s="1"/>
       <c r="B256" s="1"/>
       <c r="G256" s="5"/>
-      <c r="H256" s="5"/>
+      <c r="H256" s="6"/>
     </row>
     <row r="257" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A257" s="1"/>
       <c r="B257" s="1"/>
       <c r="G257" s="5"/>
-      <c r="H257" s="5"/>
+      <c r="H257" s="6"/>
     </row>
     <row r="258" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A258" s="1"/>
       <c r="B258" s="1"/>
       <c r="G258" s="5"/>
-      <c r="H258" s="5"/>
+      <c r="H258" s="6"/>
     </row>
     <row r="259" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A259" s="1"/>
       <c r="B259" s="1"/>
       <c r="G259" s="5"/>
-      <c r="H259" s="5"/>
+      <c r="H259" s="6"/>
     </row>
     <row r="260" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A260" s="1"/>
       <c r="B260" s="1"/>
       <c r="G260" s="5"/>
-      <c r="H260" s="5"/>
+      <c r="H260" s="6"/>
     </row>
     <row r="261" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A261" s="1"/>
       <c r="B261" s="1"/>
       <c r="G261" s="5"/>
-      <c r="H261" s="5"/>
+      <c r="H261" s="6"/>
     </row>
     <row r="262" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A262" s="1"/>
       <c r="B262" s="1"/>
       <c r="G262" s="5"/>
-      <c r="H262" s="5"/>
+      <c r="H262" s="6"/>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A263" s="1"/>
       <c r="B263" s="1"/>
       <c r="G263" s="5"/>
-      <c r="H263" s="5"/>
+      <c r="H263" s="6"/>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A264" s="1"/>
       <c r="B264" s="1"/>
       <c r="G264" s="5"/>
-      <c r="H264" s="5"/>
+      <c r="H264" s="6"/>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A265" s="1"/>
       <c r="B265" s="1"/>
       <c r="G265" s="5"/>
-      <c r="H265" s="5"/>
+      <c r="H265" s="6"/>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A266" s="1"/>
       <c r="B266" s="1"/>
       <c r="G266" s="5"/>
-      <c r="H266" s="5"/>
+      <c r="H266" s="6"/>
     </row>
     <row r="267" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A267" s="1"/>
       <c r="B267" s="1"/>
       <c r="G267" s="5"/>
-      <c r="H267" s="5"/>
+      <c r="H267" s="6"/>
     </row>
     <row r="268" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A268" s="1"/>
       <c r="B268" s="1"/>
       <c r="G268" s="5"/>
-      <c r="H268" s="5"/>
+      <c r="H268" s="6"/>
     </row>
     <row r="269" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A269" s="1"/>
       <c r="B269" s="1"/>
       <c r="G269" s="5"/>
-      <c r="H269" s="5"/>
+      <c r="H269" s="6"/>
     </row>
     <row r="270" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A270" s="1"/>
       <c r="B270" s="1"/>
       <c r="G270" s="5"/>
-      <c r="H270" s="5"/>
+      <c r="H270" s="6"/>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A271" s="1"/>
       <c r="B271" s="1"/>
       <c r="G271" s="5"/>
-      <c r="H271" s="5"/>
+      <c r="H271" s="6"/>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A272" s="1"/>
       <c r="B272" s="1"/>
       <c r="G272" s="5"/>
-      <c r="H272" s="5"/>
+      <c r="H272" s="6"/>
     </row>
     <row r="273" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A273" s="1"/>
       <c r="B273" s="1"/>
       <c r="G273" s="5"/>
-      <c r="H273" s="5"/>
+      <c r="H273" s="6"/>
     </row>
     <row r="274" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A274" s="1"/>
       <c r="B274" s="1"/>
       <c r="G274" s="5"/>
-      <c r="H274" s="5"/>
+      <c r="H274" s="6"/>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A275" s="1"/>
       <c r="B275" s="1"/>
       <c r="G275" s="5"/>
-      <c r="H275" s="5"/>
+      <c r="H275" s="6"/>
     </row>
     <row r="276" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A276" s="1"/>
       <c r="B276" s="1"/>
       <c r="G276" s="5"/>
-      <c r="H276" s="5"/>
+      <c r="H276" s="6"/>
     </row>
     <row r="277" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A277" s="1"/>
       <c r="B277" s="1"/>
       <c r="G277" s="5"/>
-      <c r="H277" s="5"/>
+      <c r="H277" s="6"/>
     </row>
     <row r="278" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A278" s="1"/>
       <c r="B278" s="1"/>
       <c r="G278" s="5"/>
-      <c r="H278" s="5"/>
+      <c r="H278" s="6"/>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A279" s="1"/>
       <c r="B279" s="1"/>
       <c r="G279" s="5"/>
-      <c r="H279" s="5"/>
+      <c r="H279" s="6"/>
     </row>
     <row r="280" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A280" s="1"/>
       <c r="B280" s="1"/>
       <c r="G280" s="5"/>
-      <c r="H280" s="5"/>
+      <c r="H280" s="6"/>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A281" s="1"/>
       <c r="B281" s="1"/>
       <c r="G281" s="5"/>
-      <c r="H281" s="5"/>
+      <c r="H281" s="6"/>
     </row>
     <row r="282" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A282" s="1"/>
       <c r="B282" s="1"/>
       <c r="G282" s="5"/>
-      <c r="H282" s="5"/>
+      <c r="H282" s="6"/>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A283" s="1"/>
       <c r="B283" s="1"/>
       <c r="G283" s="5"/>
-      <c r="H283" s="5"/>
+      <c r="H283" s="6"/>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A284" s="1"/>
       <c r="B284" s="1"/>
       <c r="G284" s="5"/>
-      <c r="H284" s="5"/>
+      <c r="H284" s="6"/>
     </row>
     <row r="285" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A285" s="1"/>
       <c r="B285" s="1"/>
       <c r="G285" s="5"/>
-      <c r="H285" s="5"/>
+      <c r="H285" s="6"/>
     </row>
     <row r="286" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A286" s="1"/>
       <c r="B286" s="1"/>
       <c r="G286" s="5"/>
-      <c r="H286" s="5"/>
+      <c r="H286" s="6"/>
     </row>
     <row r="287" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A287" s="1"/>
       <c r="B287" s="1"/>
       <c r="G287" s="5"/>
-      <c r="H287" s="5"/>
+      <c r="H287" s="6"/>
     </row>
     <row r="288" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A288" s="1"/>
       <c r="B288" s="1"/>
       <c r="G288" s="5"/>
-      <c r="H288" s="5"/>
+      <c r="H288" s="6"/>
     </row>
     <row r="289" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A289" s="1"/>
       <c r="B289" s="1"/>
       <c r="G289" s="5"/>
-      <c r="H289" s="5"/>
+      <c r="H289" s="6"/>
     </row>
     <row r="290" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A290" s="1"/>
       <c r="B290" s="1"/>
       <c r="G290" s="5"/>
-      <c r="H290" s="5"/>
+      <c r="H290" s="6"/>
     </row>
     <row r="291" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A291" s="1"/>
       <c r="B291" s="1"/>
       <c r="G291" s="5"/>
-      <c r="H291" s="5"/>
+      <c r="H291" s="6"/>
     </row>
     <row r="292" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A292" s="1"/>
       <c r="B292" s="1"/>
       <c r="G292" s="5"/>
-      <c r="H292" s="5"/>
+      <c r="H292" s="6"/>
     </row>
     <row r="293" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A293" s="1"/>
       <c r="B293" s="1"/>
       <c r="G293" s="5"/>
-      <c r="H293" s="5"/>
+      <c r="H293" s="6"/>
     </row>
     <row r="294" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A294" s="1"/>
       <c r="B294" s="1"/>
       <c r="G294" s="5"/>
-      <c r="H294" s="5"/>
+      <c r="H294" s="6"/>
     </row>
     <row r="295" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A295" s="1"/>
       <c r="B295" s="1"/>
       <c r="G295" s="5"/>
-      <c r="H295" s="5"/>
+      <c r="H295" s="6"/>
     </row>
     <row r="296" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A296" s="1"/>
       <c r="B296" s="1"/>
       <c r="G296" s="5"/>
-      <c r="H296" s="5"/>
+      <c r="H296" s="6"/>
     </row>
     <row r="297" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A297" s="1"/>
       <c r="B297" s="1"/>
       <c r="G297" s="5"/>
-      <c r="H297" s="5"/>
+      <c r="H297" s="6"/>
     </row>
     <row r="298" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A298" s="1"/>
       <c r="B298" s="1"/>
       <c r="G298" s="5"/>
-      <c r="H298" s="5"/>
+      <c r="H298" s="6"/>
     </row>
     <row r="299" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A299" s="1"/>
       <c r="B299" s="1"/>
       <c r="G299" s="5"/>
-      <c r="H299" s="5"/>
+      <c r="H299" s="6"/>
     </row>
     <row r="300" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A300" s="1"/>
       <c r="B300" s="1"/>
       <c r="G300" s="5"/>
-      <c r="H300" s="5"/>
+      <c r="H300" s="6"/>
     </row>
     <row r="301" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A301" s="1"/>
       <c r="B301" s="1"/>
       <c r="G301" s="5"/>
-      <c r="H301" s="5"/>
+      <c r="H301" s="6"/>
     </row>
     <row r="302" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A302" s="1"/>
       <c r="B302" s="1"/>
       <c r="G302" s="5"/>
-      <c r="H302" s="5"/>
+      <c r="H302" s="6"/>
     </row>
     <row r="303" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A303" s="1"/>
       <c r="B303" s="1"/>
       <c r="G303" s="5"/>
-      <c r="H303" s="5"/>
+      <c r="H303" s="6"/>
     </row>
     <row r="304" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A304" s="1"/>
       <c r="B304" s="1"/>
       <c r="G304" s="5"/>
-      <c r="H304" s="5"/>
+      <c r="H304" s="6"/>
     </row>
     <row r="305" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A305" s="1"/>
       <c r="B305" s="1"/>
       <c r="G305" s="5"/>
-      <c r="H305" s="5"/>
+      <c r="H305" s="6"/>
     </row>
     <row r="306" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A306" s="1"/>
       <c r="B306" s="1"/>
       <c r="G306" s="5"/>
-      <c r="H306" s="5"/>
+      <c r="H306" s="6"/>
     </row>
     <row r="307" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A307" s="1"/>
       <c r="B307" s="1"/>
       <c r="G307" s="5"/>
-      <c r="H307" s="5"/>
+      <c r="H307" s="6"/>
     </row>
     <row r="308" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A308" s="1"/>
       <c r="B308" s="1"/>
       <c r="G308" s="5"/>
-      <c r="H308" s="5"/>
+      <c r="H308" s="6"/>
     </row>
     <row r="309" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A309" s="1"/>
       <c r="B309" s="1"/>
       <c r="G309" s="5"/>
-      <c r="H309" s="5"/>
+      <c r="H309" s="6"/>
     </row>
     <row r="310" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A310" s="1"/>
       <c r="B310" s="1"/>
       <c r="G310" s="5"/>
-      <c r="H310" s="5"/>
+      <c r="H310" s="6"/>
     </row>
     <row r="311" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A311" s="1"/>
       <c r="B311" s="1"/>
       <c r="G311" s="5"/>
-      <c r="H311" s="5"/>
+      <c r="H311" s="6"/>
     </row>
     <row r="312" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A312" s="1"/>
       <c r="B312" s="1"/>
       <c r="G312" s="5"/>
-      <c r="H312" s="5"/>
+      <c r="H312" s="6"/>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A313" s="1"/>
       <c r="B313" s="1"/>
       <c r="G313" s="5"/>
-      <c r="H313" s="5"/>
+      <c r="H313" s="6"/>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A314" s="1"/>
       <c r="B314" s="1"/>
       <c r="G314" s="5"/>
-      <c r="H314" s="5"/>
+      <c r="H314" s="6"/>
     </row>
     <row r="315" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A315" s="1"/>
       <c r="B315" s="1"/>
       <c r="G315" s="5"/>
-      <c r="H315" s="5"/>
+      <c r="H315" s="6"/>
     </row>
     <row r="316" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A316" s="1"/>
       <c r="B316" s="1"/>
       <c r="G316" s="5"/>
-      <c r="H316" s="5"/>
+      <c r="H316" s="6"/>
     </row>
     <row r="317" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A317" s="1"/>
       <c r="B317" s="1"/>
       <c r="G317" s="5"/>
-      <c r="H317" s="5"/>
+      <c r="H317" s="6"/>
     </row>
     <row r="318" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A318" s="1"/>
       <c r="B318" s="1"/>
       <c r="G318" s="5"/>
-      <c r="H318" s="5"/>
+      <c r="H318" s="6"/>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A319" s="1"/>
       <c r="B319" s="1"/>
       <c r="G319" s="5"/>
-      <c r="H319" s="5"/>
+      <c r="H319" s="6"/>
     </row>
     <row r="320" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A320" s="1"/>
       <c r="B320" s="1"/>
       <c r="G320" s="5"/>
-      <c r="H320" s="5"/>
+      <c r="H320" s="6"/>
     </row>
     <row r="321" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A321" s="1"/>
       <c r="B321" s="1"/>
       <c r="G321" s="5"/>
-      <c r="H321" s="5"/>
+      <c r="H321" s="6"/>
     </row>
     <row r="322" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A322" s="1"/>
       <c r="B322" s="1"/>
       <c r="G322" s="5"/>
-      <c r="H322" s="5"/>
+      <c r="H322" s="6"/>
     </row>
     <row r="323" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A323" s="1"/>
       <c r="B323" s="1"/>
       <c r="G323" s="5"/>
-      <c r="H323" s="5"/>
+      <c r="H323" s="6"/>
     </row>
     <row r="324" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A324" s="1"/>
       <c r="B324" s="1"/>
       <c r="G324" s="5"/>
-      <c r="H324" s="5"/>
+      <c r="H324" s="6"/>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A325" s="1"/>
       <c r="B325" s="1"/>
       <c r="G325" s="5"/>
-      <c r="H325" s="5"/>
+      <c r="H325" s="6"/>
     </row>
     <row r="326" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A326" s="1"/>
       <c r="B326" s="1"/>
       <c r="G326" s="5"/>
-      <c r="H326" s="5"/>
+      <c r="H326" s="6"/>
     </row>
     <row r="327" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A327" s="1"/>
       <c r="B327" s="1"/>
       <c r="G327" s="5"/>
-      <c r="H327" s="5"/>
+      <c r="H327" s="6"/>
     </row>
     <row r="328" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A328" s="1"/>
       <c r="B328" s="1"/>
       <c r="G328" s="5"/>
-      <c r="H328" s="5"/>
+      <c r="H328" s="6"/>
     </row>
     <row r="329" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A329" s="1"/>
       <c r="B329" s="1"/>
       <c r="G329" s="5"/>
-      <c r="H329" s="5"/>
+      <c r="H329" s="6"/>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A330" s="1"/>
       <c r="B330" s="1"/>
       <c r="G330" s="5"/>
-      <c r="H330" s="5"/>
+      <c r="H330" s="6"/>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A331" s="1"/>
       <c r="B331" s="1"/>
       <c r="G331" s="5"/>
-      <c r="H331" s="5"/>
+      <c r="H331" s="6"/>
     </row>
     <row r="332" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A332" s="1"/>
       <c r="B332" s="1"/>
       <c r="G332" s="5"/>
-      <c r="H332" s="5"/>
+      <c r="H332" s="6"/>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A333" s="1"/>
       <c r="B333" s="1"/>
       <c r="G333" s="5"/>
-      <c r="H333" s="5"/>
+      <c r="H333" s="6"/>
     </row>
     <row r="334" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A334" s="1"/>
       <c r="B334" s="1"/>
       <c r="G334" s="5"/>
-      <c r="H334" s="5"/>
+      <c r="H334" s="6"/>
     </row>
     <row r="335" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A335" s="1"/>
       <c r="B335" s="1"/>
       <c r="G335" s="5"/>
-      <c r="H335" s="5"/>
+      <c r="H335" s="6"/>
     </row>
     <row r="336" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A336" s="1"/>
       <c r="B336" s="1"/>
       <c r="G336" s="5"/>
-      <c r="H336" s="5"/>
+      <c r="H336" s="6"/>
     </row>
     <row r="337" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A337" s="1"/>
       <c r="B337" s="1"/>
       <c r="G337" s="5"/>
-      <c r="H337" s="5"/>
+      <c r="H337" s="6"/>
     </row>
     <row r="338" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A338" s="1"/>
       <c r="B338" s="1"/>
       <c r="G338" s="5"/>
-      <c r="H338" s="5"/>
+      <c r="H338" s="6"/>
     </row>
     <row r="339" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A339" s="1"/>
       <c r="B339" s="1"/>
       <c r="G339" s="5"/>
-      <c r="H339" s="5"/>
+      <c r="H339" s="6"/>
     </row>
     <row r="340" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A340" s="1"/>
       <c r="B340" s="1"/>
       <c r="G340" s="5"/>
-      <c r="H340" s="5"/>
+      <c r="H340" s="6"/>
     </row>
     <row r="341" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A341" s="1"/>
       <c r="B341" s="1"/>
       <c r="G341" s="5"/>
-      <c r="H341" s="5"/>
+      <c r="H341" s="6"/>
     </row>
     <row r="342" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A342" s="1"/>
       <c r="B342" s="1"/>
       <c r="G342" s="5"/>
-      <c r="H342" s="5"/>
+      <c r="H342" s="6"/>
     </row>
     <row r="343" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A343" s="1"/>
       <c r="B343" s="1"/>
       <c r="G343" s="5"/>
-      <c r="H343" s="5"/>
+      <c r="H343" s="6"/>
     </row>
     <row r="344" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A344" s="1"/>
       <c r="B344" s="1"/>
       <c r="G344" s="5"/>
-      <c r="H344" s="5"/>
+      <c r="H344" s="6"/>
     </row>
     <row r="345" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A345" s="1"/>
       <c r="B345" s="1"/>
       <c r="G345" s="5"/>
-      <c r="H345" s="5"/>
+      <c r="H345" s="6"/>
     </row>
     <row r="346" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A346" s="1"/>
       <c r="B346" s="1"/>
       <c r="G346" s="5"/>
-      <c r="H346" s="5"/>
+      <c r="H346" s="6"/>
     </row>
     <row r="347" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A347" s="1"/>
       <c r="B347" s="1"/>
       <c r="G347" s="5"/>
-      <c r="H347" s="5"/>
+      <c r="H347" s="6"/>
     </row>
     <row r="348" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A348" s="1"/>
       <c r="B348" s="1"/>
       <c r="G348" s="5"/>
-      <c r="H348" s="5"/>
+      <c r="H348" s="6"/>
     </row>
     <row r="349" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A349" s="1"/>
       <c r="B349" s="1"/>
       <c r="G349" s="5"/>
-      <c r="H349" s="5"/>
+      <c r="H349" s="6"/>
     </row>
     <row r="350" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A350" s="1"/>
       <c r="B350" s="1"/>
       <c r="G350" s="5"/>
-      <c r="H350" s="5"/>
+      <c r="H350" s="6"/>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A351" s="1"/>
       <c r="B351" s="1"/>
       <c r="G351" s="5"/>
-      <c r="H351" s="5"/>
+      <c r="H351" s="6"/>
     </row>
     <row r="352" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A352" s="1"/>
       <c r="B352" s="1"/>
       <c r="G352" s="5"/>
-      <c r="H352" s="5"/>
+      <c r="H352" s="6"/>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A353" s="1"/>
       <c r="B353" s="1"/>
       <c r="G353" s="5"/>
-      <c r="H353" s="5"/>
+      <c r="H353" s="6"/>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A354" s="1"/>
       <c r="B354" s="1"/>
       <c r="G354" s="5"/>
-      <c r="H354" s="5"/>
+      <c r="H354" s="6"/>
     </row>
     <row r="355" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A355" s="1"/>
       <c r="B355" s="1"/>
       <c r="G355" s="5"/>
-      <c r="H355" s="5"/>
+      <c r="H355" s="6"/>
     </row>
     <row r="356" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A356" s="1"/>
       <c r="B356" s="1"/>
       <c r="G356" s="5"/>
-      <c r="H356" s="5"/>
+      <c r="H356" s="6"/>
     </row>
     <row r="357" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A357" s="1"/>
       <c r="B357" s="1"/>
       <c r="G357" s="5"/>
-      <c r="H357" s="5"/>
+      <c r="H357" s="6"/>
     </row>
     <row r="358" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A358" s="1"/>
       <c r="B358" s="1"/>
       <c r="G358" s="5"/>
-      <c r="H358" s="5"/>
+      <c r="H358" s="6"/>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A359" s="1"/>
       <c r="B359" s="1"/>
       <c r="G359" s="5"/>
-      <c r="H359" s="5"/>
+      <c r="H359" s="6"/>
     </row>
     <row r="360" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A360" s="1"/>
       <c r="B360" s="1"/>
       <c r="G360" s="5"/>
-      <c r="H360" s="5"/>
+      <c r="H360" s="6"/>
     </row>
     <row r="361" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A361" s="1"/>
       <c r="B361" s="1"/>
       <c r="G361" s="5"/>
-      <c r="H361" s="5"/>
+      <c r="H361" s="6"/>
     </row>
     <row r="362" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A362" s="1"/>
       <c r="B362" s="1"/>
       <c r="G362" s="5"/>
-      <c r="H362" s="5"/>
+      <c r="H362" s="6"/>
     </row>
     <row r="363" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A363" s="1"/>
       <c r="B363" s="1"/>
       <c r="G363" s="5"/>
-      <c r="H363" s="5"/>
+      <c r="H363" s="6"/>
     </row>
     <row r="364" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A364" s="1"/>
       <c r="B364" s="1"/>
       <c r="G364" s="5"/>
-      <c r="H364" s="5"/>
+      <c r="H364" s="6"/>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A365" s="1"/>
       <c r="B365" s="1"/>
       <c r="G365" s="5"/>
-      <c r="H365" s="5"/>
+      <c r="H365" s="6"/>
     </row>
     <row r="366" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A366" s="1"/>
       <c r="B366" s="1"/>
       <c r="G366" s="5"/>
-      <c r="H366" s="5"/>
+      <c r="H366" s="6"/>
     </row>
     <row r="367" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A367" s="1"/>
       <c r="B367" s="1"/>
       <c r="G367" s="5"/>
-      <c r="H367" s="5"/>
+      <c r="H367" s="6"/>
     </row>
     <row r="368" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A368" s="1"/>
       <c r="B368" s="1"/>
       <c r="G368" s="5"/>
-      <c r="H368" s="5"/>
+      <c r="H368" s="6"/>
     </row>
     <row r="369" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A369" s="1"/>
       <c r="B369" s="1"/>
       <c r="G369" s="5"/>
-      <c r="H369" s="5"/>
+      <c r="H369" s="6"/>
     </row>
     <row r="370" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A370" s="1"/>
       <c r="B370" s="1"/>
       <c r="G370" s="5"/>
-      <c r="H370" s="5"/>
+      <c r="H370" s="6"/>
     </row>
     <row r="371" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A371" s="1"/>
       <c r="B371" s="1"/>
       <c r="G371" s="5"/>
-      <c r="H371" s="5"/>
+      <c r="H371" s="6"/>
     </row>
     <row r="372" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A372" s="1"/>
       <c r="B372" s="1"/>
       <c r="G372" s="5"/>
-      <c r="H372" s="5"/>
+      <c r="H372" s="6"/>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A373" s="1"/>
       <c r="B373" s="1"/>
       <c r="G373" s="5"/>
-      <c r="H373" s="5"/>
+      <c r="H373" s="6"/>
     </row>
     <row r="374" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A374" s="1"/>
       <c r="B374" s="1"/>
       <c r="G374" s="5"/>
-      <c r="H374" s="5"/>
+      <c r="H374" s="6"/>
     </row>
     <row r="375" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A375" s="1"/>
       <c r="B375" s="1"/>
       <c r="G375" s="5"/>
-      <c r="H375" s="5"/>
+      <c r="H375" s="6"/>
     </row>
     <row r="376" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A376" s="1"/>
       <c r="B376" s="1"/>
       <c r="G376" s="5"/>
-      <c r="H376" s="5"/>
+      <c r="H376" s="6"/>
     </row>
     <row r="377" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A377" s="1"/>
       <c r="B377" s="1"/>
       <c r="G377" s="5"/>
-      <c r="H377" s="5"/>
+      <c r="H377" s="6"/>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A378" s="1"/>
       <c r="B378" s="1"/>
       <c r="G378" s="5"/>
-      <c r="H378" s="5"/>
+      <c r="H378" s="6"/>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A379" s="1"/>
       <c r="B379" s="1"/>
       <c r="G379" s="5"/>
-      <c r="H379" s="5"/>
+      <c r="H379" s="6"/>
     </row>
     <row r="380" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A380" s="1"/>
       <c r="B380" s="1"/>
       <c r="G380" s="5"/>
-      <c r="H380" s="5"/>
+      <c r="H380" s="6"/>
     </row>
     <row r="381" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A381" s="1"/>
       <c r="B381" s="1"/>
       <c r="G381" s="5"/>
-      <c r="H381" s="5"/>
+      <c r="H381" s="6"/>
     </row>
     <row r="382" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A382" s="1"/>
       <c r="B382" s="1"/>
       <c r="G382" s="5"/>
-      <c r="H382" s="5"/>
+      <c r="H382" s="6"/>
     </row>
     <row r="383" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A383" s="1"/>
       <c r="B383" s="1"/>
       <c r="G383" s="5"/>
-      <c r="H383" s="5"/>
+      <c r="H383" s="6"/>
     </row>
     <row r="384" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A384" s="1"/>
       <c r="B384" s="1"/>
       <c r="G384" s="5"/>
-      <c r="H384" s="5"/>
+      <c r="H384" s="6"/>
     </row>
     <row r="385" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A385" s="1"/>
       <c r="B385" s="1"/>
       <c r="G385" s="5"/>
-      <c r="H385" s="5"/>
+      <c r="H385" s="6"/>
     </row>
     <row r="386" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A386" s="1"/>
       <c r="B386" s="1"/>
       <c r="G386" s="5"/>
-      <c r="H386" s="5"/>
+      <c r="H386" s="6"/>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A387" s="1"/>
       <c r="B387" s="1"/>
       <c r="G387" s="5"/>
-      <c r="H387" s="5"/>
+      <c r="H387" s="6"/>
     </row>
     <row r="388" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A388" s="1"/>
       <c r="B388" s="1"/>
       <c r="G388" s="5"/>
-      <c r="H388" s="5"/>
+      <c r="H388" s="6"/>
     </row>
     <row r="389" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A389" s="1"/>
       <c r="B389" s="1"/>
       <c r="G389" s="5"/>
-      <c r="H389" s="5"/>
+      <c r="H389" s="6"/>
     </row>
     <row r="390" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A390" s="1"/>
       <c r="B390" s="1"/>
       <c r="G390" s="5"/>
-      <c r="H390" s="5"/>
+      <c r="H390" s="6"/>
     </row>
     <row r="391" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A391" s="1"/>
       <c r="B391" s="1"/>
       <c r="G391" s="5"/>
-      <c r="H391" s="5"/>
+      <c r="H391" s="6"/>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A392" s="1"/>
       <c r="B392" s="1"/>
       <c r="G392" s="5"/>
-      <c r="H392" s="5"/>
+      <c r="H392" s="6"/>
     </row>
     <row r="393" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A393" s="1"/>
       <c r="B393" s="1"/>
       <c r="G393" s="5"/>
-      <c r="H393" s="5"/>
+      <c r="H393" s="6"/>
     </row>
     <row r="394" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A394" s="1"/>
       <c r="B394" s="1"/>
       <c r="G394" s="5"/>
-      <c r="H394" s="5"/>
+      <c r="H394" s="6"/>
     </row>
     <row r="395" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A395" s="1"/>
       <c r="B395" s="1"/>
       <c r="G395" s="5"/>
-      <c r="H395" s="5"/>
+      <c r="H395" s="6"/>
     </row>
     <row r="396" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A396" s="1"/>
       <c r="B396" s="1"/>
       <c r="G396" s="5"/>
-      <c r="H396" s="5"/>
+      <c r="H396" s="6"/>
     </row>
     <row r="397" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A397" s="1"/>
       <c r="B397" s="1"/>
       <c r="G397" s="5"/>
-      <c r="H397" s="5"/>
+      <c r="H397" s="6"/>
     </row>
     <row r="398" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A398" s="1"/>
       <c r="B398" s="1"/>
       <c r="G398" s="5"/>
-      <c r="H398" s="5"/>
+      <c r="H398" s="6"/>
     </row>
     <row r="399" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A399" s="1"/>
       <c r="B399" s="1"/>
       <c r="G399" s="5"/>
-      <c r="H399" s="5"/>
+      <c r="H399" s="6"/>
     </row>
     <row r="400" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A400" s="1"/>
       <c r="B400" s="1"/>
       <c r="G400" s="5"/>
-      <c r="H400" s="5"/>
+      <c r="H400" s="6"/>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A401" s="1"/>
       <c r="B401" s="1"/>
       <c r="G401" s="5"/>
-      <c r="H401" s="5"/>
+      <c r="H401" s="6"/>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A402" s="1"/>
       <c r="B402" s="1"/>
       <c r="G402" s="5"/>
-      <c r="H402" s="5"/>
+      <c r="H402" s="6"/>
     </row>
     <row r="403" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A403" s="1"/>
       <c r="B403" s="1"/>
       <c r="G403" s="5"/>
-      <c r="H403" s="5"/>
+      <c r="H403" s="6"/>
     </row>
     <row r="404" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A404" s="1"/>
       <c r="B404" s="1"/>
       <c r="G404" s="5"/>
-      <c r="H404" s="5"/>
+      <c r="H404" s="6"/>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A405" s="1"/>
       <c r="B405" s="1"/>
       <c r="G405" s="5"/>
-      <c r="H405" s="5"/>
+      <c r="H405" s="6"/>
     </row>
     <row r="406" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A406" s="1"/>
       <c r="B406" s="1"/>
       <c r="G406" s="5"/>
-      <c r="H406" s="5"/>
+      <c r="H406" s="6"/>
     </row>
     <row r="407" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A407" s="1"/>
       <c r="B407" s="1"/>
       <c r="G407" s="5"/>
-      <c r="H407" s="5"/>
+      <c r="H407" s="6"/>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A408" s="1"/>
       <c r="B408" s="1"/>
       <c r="G408" s="5"/>
-      <c r="H408" s="5"/>
+      <c r="H408" s="6"/>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A409" s="1"/>
       <c r="B409" s="1"/>
       <c r="G409" s="5"/>
-      <c r="H409" s="5"/>
+      <c r="H409" s="6"/>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A410" s="1"/>
       <c r="B410" s="1"/>
       <c r="G410" s="5"/>
-      <c r="H410" s="5"/>
+      <c r="H410" s="6"/>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A411" s="1"/>
       <c r="B411" s="1"/>
       <c r="G411" s="5"/>
-      <c r="H411" s="5"/>
+      <c r="H411" s="6"/>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A412" s="1"/>
       <c r="B412" s="1"/>
       <c r="G412" s="5"/>
-      <c r="H412" s="5"/>
+      <c r="H412" s="6"/>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A413" s="1"/>
       <c r="B413" s="1"/>
       <c r="G413" s="5"/>
-      <c r="H413" s="5"/>
+      <c r="H413" s="6"/>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A414" s="1"/>
       <c r="B414" s="1"/>
       <c r="G414" s="5"/>
-      <c r="H414" s="5"/>
+      <c r="H414" s="6"/>
     </row>
     <row r="415" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A415" s="1"/>
       <c r="B415" s="1"/>
       <c r="G415" s="5"/>
-      <c r="H415" s="5"/>
+      <c r="H415" s="6"/>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A416" s="1"/>
       <c r="B416" s="1"/>
       <c r="G416" s="5"/>
-      <c r="H416" s="5"/>
+      <c r="H416" s="6"/>
     </row>
     <row r="417" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A417" s="1"/>
       <c r="B417" s="1"/>
       <c r="G417" s="5"/>
-      <c r="H417" s="5"/>
+      <c r="H417" s="6"/>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A418" s="1"/>
       <c r="B418" s="1"/>
       <c r="G418" s="5"/>
-      <c r="H418" s="5"/>
+      <c r="H418" s="6"/>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A419" s="1"/>
       <c r="B419" s="1"/>
       <c r="G419" s="5"/>
-      <c r="H419" s="5"/>
+      <c r="H419" s="6"/>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A420" s="1"/>
       <c r="B420" s="1"/>
       <c r="G420" s="5"/>
-      <c r="H420" s="5"/>
+      <c r="H420" s="6"/>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A421" s="1"/>
       <c r="B421" s="1"/>
       <c r="G421" s="5"/>
-      <c r="H421" s="5"/>
+      <c r="H421" s="6"/>
     </row>
     <row r="422" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A422" s="1"/>
       <c r="B422" s="1"/>
       <c r="G422" s="5"/>
-      <c r="H422" s="5"/>
+      <c r="H422" s="6"/>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A423" s="1"/>
       <c r="B423" s="1"/>
       <c r="G423" s="5"/>
-      <c r="H423" s="5"/>
+      <c r="H423" s="6"/>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A424" s="1"/>
       <c r="B424" s="1"/>
       <c r="G424" s="5"/>
-      <c r="H424" s="5"/>
+      <c r="H424" s="6"/>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A425" s="1"/>
       <c r="B425" s="1"/>
       <c r="G425" s="5"/>
-      <c r="H425" s="5"/>
+      <c r="H425" s="6"/>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A426" s="1"/>
       <c r="B426" s="1"/>
       <c r="G426" s="5"/>
-      <c r="H426" s="5"/>
+      <c r="H426" s="6"/>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A427" s="1"/>
       <c r="B427" s="1"/>
       <c r="G427" s="5"/>
-      <c r="H427" s="5"/>
+      <c r="H427" s="6"/>
     </row>
     <row r="428" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A428" s="1"/>
       <c r="B428" s="1"/>
       <c r="G428" s="5"/>
-      <c r="H428" s="5"/>
+      <c r="H428" s="6"/>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A429" s="1"/>
       <c r="B429" s="1"/>
       <c r="G429" s="5"/>
-      <c r="H429" s="5"/>
+      <c r="H429" s="6"/>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A430" s="1"/>
       <c r="B430" s="1"/>
       <c r="G430" s="5"/>
-      <c r="H430" s="5"/>
+      <c r="H430" s="6"/>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A431" s="1"/>
       <c r="B431" s="1"/>
       <c r="G431" s="5"/>
-      <c r="H431" s="5"/>
+      <c r="H431" s="6"/>
     </row>
     <row r="432" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A432" s="1"/>
       <c r="B432" s="1"/>
       <c r="G432" s="5"/>
-      <c r="H432" s="5"/>
+      <c r="H432" s="6"/>
     </row>
     <row r="433" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A433" s="1"/>
       <c r="B433" s="1"/>
       <c r="G433" s="5"/>
-      <c r="H433" s="5"/>
+      <c r="H433" s="6"/>
     </row>
     <row r="434" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A434" s="1"/>
       <c r="B434" s="1"/>
       <c r="G434" s="5"/>
-      <c r="H434" s="5"/>
+      <c r="H434" s="6"/>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A435" s="1"/>
       <c r="B435" s="1"/>
       <c r="G435" s="5"/>
-      <c r="H435" s="5"/>
+      <c r="H435" s="6"/>
     </row>
     <row r="436" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A436" s="1"/>
       <c r="B436" s="1"/>
       <c r="G436" s="5"/>
-      <c r="H436" s="5"/>
+      <c r="H436" s="6"/>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A437" s="1"/>
       <c r="B437" s="1"/>
       <c r="G437" s="5"/>
-      <c r="H437" s="5"/>
+      <c r="H437" s="6"/>
     </row>
     <row r="438" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A438" s="1"/>
       <c r="B438" s="1"/>
       <c r="G438" s="5"/>
-      <c r="H438" s="5"/>
+      <c r="H438" s="6"/>
     </row>
     <row r="439" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A439" s="1"/>
       <c r="B439" s="1"/>
       <c r="G439" s="5"/>
-      <c r="H439" s="5"/>
+      <c r="H439" s="6"/>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A440" s="1"/>
       <c r="B440" s="1"/>
       <c r="G440" s="5"/>
-      <c r="H440" s="5"/>
+      <c r="H440" s="6"/>
     </row>
     <row r="441" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A441" s="1"/>
       <c r="B441" s="1"/>
       <c r="G441" s="5"/>
-      <c r="H441" s="5"/>
+      <c r="H441" s="6"/>
     </row>
     <row r="442" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A442" s="1"/>
       <c r="B442" s="1"/>
       <c r="G442" s="5"/>
-      <c r="H442" s="5"/>
+      <c r="H442" s="6"/>
     </row>
     <row r="443" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A443" s="1"/>
       <c r="B443" s="1"/>
       <c r="G443" s="5"/>
-      <c r="H443" s="5"/>
+      <c r="H443" s="6"/>
     </row>
     <row r="444" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A444" s="1"/>
       <c r="B444" s="1"/>
       <c r="G444" s="5"/>
-      <c r="H444" s="5"/>
+      <c r="H444" s="6"/>
     </row>
     <row r="445" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A445" s="1"/>
       <c r="B445" s="1"/>
       <c r="G445" s="5"/>
-      <c r="H445" s="5"/>
+      <c r="H445" s="6"/>
     </row>
     <row r="446" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A446" s="1"/>
       <c r="B446" s="1"/>
       <c r="G446" s="5"/>
-      <c r="H446" s="5"/>
+      <c r="H446" s="6"/>
     </row>
     <row r="447" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A447" s="1"/>
       <c r="B447" s="1"/>
       <c r="G447" s="5"/>
-      <c r="H447" s="5"/>
+      <c r="H447" s="6"/>
     </row>
     <row r="448" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A448" s="1"/>
       <c r="B448" s="1"/>
       <c r="G448" s="5"/>
-      <c r="H448" s="5"/>
+      <c r="H448" s="6"/>
     </row>
     <row r="449" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A449" s="1"/>
       <c r="B449" s="1"/>
       <c r="G449" s="5"/>
-      <c r="H449" s="5"/>
+      <c r="H449" s="6"/>
     </row>
     <row r="450" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A450" s="1"/>
       <c r="B450" s="1"/>
       <c r="G450" s="5"/>
-      <c r="H450" s="5"/>
+      <c r="H450" s="6"/>
     </row>
     <row r="451" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A451" s="1"/>
       <c r="B451" s="1"/>
       <c r="G451" s="5"/>
-      <c r="H451" s="5"/>
+      <c r="H451" s="6"/>
     </row>
     <row r="452" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A452" s="1"/>
       <c r="B452" s="1"/>
       <c r="G452" s="5"/>
-      <c r="H452" s="5"/>
+      <c r="H452" s="6"/>
     </row>
     <row r="453" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A453" s="1"/>
       <c r="B453" s="1"/>
       <c r="G453" s="5"/>
-      <c r="H453" s="5"/>
+      <c r="H453" s="6"/>
     </row>
     <row r="454" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A454" s="1"/>
       <c r="B454" s="1"/>
       <c r="G454" s="5"/>
-      <c r="H454" s="5"/>
+      <c r="H454" s="6"/>
     </row>
     <row r="455" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A455" s="1"/>
       <c r="B455" s="1"/>
       <c r="G455" s="5"/>
-      <c r="H455" s="5"/>
+      <c r="H455" s="6"/>
     </row>
     <row r="456" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A456" s="1"/>
       <c r="B456" s="1"/>
       <c r="G456" s="5"/>
-      <c r="H456" s="5"/>
+      <c r="H456" s="6"/>
     </row>
     <row r="457" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A457" s="1"/>
       <c r="B457" s="1"/>
       <c r="G457" s="5"/>
-      <c r="H457" s="5"/>
+      <c r="H457" s="6"/>
     </row>
     <row r="458" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A458" s="1"/>
       <c r="B458" s="1"/>
       <c r="G458" s="5"/>
-      <c r="H458" s="5"/>
+      <c r="H458" s="6"/>
     </row>
     <row r="459" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A459" s="1"/>
       <c r="B459" s="1"/>
       <c r="G459" s="5"/>
-      <c r="H459" s="5"/>
+      <c r="H459" s="6"/>
     </row>
     <row r="460" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A460" s="1"/>
       <c r="B460" s="1"/>
       <c r="G460" s="5"/>
-      <c r="H460" s="5"/>
+      <c r="H460" s="6"/>
     </row>
     <row r="461" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A461" s="1"/>
       <c r="B461" s="1"/>
       <c r="G461" s="5"/>
-      <c r="H461" s="5"/>
+      <c r="H461" s="6"/>
     </row>
     <row r="462" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A462" s="1"/>
       <c r="B462" s="1"/>
       <c r="G462" s="5"/>
-      <c r="H462" s="5"/>
+      <c r="H462" s="6"/>
     </row>
     <row r="463" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A463" s="1"/>
       <c r="B463" s="1"/>
       <c r="G463" s="5"/>
-      <c r="H463" s="5"/>
+      <c r="H463" s="6"/>
     </row>
     <row r="464" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A464" s="1"/>
       <c r="B464" s="1"/>
       <c r="G464" s="5"/>
-      <c r="H464" s="5"/>
+      <c r="H464" s="6"/>
     </row>
     <row r="465" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A465" s="1"/>
       <c r="B465" s="1"/>
       <c r="G465" s="5"/>
-      <c r="H465" s="5"/>
+      <c r="H465" s="6"/>
     </row>
     <row r="466" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A466" s="1"/>
       <c r="B466" s="1"/>
       <c r="G466" s="5"/>
-      <c r="H466" s="5"/>
+      <c r="H466" s="6"/>
     </row>
     <row r="467" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A467" s="1"/>
       <c r="B467" s="1"/>
       <c r="G467" s="5"/>
-      <c r="H467" s="5"/>
+      <c r="H467" s="6"/>
     </row>
     <row r="468" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A468" s="1"/>
       <c r="B468" s="1"/>
       <c r="G468" s="5"/>
-      <c r="H468" s="5"/>
+      <c r="H468" s="6"/>
     </row>
     <row r="469" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A469" s="1"/>
       <c r="B469" s="1"/>
       <c r="G469" s="5"/>
-      <c r="H469" s="5"/>
+      <c r="H469" s="6"/>
     </row>
     <row r="470" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A470" s="1"/>
       <c r="B470" s="1"/>
       <c r="G470" s="5"/>
-      <c r="H470" s="5"/>
+      <c r="H470" s="6"/>
     </row>
     <row r="471" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A471" s="1"/>
       <c r="B471" s="1"/>
       <c r="G471" s="5"/>
-      <c r="H471" s="5"/>
+      <c r="H471" s="6"/>
     </row>
     <row r="472" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A472" s="1"/>
       <c r="B472" s="1"/>
       <c r="G472" s="5"/>
-      <c r="H472" s="5"/>
+      <c r="H472" s="6"/>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A473" s="1"/>
       <c r="B473" s="1"/>
       <c r="G473" s="5"/>
-      <c r="H473" s="5"/>
+      <c r="H473" s="6"/>
     </row>
     <row r="474" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A474" s="1"/>
       <c r="B474" s="1"/>
       <c r="G474" s="5"/>
-      <c r="H474" s="5"/>
+      <c r="H474" s="6"/>
     </row>
     <row r="475" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A475" s="1"/>
       <c r="B475" s="1"/>
       <c r="G475" s="5"/>
-      <c r="H475" s="5"/>
+      <c r="H475" s="6"/>
     </row>
     <row r="476" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A476" s="1"/>
       <c r="B476" s="1"/>
       <c r="G476" s="5"/>
-      <c r="H476" s="5"/>
+      <c r="H476" s="6"/>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A477" s="1"/>
       <c r="B477" s="1"/>
       <c r="G477" s="5"/>
-      <c r="H477" s="5"/>
+      <c r="H477" s="6"/>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A478" s="1"/>
       <c r="B478" s="1"/>
       <c r="G478" s="5"/>
-      <c r="H478" s="5"/>
+      <c r="H478" s="6"/>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A479" s="1"/>
       <c r="B479" s="1"/>
       <c r="G479" s="5"/>
-      <c r="H479" s="5"/>
+      <c r="H479" s="6"/>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A480" s="1"/>
       <c r="B480" s="1"/>
       <c r="G480" s="5"/>
-      <c r="H480" s="5"/>
+      <c r="H480" s="6"/>
     </row>
     <row r="481" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A481" s="1"/>
       <c r="B481" s="1"/>
       <c r="G481" s="5"/>
-      <c r="H481" s="5"/>
+      <c r="H481" s="6"/>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A482" s="1"/>
       <c r="B482" s="1"/>
       <c r="G482" s="5"/>
-      <c r="H482" s="5"/>
+      <c r="H482" s="6"/>
     </row>
     <row r="483" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A483" s="1"/>
       <c r="B483" s="1"/>
       <c r="G483" s="5"/>
-      <c r="H483" s="5"/>
+      <c r="H483" s="6"/>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A484" s="1"/>
       <c r="B484" s="1"/>
       <c r="G484" s="5"/>
-      <c r="H484" s="5"/>
+      <c r="H484" s="6"/>
     </row>
     <row r="485" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A485" s="1"/>
       <c r="B485" s="1"/>
       <c r="G485" s="5"/>
-      <c r="H485" s="5"/>
+      <c r="H485" s="6"/>
     </row>
     <row r="486" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A486" s="1"/>
       <c r="B486" s="1"/>
       <c r="G486" s="5"/>
-      <c r="H486" s="5"/>
+      <c r="H486" s="6"/>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A487" s="1"/>
       <c r="B487" s="1"/>
       <c r="G487" s="5"/>
-      <c r="H487" s="5"/>
+      <c r="H487" s="6"/>
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A488" s="1"/>
       <c r="B488" s="1"/>
       <c r="G488" s="5"/>
-      <c r="H488" s="5"/>
+      <c r="H488" s="6"/>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A489" s="1"/>
       <c r="B489" s="1"/>
       <c r="G489" s="5"/>
-      <c r="H489" s="5"/>
+      <c r="H489" s="6"/>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A490" s="1"/>
       <c r="B490" s="1"/>
       <c r="G490" s="5"/>
-      <c r="H490" s="5"/>
+      <c r="H490" s="6"/>
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A491" s="1"/>
       <c r="B491" s="1"/>
       <c r="G491" s="5"/>
-      <c r="H491" s="5"/>
+      <c r="H491" s="6"/>
     </row>
     <row r="492" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A492" s="1"/>
       <c r="B492" s="1"/>
       <c r="G492" s="5"/>
-      <c r="H492" s="5"/>
+      <c r="H492" s="6"/>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A493" s="1"/>
       <c r="B493" s="1"/>
       <c r="G493" s="5"/>
-      <c r="H493" s="5"/>
+      <c r="H493" s="6"/>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A494" s="1"/>
       <c r="B494" s="1"/>
       <c r="G494" s="5"/>
-      <c r="H494" s="5"/>
+      <c r="H494" s="6"/>
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A495" s="1"/>
       <c r="B495" s="1"/>
       <c r="G495" s="5"/>
-      <c r="H495" s="5"/>
+      <c r="H495" s="6"/>
     </row>
     <row r="496" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A496" s="1"/>
       <c r="B496" s="1"/>
       <c r="G496" s="5"/>
-      <c r="H496" s="5"/>
+      <c r="H496" s="6"/>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A497" s="1"/>
       <c r="B497" s="1"/>
       <c r="G497" s="5"/>
-      <c r="H497" s="5"/>
+      <c r="H497" s="6"/>
     </row>
     <row r="498" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A498" s="1"/>
       <c r="B498" s="1"/>
       <c r="G498" s="5"/>
-      <c r="H498" s="5"/>
+      <c r="H498" s="6"/>
     </row>
     <row r="499" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A499" s="1"/>
       <c r="B499" s="1"/>
       <c r="G499" s="5"/>
-      <c r="H499" s="5"/>
+      <c r="H499" s="6"/>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A500" s="1"/>
       <c r="B500" s="1"/>
       <c r="G500" s="5"/>
-      <c r="H500" s="5"/>
+      <c r="H500" s="6"/>
     </row>
     <row r="501" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A501" s="1"/>
       <c r="B501" s="1"/>
       <c r="G501" s="5"/>
-      <c r="H501" s="5"/>
+      <c r="H501" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C1A2511-01CE-A94B-B998-1A6032BA3890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E6C045-6722-B44E-B053-772DDA96A661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="36000" windowHeight="22600" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="104220" yWindow="-7500" windowWidth="36000" windowHeight="22600" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
@@ -110,9 +110,6 @@
     <t>;20260114000000000001;20260114000000000002</t>
   </si>
   <si>
-    <t>136064-140-10</t>
-  </si>
-  <si>
     <t>Today</t>
   </si>
   <si>
@@ -120,6 +117,9 @@
   </si>
   <si>
     <t>0215056616</t>
+  </si>
+  <si>
+    <t>394055-100-7</t>
   </si>
 </sst>
 </file>
@@ -576,11 +576,11 @@
         <v>6</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E2" s="3"/>
       <c r="G2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I2" t="s">
         <v>20</v>
@@ -589,7 +589,7 @@
         <v>19</v>
       </c>
       <c r="K2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -650,7 +650,7 @@
         <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F2" s="1"/>
       <c r="G2" s="7"/>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10208"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E6C045-6722-B44E-B053-772DDA96A661}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B9220C-06C8-4949-A946-677546ABACD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="104220" yWindow="-7500" windowWidth="36000" windowHeight="22600" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="-37120" yWindow="-740" windowWidth="36000" windowHeight="21000" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
@@ -119,7 +119,7 @@
     <t>0215056616</t>
   </si>
   <si>
-    <t>394055-100-7</t>
+    <t>AR4999-101-XL</t>
   </si>
 </sst>
 </file>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B9220C-06C8-4949-A946-677546ABACD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365E2589-D92C-C545-92B9-3628F4B61C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37120" yWindow="-740" windowWidth="36000" windowHeight="21000" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="-37120" yWindow="-3000" windowWidth="36000" windowHeight="21000" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="44">
   <si>
     <t>ASN_FLAG</t>
   </si>
@@ -119,7 +119,58 @@
     <t>0215056616</t>
   </si>
   <si>
-    <t>AR4999-101-XL</t>
+    <t>HQ0027-744-4XL</t>
+  </si>
+  <si>
+    <t>HQ0027-744-M</t>
+  </si>
+  <si>
+    <t>HQ0027-100-M</t>
+  </si>
+  <si>
+    <t>HQ0027-100-5XL</t>
+  </si>
+  <si>
+    <t>HQ0027-010-3XL</t>
+  </si>
+  <si>
+    <t>HQ0027-010-L</t>
+  </si>
+  <si>
+    <t>HJ2624-451-L</t>
+  </si>
+  <si>
+    <t>HJ2624-451-XL</t>
+  </si>
+  <si>
+    <t>HJ2534-010-L</t>
+  </si>
+  <si>
+    <t>HJ2534-010-M</t>
+  </si>
+  <si>
+    <t>HJ2219-100-3XL</t>
+  </si>
+  <si>
+    <t>HJ2219-100-S</t>
+  </si>
+  <si>
+    <t>HJ2160-234-S</t>
+  </si>
+  <si>
+    <t>HJ2160-234-4XL</t>
+  </si>
+  <si>
+    <t>HJ0958-233-4XL</t>
+  </si>
+  <si>
+    <t>HJ0958-233-3XL</t>
+  </si>
+  <si>
+    <t>HJ0599-010-L</t>
+  </si>
+  <si>
+    <t>HJ0599-010-3XL</t>
   </si>
 </sst>
 </file>
@@ -518,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{627F3B23-F0A4-3C4D-9FCD-57514569CCB0}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.33203125" bestFit="1" customWidth="1"/>
@@ -590,6 +641,193 @@
       </c>
       <c r="K2" t="s">
         <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3">
+        <v>1081</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>1081</v>
+      </c>
+      <c r="B4" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5">
+        <v>1081</v>
+      </c>
+      <c r="B5" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A6">
+        <v>1081</v>
+      </c>
+      <c r="B6" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7">
+        <v>1081</v>
+      </c>
+      <c r="B7" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8">
+        <v>1081</v>
+      </c>
+      <c r="B8" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A9">
+        <v>1081</v>
+      </c>
+      <c r="B9" t="s">
+        <v>6</v>
+      </c>
+      <c r="G9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>1081</v>
+      </c>
+      <c r="B10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A11">
+        <v>1081</v>
+      </c>
+      <c r="B11" t="s">
+        <v>6</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>1081</v>
+      </c>
+      <c r="B12" t="s">
+        <v>6</v>
+      </c>
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>1081</v>
+      </c>
+      <c r="B13" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>1081</v>
+      </c>
+      <c r="B14" t="s">
+        <v>6</v>
+      </c>
+      <c r="G14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>1081</v>
+      </c>
+      <c r="B15" t="s">
+        <v>6</v>
+      </c>
+      <c r="G15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16">
+        <v>1081</v>
+      </c>
+      <c r="B16" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>1081</v>
+      </c>
+      <c r="B17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>1081</v>
+      </c>
+      <c r="B18" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>1081</v>
+      </c>
+      <c r="B19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/J30/Input_files/Inventory_Worksheet.xlsx
+++ b/J30/Input_files/Inventory_Worksheet.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/vgana3/Documents/GitHub/Nike/J30/Input_files/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{365E2589-D92C-C545-92B9-3628F4B61C15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{092662EE-35F0-F648-B219-AAC932B1FA28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37120" yWindow="-3000" windowWidth="36000" windowHeight="21000" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
+    <workbookView xWindow="18060" yWindow="-21000" windowWidth="19200" windowHeight="21000" activeTab="1" xr2:uid="{64371699-0414-B444-9D3A-2B17F89C9B52}"/>
   </bookViews>
   <sheets>
     <sheet name="iLPN_Info" sheetId="1" r:id="rId1"/>
-    <sheet name="ItemSearch" sheetId="2" r:id="rId2"/>
-    <sheet name="Recall_iLPN" sheetId="4" r:id="rId3"/>
-    <sheet name="Backup" sheetId="3" r:id="rId4"/>
+    <sheet name="CubiScan" sheetId="5" r:id="rId2"/>
+    <sheet name="ItemSearch" sheetId="2" r:id="rId3"/>
+    <sheet name="Recall_iLPN" sheetId="4" r:id="rId4"/>
+    <sheet name="Backup" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="52">
   <si>
     <t>ASN_FLAG</t>
   </si>
@@ -171,6 +172,30 @@
   </si>
   <si>
     <t>HJ0599-010-3XL</t>
+  </si>
+  <si>
+    <t>Item</t>
+  </si>
+  <si>
+    <t>Length</t>
+  </si>
+  <si>
+    <t>Width</t>
+  </si>
+  <si>
+    <t>Height</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>GTIN</t>
+  </si>
+  <si>
+    <t>Conveyable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PickingMHEConveyable </t>
   </si>
 </sst>
 </file>
@@ -837,6 +862,58 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C4AC4F3-4A4D-E94F-B11E-39528B29A435}">
+  <dimension ref="A1:J2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="20.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F1" t="s">
+        <v>46</v>
+      </c>
+      <c r="G1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I1" t="s">
+        <v>50</v>
+      </c>
+      <c r="J1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4038F4B-96B4-9849-B09E-D02D2C5271C4}">
   <dimension ref="A1:H501"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3909,7 +3986,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{81303470-562A-AE41-967B-7DC015162790}">
   <dimension ref="A1:C2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -3944,7 +4021,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{576B9CE8-4226-8341-81D1-B38F48D3C014}">
   <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
